--- a/Analysis/Results/literature_gap_matrix.xlsx
+++ b/Analysis/Results/literature_gap_matrix.xlsx
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C2" s="5" t="n">
         <v>75</v>
@@ -843,7 +843,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>69</v>
@@ -855,7 +855,7 @@
         <v>213</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>104</v>
@@ -885,10 +885,10 @@
         <v>1239</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S3" s="7" t="n">
         <v>40</v>
@@ -903,7 +903,7 @@
         <v>46</v>
       </c>
       <c r="W3" s="6" t="n">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="X3" s="8" t="n">
         <v>4</v>
@@ -921,10 +921,10 @@
         <v>12</v>
       </c>
       <c r="AC3" s="6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AD3" s="10" t="n">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="AE3" s="6" t="n">
         <v>507</v>
@@ -943,7 +943,7 @@
         <v>69</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>24</v>
@@ -958,7 +958,7 @@
         <v>113</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>57</v>
@@ -1006,7 +1006,7 @@
         <v>37</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Z4" s="8" t="n">
         <v>3</v>
@@ -1015,7 +1015,7 @@
         <v>148</v>
       </c>
       <c r="AB4" s="6" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AC4" s="7" t="n">
         <v>31</v>
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>533</v>
@@ -1231,7 +1231,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>178</v>
@@ -1243,7 +1243,7 @@
         <v>533</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>166</v>
@@ -1252,7 +1252,7 @@
         <v>53</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>127</v>
@@ -1267,16 +1267,16 @@
         <v>50</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S7" s="7" t="n">
         <v>24</v>
@@ -1285,7 +1285,7 @@
         <v>289</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>79</v>
@@ -1303,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="AA7" s="6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AB7" s="8" t="n">
         <v>2</v>
@@ -1343,7 +1343,7 @@
         <v>166</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>66</v>
@@ -1409,7 +1409,7 @@
         <v>12</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AE8" s="7" t="n">
         <v>27</v>
@@ -1428,7 +1428,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>7</v>
@@ -1443,7 +1443,7 @@
         <v>66</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>15</v>
@@ -1467,7 +1467,7 @@
         <v>55</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R9" s="7" t="n">
         <v>17</v>
@@ -1481,8 +1481,8 @@
       <c r="U9" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
+      <c r="V9" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="W9" s="7" t="n">
         <v>17</v>
@@ -1534,7 +1534,7 @@
         <v>60</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>70</v>
@@ -1543,16 +1543,16 @@
         <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>34</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>16</v>
@@ -1561,28 +1561,28 @@
         <v>110</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S10" s="5" t="n">
         <v>56</v>
       </c>
       <c r="T10" s="6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="V10" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>29</v>
@@ -1594,7 +1594,7 @@
         <v>48</v>
       </c>
       <c r="AA10" s="6" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>16</v>
@@ -1603,7 +1603,7 @@
         <v>68</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>2776</v>
+        <v>2783</v>
       </c>
       <c r="AE10" s="6" t="n">
         <v>317</v>
@@ -1640,10 +1640,10 @@
         <v>4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>13</v>
@@ -1673,7 +1673,7 @@
         <v>81</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="V11" s="7" t="n">
         <v>23</v>
@@ -1691,7 +1691,7 @@
         <v>12</v>
       </c>
       <c r="AA11" s="6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AB11" s="7" t="n">
         <v>12</v>
@@ -1700,7 +1700,7 @@
         <v>16</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="AE11" s="5" t="n">
         <v>119</v>
@@ -1834,7 +1834,7 @@
         <v>112</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>88</v>
@@ -1843,7 +1843,7 @@
         <v>8</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>158</v>
@@ -1852,10 +1852,10 @@
         <v>221</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R13" s="6" t="n">
         <v>334</v>
@@ -1873,7 +1873,7 @@
         <v>38</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>10</v>
@@ -1885,7 +1885,7 @@
         <v>9</v>
       </c>
       <c r="AA13" s="6" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB13" s="8" t="n">
         <v>9</v>
@@ -1894,7 +1894,7 @@
         <v>521</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>271</v>
@@ -2019,7 +2019,7 @@
         <v>255</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>87</v>
@@ -2043,13 +2043,13 @@
         <v>14</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>276</v>
@@ -2116,7 +2116,7 @@
         <v>319</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>98</v>
@@ -2125,7 +2125,7 @@
         <v>55</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K16" s="5" t="n">
         <v>184</v>
@@ -2134,22 +2134,22 @@
         <v>31</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>91</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="S16" s="7" t="n">
         <v>18</v>
@@ -2185,7 +2185,7 @@
         <v>533</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="AE16" s="6" t="n">
         <v>232</v>
@@ -2201,7 +2201,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>49</v>
@@ -2213,16 +2213,16 @@
         <v>230</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>48</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>45</v>
@@ -2231,22 +2231,22 @@
         <v>2</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>40</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S17" s="7" t="n">
         <v>21</v>
@@ -2258,7 +2258,7 @@
         <v>160</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W17" s="5" t="n">
         <v>87</v>
@@ -2298,7 +2298,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>72</v>
@@ -2310,7 +2310,7 @@
         <v>235</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>51</v>
@@ -2319,7 +2319,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>80</v>
@@ -2337,22 +2337,22 @@
         <v>276</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="S18" s="5" t="n">
         <v>50</v>
       </c>
       <c r="T18" s="10" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="V18" s="5" t="n">
         <v>68</v>
@@ -2379,7 +2379,7 @@
         <v>349</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="AE18" s="5" t="n">
         <v>57</v>
@@ -2513,7 +2513,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>81</v>
@@ -2537,13 +2537,13 @@
         <v>76</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="S20" s="7" t="n">
         <v>14</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="U20" s="6" t="n">
         <v>985</v>
@@ -2573,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>2958</v>
+        <v>2960</v>
       </c>
       <c r="AE20" s="5" t="n">
         <v>58</v>
@@ -2601,7 +2601,7 @@
         <v>221</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>71</v>
@@ -2610,10 +2610,10 @@
         <v>23</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>11</v>
@@ -2634,7 +2634,7 @@
         <v>160</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="S21" s="7" t="n">
         <v>20</v>
@@ -2643,7 +2643,7 @@
         <v>985</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="V21" s="6" t="n">
         <v>318</v>
@@ -2703,11 +2703,11 @@
       <c r="H22" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I22" s="9" t="n">
-        <v>0</v>
+      <c r="I22" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>23</v>
@@ -2728,7 +2728,7 @@
         <v>80</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>68</v>
@@ -2743,10 +2743,10 @@
         <v>318</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>7</v>
@@ -2783,7 +2783,7 @@
         <v>14</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>90</v>
@@ -2804,7 +2804,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>1608</v>
@@ -2813,7 +2813,7 @@
         <v>22</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N23" s="7" t="n">
         <v>42</v>
@@ -2840,10 +2840,10 @@
         <v>1309</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>26</v>
@@ -2861,13 +2861,13 @@
         <v>23</v>
       </c>
       <c r="AC23" s="6" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>8244</v>
+        <v>8257</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24">
@@ -2943,10 +2943,10 @@
         <v>26</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Z24" s="7" t="n">
         <v>12</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AE24" s="8" t="n">
         <v>6</v>
@@ -2980,7 +2980,7 @@
         <v>37</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>12</v>
@@ -3040,10 +3040,10 @@
         <v>252</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="Z25" s="5" t="n">
         <v>75</v>
@@ -3183,7 +3183,7 @@
         <v>310</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>43</v>
@@ -3192,16 +3192,16 @@
         <v>8</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L27" s="7" t="n">
         <v>48</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N27" s="7" t="n">
         <v>20</v>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="AB27" s="7" t="n">
         <v>30</v>
@@ -3252,7 +3252,7 @@
         <v>325</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="AE27" s="6" t="n">
         <v>283</v>
@@ -3271,7 +3271,7 @@
         <v>12</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>1</v>
@@ -3343,7 +3343,7 @@
         <v>30</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AC28" s="7" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>31</v>
@@ -3425,7 +3425,7 @@
         <v>4</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="X29" s="7" t="n">
         <v>14</v>
@@ -3443,10 +3443,10 @@
         <v>10</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="AD29" s="10" t="n">
-        <v>3632</v>
+        <v>3636</v>
       </c>
       <c r="AE29" s="7" t="n">
         <v>38</v>
@@ -3462,7 +3462,7 @@
         <v>245</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>1030</v>
@@ -3477,22 +3477,22 @@
         <v>1563</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>221</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2776</v>
+        <v>2783</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>116</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>341</v>
@@ -3501,19 +3501,19 @@
         <v>868</v>
       </c>
       <c r="P30" s="10" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>373</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="S30" s="5" t="n">
         <v>132</v>
       </c>
       <c r="T30" s="10" t="n">
-        <v>2958</v>
+        <v>2960</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>2849</v>
@@ -3522,10 +3522,10 @@
         <v>578</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>8244</v>
+        <v>8257</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Y30" s="10" t="n">
         <v>1127</v>
@@ -3534,19 +3534,19 @@
         <v>728</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="AB30" s="7" t="n">
         <v>44</v>
       </c>
       <c r="AC30" s="10" t="n">
-        <v>3632</v>
+        <v>3636</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="AE30" s="6" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="31">
@@ -3619,7 +3619,7 @@
         <v>26</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>6</v>
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="AD31" s="6" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
     </row>
   </sheetData>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>1756.5</v>
+        <v>1757.1</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>2061</v>
@@ -3774,10 +3774,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>2283.2</v>
+        <v>2284</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>253</v>
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>1175.1</v>
+        <v>1175.2</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3269.1</v>
+        <v>3270.2</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -3984,13 +3984,13 @@
         <v>3</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>6176.7</v>
+        <v>6180.3</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1191.4</v>
+        <v>1192.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -4054,10 +4054,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>919.4</v>
+        <v>920.4</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>860</v>
@@ -4079,23 +4079,23 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Neuropathy</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>100</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>1779.1</v>
+        <v>2625.3</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>3220</v>
+        <v>6997</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -4109,28 +4109,28 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>Glucokinase</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
         <v>100</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>2621.3</v>
+        <v>730.8</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>983</v>
+        <v>860</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>6990</v>
+        <v>621</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
@@ -4159,13 +4159,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>730.8</v>
+        <v>1331.3</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>621</v>
+        <v>2061</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
@@ -4194,13 +4194,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>1331.3</v>
+        <v>720.1</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2061</v>
+        <v>603</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Glucokinase</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>Closed Loop / AP</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
@@ -4229,13 +4229,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>719.5</v>
+        <v>1165.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>860</v>
+        <v>693</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>602</v>
+        <v>1959</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Closed Loop / AP</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
@@ -4264,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>1164.9</v>
+        <v>646.4</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>1958</v>
+        <v>603</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>Closed Loop / AP</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>645.9</v>
+        <v>1103</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>693</v>
+        <v>621</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>602</v>
+        <v>1959</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Closed Loop / AP</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -4334,13 +4334,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>1102.7</v>
+        <v>2084.5</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>1958</v>
+        <v>6997</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
@@ -4369,13 +4369,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>2083.5</v>
+        <v>1131.3</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6990</v>
+        <v>2061</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
@@ -4404,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>1131.3</v>
+        <v>611.9</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>2061</v>
+        <v>603</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -4439,13 +4439,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>611.4</v>
+        <v>1114.8</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>621</v>
+        <v>2061</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -4459,28 +4459,28 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>Beta Cell Regen</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1113.9</v>
+        <v>1018.9</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2061</v>
+        <v>1498</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>602</v>
+        <v>693</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -4499,23 +4499,23 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Retinopathy</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1018.5</v>
+        <v>5083.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>693</v>
+        <v>17251</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -4534,23 +4534,23 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Retinopathy</t>
+          <t>Neuropathy</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>5080.5</v>
+        <v>2197.6</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17242</v>
+        <v>3224</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -4564,28 +4564,28 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Beta Cell Regen</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Neuropathy</t>
+          <t>Closed Loop / AP</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>2195.5</v>
+        <v>6355.7</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1497</v>
+        <v>20620</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3220</v>
+        <v>1959</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -4604,23 +4604,23 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Closed Loop / AP</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>6351.6</v>
+        <v>6519</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>1958</v>
+        <v>2061</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -4634,28 +4634,28 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Autoimmunity T1D</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>6516.5</v>
+        <v>1805.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>20604</v>
+        <v>4702</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2061</v>
+        <v>693</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -4674,23 +4674,23 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>1804.6</v>
+        <v>3113</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>693</v>
+        <v>2061</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -4704,28 +4704,28 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Autoimmunity T1D</t>
+          <t>Islet Transplant</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>3112</v>
+        <v>1394.4</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>4699</v>
+        <v>253</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2061</v>
+        <v>7685</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -4744,23 +4744,23 @@
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Microbiome Gut</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>1393.7</v>
+        <v>1641.2</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7678</v>
+        <v>10646</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Microbiome Gut</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>1640.9</v>
+        <v>685.4</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>10643</v>
+        <v>1857</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -4814,23 +4814,23 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Retinopathy</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>684.5</v>
+        <v>2089.1</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>1852</v>
+        <v>17251</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Retinopathy</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
@@ -4859,13 +4859,13 @@
         <v>2</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>2088.6</v>
+        <v>1913.1</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>17242</v>
+        <v>14466</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4884,23 +4884,23 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Neuropathy</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>1912.6</v>
+        <v>903.1</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>14458</v>
+        <v>3224</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>Neuropathy</t>
+          <t>Gestational DM</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
@@ -4929,13 +4929,13 @@
         <v>1</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>902.6</v>
+        <v>1988.1</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3220</v>
+        <v>15622</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -4949,28 +4949,28 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Islet Transplant</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Gestational DM</t>
+          <t>LADA</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>1987.4</v>
+        <v>2164.8</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>253</v>
+        <v>7772</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>15611</v>
+        <v>603</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4984,28 +4984,28 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>LADA</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>2162.5</v>
+        <v>2751.3</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>7768</v>
+        <v>985</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>602</v>
+        <v>7685</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -5024,23 +5024,23 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>2747.3</v>
+        <v>826.2</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>7678</v>
+        <v>693</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Neuropathy</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
@@ -5069,13 +5069,13 @@
         <v>1</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>825.4</v>
+        <v>1782</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>693</v>
+        <v>3224</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -5104,10 +5104,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1423.4</v>
+        <v>1424.8</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>2061</v>
@@ -5139,10 +5139,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>2306.7</v>
+        <v>2307.7</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>693</v>
@@ -5174,13 +5174,13 @@
         <v>16</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>10948.1</v>
+        <v>10957</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -5244,13 +5244,13 @@
         <v>1</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1664.1</v>
+        <v>1665.1</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -5279,13 +5279,13 @@
         <v>1</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1493.8</v>
+        <v>1494.7</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -5314,13 +5314,13 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3122.6</v>
+        <v>3123.7</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -5349,13 +5349,13 @@
         <v>4</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2779.1</v>
+        <v>2782.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -5384,13 +5384,13 @@
         <v>1</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>1055.9</v>
+        <v>1058.2</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -5419,13 +5419,13 @@
         <v>2</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3113.6</v>
+        <v>3114.7</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -5454,10 +5454,10 @@
         <v>3</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>2576.1</v>
+        <v>2577.7</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>2061</v>
@@ -5489,13 +5489,13 @@
         <v>4</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>7090</v>
+        <v>7096.9</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         <v>11</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>4652.3</v>
+        <v>4655.1</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -5559,13 +5559,13 @@
         <v>14</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>6288.1</v>
+        <v>6293.7</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>14</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>6006.6</v>
+        <v>6011.2</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5629,13 +5629,13 @@
         <v>4</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1864.1</v>
+        <v>1865.1</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -5699,13 +5699,13 @@
         <v>4</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1801.7</v>
+        <v>1802.2</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5734,13 +5734,13 @@
         <v>3</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1738.1</v>
+        <v>1739.1</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -5769,13 +5769,13 @@
         <v>3</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1437.9</v>
+        <v>1438.6</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -5804,13 +5804,13 @@
         <v>2</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1055.9</v>
+        <v>1056.5</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -5839,13 +5839,13 @@
         <v>8</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3900</v>
+        <v>3902</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
         <v>7</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>4001.2</v>
+        <v>4002.3</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>2061</v>
@@ -5909,10 +5909,10 @@
         <v>2</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1278.3</v>
+        <v>1278.9</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>693</v>
@@ -5944,10 +5944,10 @@
         <v>3</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>1210.1</v>
+        <v>1210.6</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>621</v>
@@ -5979,10 +5979,10 @@
         <v>5</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2204.5</v>
+        <v>2205.4</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>2061</v>
@@ -6014,13 +6014,13 @@
         <v>12</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>6067.2</v>
+        <v>6071.9</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -6049,13 +6049,13 @@
         <v>2</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1262</v>
+        <v>1263.7</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -6084,13 +6084,13 @@
         <v>6</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>3850.7</v>
+        <v>3851.7</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>4565</v>
+        <v>4566.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         <v>9</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>4683.5</v>
+        <v>4684.2</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>2061</v>
@@ -6224,13 +6224,13 @@
         <v>8</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>3456.7</v>
+        <v>3457.6</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -6259,13 +6259,13 @@
         <v>6</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>3165.3</v>
+        <v>3166.2</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         <v>7</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>3203.7</v>
+        <v>3204</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>2061</v>
@@ -6329,13 +6329,13 @@
         <v>4</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1731.5</v>
+        <v>1733.1</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -6364,13 +6364,13 @@
         <v>12</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>5012.1</v>
+        <v>5014.7</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         <v>8</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>5142.2</v>
+        <v>5143.6</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>2061</v>
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1904.3</v>
+        <v>1907.3</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -6469,10 +6469,10 @@
         <v>3</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1953.7</v>
+        <v>1956.3</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>2061</v>
@@ -6504,13 +6504,13 @@
         <v>5</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2681</v>
+        <v>2684.8</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -6539,13 +6539,13 @@
         <v>8</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>3221.8</v>
+        <v>3225.3</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -6574,13 +6574,13 @@
         <v>10</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>5320.6</v>
+        <v>5323.4</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -6609,13 +6609,13 @@
         <v>24</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>15023.4</v>
+        <v>15032.9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -6644,13 +6644,13 @@
         <v>3</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1392.3</v>
+        <v>1394.3</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -6679,13 +6679,13 @@
         <v>6</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2937.5</v>
+        <v>2939.9</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -6714,13 +6714,13 @@
         <v>5</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>3013.8</v>
+        <v>3015.5</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>2061</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -6749,13 +6749,13 @@
         <v>4</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1628.8</v>
+        <v>1631.1</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -6784,13 +6784,13 @@
         <v>14</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4227.8</v>
+        <v>4231.7</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -6819,13 +6819,13 @@
         <v>13</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>4834.2</v>
+        <v>4837.5</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -6854,13 +6854,13 @@
         <v>37</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>12000.9</v>
+        <v>12011.6</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -6889,13 +6889,13 @@
         <v>12</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>3521.9</v>
+        <v>3526.2</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -6924,13 +6924,13 @@
         <v>8</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>2585.1</v>
+        <v>2586.5</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -6959,13 +6959,13 @@
         <v>1</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>390.3</v>
+        <v>390.6</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -6994,13 +6994,13 @@
         <v>11</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>4059.9</v>
+        <v>4063.6</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         <v>2</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>781.3</v>
+        <v>782.1</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>621</v>
@@ -7064,13 +7064,13 @@
         <v>17</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>5095.5</v>
+        <v>5103.5</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -7099,13 +7099,13 @@
         <v>4</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1387.3</v>
+        <v>1389.1</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -7134,13 +7134,13 @@
         <v>8</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>2834.3</v>
+        <v>2838.5</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H99" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -7169,13 +7169,13 @@
         <v>7</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>2081.4</v>
+        <v>2084.7</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -7204,10 +7204,10 @@
         <v>12</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>3978</v>
+        <v>3979.8</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H101" s="12" t="n">
         <v>2061</v>
@@ -7239,13 +7239,13 @@
         <v>8</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>3025.4</v>
+        <v>3025.8</v>
       </c>
       <c r="G102" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -7274,13 +7274,13 @@
         <v>7</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>2069.5</v>
+        <v>2069.7</v>
       </c>
       <c r="G103" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -7309,13 +7309,13 @@
         <v>11</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>3526.2</v>
+        <v>3527.1</v>
       </c>
       <c r="G104" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -7344,13 +7344,13 @@
         <v>15</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>5900</v>
+        <v>5903.6</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -7379,13 +7379,13 @@
         <v>15</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>5810.3</v>
+        <v>5813.3</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -7414,13 +7414,13 @@
         <v>49</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>16406.2</v>
+        <v>16416.3</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -7449,10 +7449,10 @@
         <v>15</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>5458.7</v>
+        <v>5460.3</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H108" s="12" t="n">
         <v>2061</v>
@@ -7484,13 +7484,13 @@
         <v>8</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>2950.2</v>
+        <v>2953.5</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -7519,13 +7519,13 @@
         <v>7</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>2510.9</v>
+        <v>2513.1</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -7554,13 +7554,13 @@
         <v>14</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>5528.7</v>
+        <v>5532</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -7589,13 +7589,13 @@
         <v>10</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3065.6</v>
+        <v>3069.2</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -7624,13 +7624,13 @@
         <v>15</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>3390.3</v>
+        <v>3393</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         <v>4</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>964.2</v>
+        <v>964.5</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H114" s="12" t="n">
         <v>621</v>
@@ -7694,13 +7694,13 @@
         <v>4</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>949.3</v>
+        <v>950.4</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -7729,13 +7729,13 @@
         <v>34</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>9001.1</v>
+        <v>9006.299999999999</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -7764,13 +7764,13 @@
         <v>17</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>3889.8</v>
+        <v>3893.5</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -7799,13 +7799,13 @@
         <v>31</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>8564.799999999999</v>
+        <v>8570.6</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         <v>6</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1401.9</v>
+        <v>1402.3</v>
       </c>
       <c r="G119" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -7869,13 +7869,13 @@
         <v>23</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>6473.5</v>
+        <v>6477.1</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -7904,10 +7904,10 @@
         <v>13</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>3353.9</v>
+        <v>3354.3</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H121" s="12" t="n">
         <v>2061</v>
@@ -7939,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>7368.7</v>
+        <v>7374.3</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -7974,13 +7974,13 @@
         <v>15</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>3674.4</v>
+        <v>3680.2</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -8009,13 +8009,13 @@
         <v>3</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>769.3</v>
+        <v>770.7</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -8044,13 +8044,13 @@
         <v>16</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>3877.3</v>
+        <v>3880.1</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -8079,13 +8079,13 @@
         <v>9</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>2531.2</v>
+        <v>2533.7</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -8114,13 +8114,13 @@
         <v>14</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>3272.2</v>
+        <v>3273.1</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -8149,13 +8149,13 @@
         <v>17</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>4744.2</v>
+        <v>4749.6</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>26</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>7191.4</v>
+        <v>7197.2</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -8219,13 +8219,13 @@
         <v>4</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>1085.7</v>
+        <v>1086.9</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -8254,13 +8254,13 @@
         <v>21</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>3991.6</v>
+        <v>3993.5</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -8289,13 +8289,13 @@
         <v>85</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>18848.2</v>
+        <v>18860.4</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -8324,10 +8324,10 @@
         <v>10</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>2010.3</v>
+        <v>2010.9</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H133" s="12" t="n">
         <v>860</v>
@@ -8359,13 +8359,13 @@
         <v>42</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>8242.5</v>
+        <v>8247.4</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -8394,13 +8394,13 @@
         <v>22</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>4550.7</v>
+        <v>4554.7</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H135" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -8429,13 +8429,13 @@
         <v>6</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1122.5</v>
+        <v>1122.6</v>
       </c>
       <c r="G136" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -8464,13 +8464,13 @@
         <v>11</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>2148.7</v>
+        <v>2150.2</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H137" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -8499,13 +8499,13 @@
         <v>17</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>3425.9</v>
+        <v>3431.4</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -8534,13 +8534,13 @@
         <v>20</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>4116.9</v>
+        <v>4122.2</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         <v>16</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>3085.2</v>
+        <v>3086.9</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H140" s="12" t="n">
         <v>693</v>
@@ -8601,16 +8601,16 @@
         <v>99.5</v>
       </c>
       <c r="E141" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>6650.3</v>
+        <v>6658.1</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H141" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -8639,13 +8639,13 @@
         <v>68</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>14643</v>
+        <v>14656.1</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         <v>13</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>2569.6</v>
+        <v>2570.8</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H143" s="12" t="n">
         <v>860</v>
@@ -8709,13 +8709,13 @@
         <v>23</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>4972.2</v>
+        <v>4977.6</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -8744,13 +8744,13 @@
         <v>22</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>4766</v>
+        <v>4768.7</v>
       </c>
       <c r="G145" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -8779,10 +8779,10 @@
         <v>14</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>2570.9</v>
+        <v>2571.2</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H146" s="12" t="n">
         <v>621</v>
@@ -8846,16 +8846,16 @@
         <v>99.5</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>2442</v>
+        <v>2446.8</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -8884,13 +8884,13 @@
         <v>19</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>3598</v>
+        <v>3604.6</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H149" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -8919,13 +8919,13 @@
         <v>11</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>2252.7</v>
+        <v>2253.8</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -8954,13 +8954,13 @@
         <v>38</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>8294.4</v>
+        <v>8302.1</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="H151" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -8989,13 +8989,13 @@
         <v>28</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>4500.4</v>
+        <v>4506.7</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -9024,13 +9024,13 @@
         <v>46</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>8145.2</v>
+        <v>8153.5</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H153" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -9059,13 +9059,13 @@
         <v>11</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>1812.7</v>
+        <v>1814.3</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -9094,10 +9094,10 @@
         <v>9</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>1424</v>
+        <v>1424.6</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H155" s="12" t="n">
         <v>860</v>
@@ -9129,13 +9129,13 @@
         <v>13</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>2212.5</v>
+        <v>2215</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -9164,13 +9164,13 @@
         <v>23</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>3769.9</v>
+        <v>3774.8</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H157" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -9199,13 +9199,13 @@
         <v>22</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>3917.3</v>
+        <v>3922.7</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -9234,13 +9234,13 @@
         <v>29</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>5185.9</v>
+        <v>5190</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H159" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -9269,13 +9269,13 @@
         <v>16</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2875.5</v>
+        <v>2879.5</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -9304,13 +9304,13 @@
         <v>12</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>2149.9</v>
+        <v>2152.7</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H161" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -9339,13 +9339,13 @@
         <v>38</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>5854.1</v>
+        <v>5858.6</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -9374,10 +9374,10 @@
         <v>18</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>2822.7</v>
+        <v>2823.4</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H163" s="12" t="n">
         <v>621</v>
@@ -9409,13 +9409,13 @@
         <v>9</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>1414.1</v>
+        <v>1415</v>
       </c>
       <c r="G164" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -9444,13 +9444,13 @@
         <v>10</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>1654.3</v>
+        <v>1655.2</v>
       </c>
       <c r="G165" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H165" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -9479,13 +9479,13 @@
         <v>65</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>10052.9</v>
+        <v>10060.7</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -9514,13 +9514,13 @@
         <v>23</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>3987.6</v>
+        <v>3993.1</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H167" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -9549,10 +9549,10 @@
         <v>12</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>2008.8</v>
+        <v>2009.4</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H168" s="12" t="n">
         <v>2061</v>
@@ -9584,13 +9584,13 @@
         <v>44</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>7025</v>
+        <v>7032.9</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H169" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -9619,10 +9619,10 @@
         <v>8</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>1134.6</v>
+        <v>1135</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H170" s="12" t="n">
         <v>860</v>
@@ -9654,13 +9654,13 @@
         <v>30</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>4382.5</v>
+        <v>4385.2</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H171" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -9689,13 +9689,13 @@
         <v>22</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3234.8</v>
+        <v>3237.5</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I172" s="13" t="inlineStr">
         <is>
@@ -9724,13 +9724,13 @@
         <v>69</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>9839.6</v>
+        <v>9846.6</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H173" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -9759,13 +9759,13 @@
         <v>57</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>8033.7</v>
+        <v>8040.7</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -9794,13 +9794,13 @@
         <v>60</v>
       </c>
       <c r="F175" s="12" t="n">
-        <v>8658.299999999999</v>
+        <v>8663.799999999999</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H175" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -9829,10 +9829,10 @@
         <v>17</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2584.7</v>
+        <v>2585.3</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H176" s="12" t="n">
         <v>860</v>
@@ -9864,13 +9864,13 @@
         <v>30</v>
       </c>
       <c r="F177" s="12" t="n">
-        <v>4255</v>
+        <v>4258.7</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H177" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -9899,13 +9899,13 @@
         <v>20</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>2755.5</v>
+        <v>2758.4</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I178" s="13" t="inlineStr">
         <is>
@@ -9934,13 +9934,13 @@
         <v>81</v>
       </c>
       <c r="F179" s="12" t="n">
-        <v>11505.8</v>
+        <v>11514.1</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H179" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -9969,13 +9969,13 @@
         <v>23</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>3204.4</v>
+        <v>3206.3</v>
       </c>
       <c r="G180" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I180" s="13" t="inlineStr">
         <is>
@@ -10004,13 +10004,13 @@
         <v>14</v>
       </c>
       <c r="F181" s="12" t="n">
-        <v>1946.8</v>
+        <v>1947.9</v>
       </c>
       <c r="G181" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H181" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         <v>24</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>3289.1</v>
+        <v>3290.3</v>
       </c>
       <c r="G182" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
@@ -10074,13 +10074,13 @@
         <v>67</v>
       </c>
       <c r="F183" s="12" t="n">
-        <v>9470</v>
+        <v>9477.4</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H183" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -10109,13 +10109,13 @@
         <v>20</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>2996.4</v>
+        <v>2997.2</v>
       </c>
       <c r="G184" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -10144,13 +10144,13 @@
         <v>58</v>
       </c>
       <c r="F185" s="12" t="n">
-        <v>8717</v>
+        <v>8724.200000000001</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H185" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -10179,13 +10179,13 @@
         <v>26</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>3767</v>
+        <v>3771.5</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -10214,10 +10214,10 @@
         <v>54</v>
       </c>
       <c r="F187" s="12" t="n">
-        <v>7378.2</v>
+        <v>7382.2</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H187" s="12" t="n">
         <v>2061</v>
@@ -10249,13 +10249,13 @@
         <v>14</v>
       </c>
       <c r="F188" s="12" t="n">
-        <v>1665.1</v>
+        <v>1667.9</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H188" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -10281,16 +10281,16 @@
         <v>99.2</v>
       </c>
       <c r="E189" s="12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F189" s="12" t="n">
-        <v>15684.8</v>
+        <v>15700</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H189" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -10319,10 +10319,10 @@
         <v>14</v>
       </c>
       <c r="F190" s="12" t="n">
-        <v>1708.2</v>
+        <v>1708.8</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H190" s="12" t="n">
         <v>621</v>
@@ -10354,13 +10354,13 @@
         <v>90</v>
       </c>
       <c r="F191" s="12" t="n">
-        <v>11140.7</v>
+        <v>11150.3</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H191" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
@@ -10389,13 +10389,13 @@
         <v>27</v>
       </c>
       <c r="F192" s="12" t="n">
-        <v>3223.6</v>
+        <v>3226.8</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H192" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I192" s="13" t="inlineStr">
         <is>
@@ -10424,13 +10424,13 @@
         <v>50</v>
       </c>
       <c r="F193" s="12" t="n">
-        <v>6183.6</v>
+        <v>6187</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H193" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -10459,13 +10459,13 @@
         <v>80</v>
       </c>
       <c r="F194" s="12" t="n">
-        <v>9574.700000000001</v>
+        <v>9584.700000000001</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H194" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I194" s="13" t="inlineStr">
         <is>
@@ -10494,13 +10494,13 @@
         <v>67</v>
       </c>
       <c r="F195" s="12" t="n">
-        <v>8625.200000000001</v>
+        <v>8630.799999999999</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H195" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I195" s="13" t="inlineStr">
         <is>
@@ -10529,13 +10529,13 @@
         <v>14</v>
       </c>
       <c r="F196" s="12" t="n">
-        <v>1857.7</v>
+        <v>1857.9</v>
       </c>
       <c r="G196" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H196" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I196" s="13" t="inlineStr">
         <is>
@@ -10564,13 +10564,13 @@
         <v>20</v>
       </c>
       <c r="F197" s="12" t="n">
-        <v>2379.7</v>
+        <v>2380.9</v>
       </c>
       <c r="G197" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H197" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I197" s="13" t="inlineStr">
         <is>
@@ -10599,13 +10599,13 @@
         <v>33</v>
       </c>
       <c r="F198" s="12" t="n">
-        <v>4004.4</v>
+        <v>4007.3</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H198" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I198" s="13" t="inlineStr">
         <is>
@@ -10634,13 +10634,13 @@
         <v>57</v>
       </c>
       <c r="F199" s="12" t="n">
-        <v>7253.9</v>
+        <v>7262.3</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H199" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I199" s="13" t="inlineStr">
         <is>
@@ -10669,13 +10669,13 @@
         <v>31</v>
       </c>
       <c r="F200" s="12" t="n">
-        <v>4050</v>
+        <v>4052.2</v>
       </c>
       <c r="G200" s="12" t="n">
         <v>621</v>
       </c>
       <c r="H200" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I200" s="13" t="inlineStr">
         <is>
@@ -10704,13 +10704,13 @@
         <v>87</v>
       </c>
       <c r="F201" s="12" t="n">
-        <v>10978.2</v>
+        <v>10986.6</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H201" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I201" s="13" t="inlineStr">
         <is>
@@ -10739,10 +10739,10 @@
         <v>45</v>
       </c>
       <c r="F202" s="12" t="n">
-        <v>5961.2</v>
+        <v>5962.7</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>2061</v>
@@ -10774,13 +10774,13 @@
         <v>42</v>
       </c>
       <c r="F203" s="12" t="n">
-        <v>5129.7</v>
+        <v>5135.4</v>
       </c>
       <c r="G203" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H203" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I203" s="13" t="inlineStr">
         <is>
@@ -10809,13 +10809,13 @@
         <v>32</v>
       </c>
       <c r="F204" s="12" t="n">
-        <v>4000.1</v>
+        <v>4003.1</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H204" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I204" s="13" t="inlineStr">
         <is>
@@ -10844,13 +10844,13 @@
         <v>27</v>
       </c>
       <c r="F205" s="12" t="n">
-        <v>2858.4</v>
+        <v>2859.6</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H205" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="I205" s="13" t="inlineStr">
         <is>
@@ -10879,13 +10879,13 @@
         <v>12</v>
       </c>
       <c r="F206" s="12" t="n">
-        <v>1329.8</v>
+        <v>1330.5</v>
       </c>
       <c r="G206" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H206" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I206" s="13" t="inlineStr">
         <is>
@@ -10914,13 +10914,13 @@
         <v>39</v>
       </c>
       <c r="F207" s="12" t="n">
-        <v>4554.1</v>
+        <v>4555.5</v>
       </c>
       <c r="G207" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H207" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I207" s="13" t="inlineStr">
         <is>
@@ -10949,10 +10949,10 @@
         <v>48</v>
       </c>
       <c r="F208" s="12" t="n">
-        <v>5320.5</v>
+        <v>5323.4</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>2061</v>
@@ -10984,13 +10984,13 @@
         <v>31</v>
       </c>
       <c r="F209" s="12" t="n">
-        <v>3321.7</v>
+        <v>3322.6</v>
       </c>
       <c r="G209" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H209" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I209" s="13" t="inlineStr">
         <is>
@@ -11019,13 +11019,13 @@
         <v>33</v>
       </c>
       <c r="F210" s="12" t="n">
-        <v>3664.1</v>
+        <v>3665.4</v>
       </c>
       <c r="G210" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H210" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I210" s="13" t="inlineStr">
         <is>
@@ -11054,13 +11054,13 @@
         <v>18</v>
       </c>
       <c r="F211" s="12" t="n">
-        <v>2051.3</v>
+        <v>2054.1</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H211" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I211" s="13" t="inlineStr">
         <is>
@@ -11089,13 +11089,13 @@
         <v>51</v>
       </c>
       <c r="F212" s="12" t="n">
-        <v>5550.2</v>
+        <v>5556.1</v>
       </c>
       <c r="G212" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H212" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I212" s="13" t="inlineStr">
         <is>
@@ -11124,13 +11124,13 @@
         <v>36</v>
       </c>
       <c r="F213" s="12" t="n">
-        <v>3497.6</v>
+        <v>3500.5</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H213" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I213" s="13" t="inlineStr">
         <is>
@@ -11159,13 +11159,13 @@
         <v>72</v>
       </c>
       <c r="F214" s="12" t="n">
-        <v>7490.4</v>
+        <v>7497.2</v>
       </c>
       <c r="G214" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H214" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I214" s="13" t="inlineStr">
         <is>
@@ -11194,13 +11194,13 @@
         <v>8</v>
       </c>
       <c r="F215" s="12" t="n">
-        <v>772.4</v>
+        <v>772.7</v>
       </c>
       <c r="G215" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H215" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I215" s="13" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         <v>51</v>
       </c>
       <c r="F216" s="12" t="n">
-        <v>5009.6</v>
+        <v>5012.4</v>
       </c>
       <c r="G216" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H216" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I216" s="13" t="inlineStr">
         <is>
@@ -11264,13 +11264,13 @@
         <v>51</v>
       </c>
       <c r="F217" s="12" t="n">
-        <v>5306.1</v>
+        <v>5311.4</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H217" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I217" s="13" t="inlineStr">
         <is>
@@ -11299,13 +11299,13 @@
         <v>43</v>
       </c>
       <c r="F218" s="12" t="n">
-        <v>4389.7</v>
+        <v>4393.7</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H218" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I218" s="13" t="inlineStr">
         <is>
@@ -11334,10 +11334,10 @@
         <v>34</v>
       </c>
       <c r="F219" s="12" t="n">
-        <v>3436.9</v>
+        <v>3438.7</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H219" s="12" t="n">
         <v>860</v>
@@ -11369,13 +11369,13 @@
         <v>88</v>
       </c>
       <c r="F220" s="12" t="n">
-        <v>9039.700000000001</v>
+        <v>9045.1</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H220" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I220" s="13" t="inlineStr">
         <is>
@@ -11404,13 +11404,13 @@
         <v>138</v>
       </c>
       <c r="F221" s="12" t="n">
-        <v>13546.5</v>
+        <v>13551.9</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H221" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I221" s="13" t="inlineStr">
         <is>
@@ -11439,13 +11439,13 @@
         <v>42</v>
       </c>
       <c r="F222" s="12" t="n">
-        <v>4278.3</v>
+        <v>4280.7</v>
       </c>
       <c r="G222" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H222" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I222" s="13" t="inlineStr">
         <is>
@@ -11474,13 +11474,13 @@
         <v>17</v>
       </c>
       <c r="F223" s="12" t="n">
-        <v>1747.6</v>
+        <v>1748.6</v>
       </c>
       <c r="G223" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H223" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I223" s="13" t="inlineStr">
         <is>
@@ -11509,13 +11509,13 @@
         <v>29</v>
       </c>
       <c r="F224" s="12" t="n">
-        <v>2856.9</v>
+        <v>2862.4</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H224" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I224" s="13" t="inlineStr">
         <is>
@@ -11544,10 +11544,10 @@
         <v>40</v>
       </c>
       <c r="F225" s="12" t="n">
-        <v>3577</v>
+        <v>3578.4</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H225" s="12" t="n">
         <v>621</v>
@@ -11579,13 +11579,13 @@
         <v>8</v>
       </c>
       <c r="F226" s="12" t="n">
-        <v>703.8</v>
+        <v>704</v>
       </c>
       <c r="G226" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H226" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I226" s="13" t="inlineStr">
         <is>
@@ -11614,13 +11614,13 @@
         <v>25</v>
       </c>
       <c r="F227" s="12" t="n">
-        <v>2316.3</v>
+        <v>2318.9</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H227" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I227" s="13" t="inlineStr">
         <is>
@@ -11649,10 +11649,10 @@
         <v>23</v>
       </c>
       <c r="F228" s="12" t="n">
-        <v>2166.5</v>
+        <v>2166.7</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H228" s="12" t="n">
         <v>860</v>
@@ -11684,13 +11684,13 @@
         <v>45</v>
       </c>
       <c r="F229" s="12" t="n">
-        <v>4192.2</v>
+        <v>4195.2</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H229" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I229" s="13" t="inlineStr">
         <is>
@@ -11719,10 +11719,10 @@
         <v>24</v>
       </c>
       <c r="F230" s="12" t="n">
-        <v>2196.3</v>
+        <v>2196.9</v>
       </c>
       <c r="G230" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H230" s="12" t="n">
         <v>621</v>
@@ -11751,16 +11751,16 @@
         <v>98.90000000000001</v>
       </c>
       <c r="E231" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F231" s="12" t="n">
-        <v>5043.5</v>
+        <v>5053.1</v>
       </c>
       <c r="G231" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H231" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I231" s="13" t="inlineStr">
         <is>
@@ -11789,13 +11789,13 @@
         <v>77</v>
       </c>
       <c r="F232" s="12" t="n">
-        <v>7325.9</v>
+        <v>7332.9</v>
       </c>
       <c r="G232" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H232" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I232" s="13" t="inlineStr">
         <is>
@@ -11824,13 +11824,13 @@
         <v>68</v>
       </c>
       <c r="F233" s="12" t="n">
-        <v>6200.5</v>
+        <v>6208</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H233" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I233" s="13" t="inlineStr">
         <is>
@@ -11859,13 +11859,13 @@
         <v>32</v>
       </c>
       <c r="F234" s="12" t="n">
-        <v>2568.5</v>
+        <v>2570.8</v>
       </c>
       <c r="G234" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H234" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I234" s="13" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>37</v>
       </c>
       <c r="F235" s="12" t="n">
-        <v>3033.3</v>
+        <v>3035</v>
       </c>
       <c r="G235" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H235" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I235" s="13" t="inlineStr">
         <is>
@@ -11929,13 +11929,13 @@
         <v>70</v>
       </c>
       <c r="F236" s="12" t="n">
-        <v>5691</v>
+        <v>5696.5</v>
       </c>
       <c r="G236" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H236" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I236" s="13" t="inlineStr">
         <is>
@@ -11964,13 +11964,13 @@
         <v>71</v>
       </c>
       <c r="F237" s="12" t="n">
-        <v>5838.8</v>
+        <v>5842.9</v>
       </c>
       <c r="G237" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H237" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I237" s="13" t="inlineStr">
         <is>
@@ -11999,13 +11999,13 @@
         <v>92</v>
       </c>
       <c r="F238" s="12" t="n">
-        <v>7891.9</v>
+        <v>7899.6</v>
       </c>
       <c r="G238" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H238" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I238" s="13" t="inlineStr">
         <is>
@@ -12034,13 +12034,13 @@
         <v>45</v>
       </c>
       <c r="F239" s="12" t="n">
-        <v>3770.9</v>
+        <v>3777.7</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H239" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I239" s="13" t="inlineStr">
         <is>
@@ -12069,13 +12069,13 @@
         <v>80</v>
       </c>
       <c r="F240" s="12" t="n">
-        <v>6427.5</v>
+        <v>6433.2</v>
       </c>
       <c r="G240" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H240" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I240" s="13" t="inlineStr">
         <is>
@@ -12104,13 +12104,13 @@
         <v>87</v>
       </c>
       <c r="F241" s="12" t="n">
-        <v>6994.1</v>
+        <v>7007.3</v>
       </c>
       <c r="G241" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H241" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I241" s="13" t="inlineStr">
         <is>
@@ -12124,28 +12124,28 @@
       </c>
       <c r="B242" s="12" t="inlineStr">
         <is>
+          <t>Beta Cell Regen</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
           <t>Insulin Resistance</t>
-        </is>
-      </c>
-      <c r="C242" s="12" t="inlineStr">
-        <is>
-          <t>Glucokinase</t>
         </is>
       </c>
       <c r="D242" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E242" s="12" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F242" s="12" t="n">
-        <v>4209.4</v>
+        <v>5557.8</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>20604</v>
+        <v>1498</v>
       </c>
       <c r="H242" s="12" t="n">
-        <v>860</v>
+        <v>20620</v>
       </c>
       <c r="I242" s="13" t="inlineStr">
         <is>
@@ -12164,23 +12164,23 @@
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Glucokinase</t>
         </is>
       </c>
       <c r="D243" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E243" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F243" s="12" t="n">
-        <v>3778.7</v>
+        <v>4211.1</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H243" s="12" t="n">
-        <v>693</v>
+        <v>860</v>
       </c>
       <c r="I243" s="13" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="B244" s="12" t="inlineStr">
         <is>
-          <t>GWAS / Polygenic</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C244" s="12" t="inlineStr">
@@ -12206,13 +12206,13 @@
         <v>98.7</v>
       </c>
       <c r="E244" s="12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F244" s="12" t="n">
-        <v>1944.8</v>
+        <v>3780.2</v>
       </c>
       <c r="G244" s="12" t="n">
-        <v>5458</v>
+        <v>20620</v>
       </c>
       <c r="H244" s="12" t="n">
         <v>693</v>
@@ -12229,28 +12229,28 @@
       </c>
       <c r="B245" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>GWAS / Polygenic</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="D245" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E245" s="12" t="n">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="F245" s="12" t="n">
-        <v>10329.3</v>
+        <v>1945</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>7768</v>
+        <v>5459</v>
       </c>
       <c r="H245" s="12" t="n">
-        <v>13735</v>
+        <v>693</v>
       </c>
       <c r="I245" s="13" t="inlineStr">
         <is>
@@ -12264,28 +12264,28 @@
       </c>
       <c r="B246" s="12" t="inlineStr">
         <is>
+          <t>Epigenetics</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
           <t>GLP-1 Agonists</t>
-        </is>
-      </c>
-      <c r="C246" s="12" t="inlineStr">
-        <is>
-          <t>Proteomics</t>
         </is>
       </c>
       <c r="D246" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E246" s="12" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="F246" s="12" t="n">
-        <v>8270.4</v>
+        <v>10337.6</v>
       </c>
       <c r="G246" s="12" t="n">
-        <v>13735</v>
+        <v>7772</v>
       </c>
       <c r="H246" s="12" t="n">
-        <v>4980</v>
+        <v>13750</v>
       </c>
       <c r="I246" s="13" t="inlineStr">
         <is>
@@ -12304,23 +12304,23 @@
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="D247" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E247" s="12" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="F247" s="12" t="n">
-        <v>12806.1</v>
+        <v>8275.799999999999</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H247" s="12" t="n">
-        <v>11940</v>
+        <v>4981</v>
       </c>
       <c r="I247" s="13" t="inlineStr">
         <is>
@@ -12334,28 +12334,28 @@
       </c>
       <c r="B248" s="12" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C248" s="12" t="inlineStr">
         <is>
-          <t>Gestational DM</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D248" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E248" s="12" t="n">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="F248" s="12" t="n">
-        <v>8817.200000000001</v>
+        <v>12820.6</v>
       </c>
       <c r="G248" s="12" t="n">
-        <v>4980</v>
+        <v>13750</v>
       </c>
       <c r="H248" s="12" t="n">
-        <v>15611</v>
+        <v>11954</v>
       </c>
       <c r="I248" s="13" t="inlineStr">
         <is>
@@ -12369,28 +12369,28 @@
       </c>
       <c r="B249" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Retinopathy</t>
+          <t>Gestational DM</t>
         </is>
       </c>
       <c r="D249" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E249" s="12" t="n">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="F249" s="12" t="n">
-        <v>5650.9</v>
+        <v>8821.200000000001</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>1852</v>
+        <v>4981</v>
       </c>
       <c r="H249" s="12" t="n">
-        <v>17242</v>
+        <v>15622</v>
       </c>
       <c r="I249" s="13" t="inlineStr">
         <is>
@@ -12409,23 +12409,23 @@
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>Gestational DM</t>
+          <t>Retinopathy</t>
         </is>
       </c>
       <c r="D250" s="12" t="n">
         <v>98.7</v>
       </c>
       <c r="E250" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F250" s="12" t="n">
-        <v>5376.9</v>
+        <v>5660</v>
       </c>
       <c r="G250" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H250" s="12" t="n">
-        <v>15611</v>
+        <v>17251</v>
       </c>
       <c r="I250" s="13" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="B251" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
@@ -12451,16 +12451,16 @@
         <v>98.7</v>
       </c>
       <c r="E251" s="12" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F251" s="12" t="n">
-        <v>5672.2</v>
+        <v>5386.1</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>2061</v>
+        <v>1857</v>
       </c>
       <c r="H251" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I251" s="13" t="inlineStr">
         <is>
@@ -12474,28 +12474,28 @@
       </c>
       <c r="B252" s="12" t="inlineStr">
         <is>
-          <t>Beta Cell Regen</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="C252" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Gestational DM</t>
         </is>
       </c>
       <c r="D252" s="12" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="E252" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F252" s="12" t="n">
-        <v>5553.8</v>
+        <v>5674.2</v>
       </c>
       <c r="G252" s="12" t="n">
-        <v>1497</v>
+        <v>2061</v>
       </c>
       <c r="H252" s="12" t="n">
-        <v>20604</v>
+        <v>15622</v>
       </c>
       <c r="I252" s="13" t="inlineStr">
         <is>
@@ -12524,13 +12524,13 @@
         <v>7</v>
       </c>
       <c r="F253" s="12" t="n">
-        <v>498.7</v>
+        <v>499.2</v>
       </c>
       <c r="G253" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H253" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I253" s="13" t="inlineStr">
         <is>
@@ -12556,16 +12556,16 @@
         <v>98.59999999999999</v>
       </c>
       <c r="E254" s="12" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F254" s="12" t="n">
-        <v>15388.9</v>
+        <v>15401.3</v>
       </c>
       <c r="G254" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H254" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
@@ -12594,13 +12594,13 @@
         <v>116</v>
       </c>
       <c r="F255" s="12" t="n">
-        <v>8396.4</v>
+        <v>8399</v>
       </c>
       <c r="G255" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H255" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I255" s="13" t="inlineStr">
         <is>
@@ -12629,10 +12629,10 @@
         <v>25</v>
       </c>
       <c r="F256" s="12" t="n">
-        <v>1758.6</v>
+        <v>1758.7</v>
       </c>
       <c r="G256" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H256" s="12" t="n">
         <v>621</v>
@@ -12664,13 +12664,13 @@
         <v>56</v>
       </c>
       <c r="F257" s="12" t="n">
-        <v>3890.3</v>
+        <v>3897.5</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H257" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I257" s="13" t="inlineStr">
         <is>
@@ -12699,13 +12699,13 @@
         <v>168</v>
       </c>
       <c r="F258" s="12" t="n">
-        <v>11870.2</v>
+        <v>11879.1</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H258" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I258" s="13" t="inlineStr">
         <is>
@@ -12734,13 +12734,13 @@
         <v>30</v>
       </c>
       <c r="F259" s="12" t="n">
-        <v>2218</v>
+        <v>2220.9</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="H259" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I259" s="13" t="inlineStr">
         <is>
@@ -12769,13 +12769,13 @@
         <v>104</v>
       </c>
       <c r="F260" s="12" t="n">
-        <v>6970.2</v>
+        <v>6975.9</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H260" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I260" s="13" t="inlineStr">
         <is>
@@ -12804,13 +12804,13 @@
         <v>55</v>
       </c>
       <c r="F261" s="12" t="n">
-        <v>3551.3</v>
+        <v>3555.9</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H261" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
@@ -12839,13 +12839,13 @@
         <v>96</v>
       </c>
       <c r="F262" s="12" t="n">
-        <v>6379.4</v>
+        <v>6383.1</v>
       </c>
       <c r="G262" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H262" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I262" s="13" t="inlineStr">
         <is>
@@ -12874,13 +12874,13 @@
         <v>27</v>
       </c>
       <c r="F263" s="12" t="n">
-        <v>1712.1</v>
+        <v>1713.1</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H263" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I263" s="13" t="inlineStr">
         <is>
@@ -12906,16 +12906,16 @@
         <v>98.40000000000001</v>
       </c>
       <c r="E264" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F264" s="12" t="n">
-        <v>5731.1</v>
+        <v>5735.8</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H264" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I264" s="13" t="inlineStr">
         <is>
@@ -12944,13 +12944,13 @@
         <v>127</v>
       </c>
       <c r="F265" s="12" t="n">
-        <v>7722.9</v>
+        <v>7728.4</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H265" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I265" s="13" t="inlineStr">
         <is>
@@ -12979,13 +12979,13 @@
         <v>79</v>
       </c>
       <c r="F266" s="12" t="n">
-        <v>5001.3</v>
+        <v>5005.7</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H266" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I266" s="13" t="inlineStr">
         <is>
@@ -13014,10 +13014,10 @@
         <v>79</v>
       </c>
       <c r="F267" s="12" t="n">
-        <v>4960.7</v>
+        <v>4963.6</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H267" s="12" t="n">
         <v>2061</v>
@@ -13049,13 +13049,13 @@
         <v>78</v>
       </c>
       <c r="F268" s="12" t="n">
-        <v>4534.5</v>
+        <v>4538.4</v>
       </c>
       <c r="G268" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H268" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I268" s="13" t="inlineStr">
         <is>
@@ -13084,13 +13084,13 @@
         <v>47</v>
       </c>
       <c r="F269" s="12" t="n">
-        <v>2730.4</v>
+        <v>2731.6</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H269" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I269" s="13" t="inlineStr">
         <is>
@@ -13119,13 +13119,13 @@
         <v>294</v>
       </c>
       <c r="F270" s="12" t="n">
-        <v>17259.6</v>
+        <v>17271</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H270" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
@@ -13154,13 +13154,13 @@
         <v>49</v>
       </c>
       <c r="F271" s="12" t="n">
-        <v>2950</v>
+        <v>2954.9</v>
       </c>
       <c r="G271" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H271" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I271" s="13" t="inlineStr">
         <is>
@@ -13174,28 +13174,28 @@
       </c>
       <c r="B272" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C272" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D272" s="12" t="n">
         <v>98.3</v>
       </c>
       <c r="E272" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F272" s="12" t="n">
-        <v>1349.3</v>
+        <v>2184.6</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>983</v>
+        <v>7685</v>
       </c>
       <c r="H272" s="12" t="n">
-        <v>1852</v>
+        <v>621</v>
       </c>
       <c r="I272" s="13" t="inlineStr">
         <is>
@@ -13209,28 +13209,28 @@
       </c>
       <c r="B273" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D273" s="12" t="n">
         <v>98.3</v>
       </c>
       <c r="E273" s="12" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="F273" s="12" t="n">
-        <v>2183.6</v>
+        <v>4687.9</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>7678</v>
+        <v>4981</v>
       </c>
       <c r="H273" s="12" t="n">
-        <v>621</v>
+        <v>4412</v>
       </c>
       <c r="I273" s="13" t="inlineStr">
         <is>
@@ -13244,28 +13244,28 @@
       </c>
       <c r="B274" s="12" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="C274" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>Youth Diabetes</t>
         </is>
       </c>
       <c r="D274" s="12" t="n">
         <v>98.3</v>
       </c>
       <c r="E274" s="12" t="n">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="F274" s="12" t="n">
-        <v>4684.7</v>
+        <v>9888.6</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>4980</v>
+        <v>11954</v>
       </c>
       <c r="H274" s="12" t="n">
-        <v>4407</v>
+        <v>8180</v>
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
@@ -13279,28 +13279,28 @@
       </c>
       <c r="B275" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Youth Diabetes</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D275" s="12" t="n">
         <v>98.3</v>
       </c>
       <c r="E275" s="12" t="n">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="F275" s="12" t="n">
-        <v>9877.9</v>
+        <v>7989</v>
       </c>
       <c r="G275" s="12" t="n">
-        <v>11940</v>
+        <v>14466</v>
       </c>
       <c r="H275" s="12" t="n">
-        <v>8172</v>
+        <v>4412</v>
       </c>
       <c r="I275" s="13" t="inlineStr">
         <is>
@@ -13314,28 +13314,28 @@
       </c>
       <c r="B276" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C276" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="D276" s="12" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="E276" s="12" t="n">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="F276" s="12" t="n">
-        <v>7982.3</v>
+        <v>12588.3</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>14458</v>
+        <v>20620</v>
       </c>
       <c r="H276" s="12" t="n">
-        <v>4407</v>
+        <v>7685</v>
       </c>
       <c r="I276" s="13" t="inlineStr">
         <is>
@@ -13349,28 +13349,28 @@
       </c>
       <c r="B277" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Gene Therapy</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Metabolomics</t>
         </is>
       </c>
       <c r="D277" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E277" s="12" t="n">
-        <v>221</v>
+        <v>98</v>
       </c>
       <c r="F277" s="12" t="n">
-        <v>12577.7</v>
+        <v>5504.1</v>
       </c>
       <c r="G277" s="12" t="n">
-        <v>20604</v>
+        <v>2360</v>
       </c>
       <c r="H277" s="12" t="n">
-        <v>7678</v>
+        <v>12837</v>
       </c>
       <c r="I277" s="13" t="inlineStr">
         <is>
@@ -13384,28 +13384,28 @@
       </c>
       <c r="B278" s="12" t="inlineStr">
         <is>
-          <t>Gene Therapy</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="C278" s="12" t="inlineStr">
         <is>
-          <t>Metabolomics</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D278" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E278" s="12" t="n">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="F278" s="12" t="n">
-        <v>5500.3</v>
+        <v>1352.5</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>2358</v>
+        <v>985</v>
       </c>
       <c r="H278" s="12" t="n">
-        <v>12830</v>
+        <v>1857</v>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
@@ -13434,13 +13434,13 @@
         <v>48</v>
       </c>
       <c r="F279" s="12" t="n">
-        <v>2651</v>
+        <v>2652.3</v>
       </c>
       <c r="G279" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
@@ -13469,10 +13469,10 @@
         <v>50</v>
       </c>
       <c r="F280" s="12" t="n">
-        <v>2723</v>
+        <v>2724.6</v>
       </c>
       <c r="G280" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H280" s="12" t="n">
         <v>621</v>
@@ -13489,28 +13489,28 @@
       </c>
       <c r="B281" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D281" s="12" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="E281" s="12" t="n">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="F281" s="12" t="n">
-        <v>2763.3</v>
+        <v>7137.1</v>
       </c>
       <c r="G281" s="12" t="n">
-        <v>7768</v>
+        <v>621</v>
       </c>
       <c r="H281" s="12" t="n">
-        <v>983</v>
+        <v>82027</v>
       </c>
       <c r="I281" s="13" t="inlineStr">
         <is>
@@ -13529,23 +13529,23 @@
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="D282" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E282" s="12" t="n">
-        <v>184</v>
+        <v>53</v>
       </c>
       <c r="F282" s="12" t="n">
-        <v>9630.700000000001</v>
+        <v>2766.8</v>
       </c>
       <c r="G282" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H282" s="12" t="n">
-        <v>11940</v>
+        <v>985</v>
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
@@ -13559,28 +13559,28 @@
       </c>
       <c r="B283" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D283" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E283" s="12" t="n">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="F283" s="12" t="n">
-        <v>2920.5</v>
+        <v>9638.799999999999</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>13735</v>
+        <v>7772</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>621</v>
+        <v>11954</v>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
@@ -13599,23 +13599,23 @@
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D284" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E284" s="12" t="n">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="F284" s="12" t="n">
-        <v>9798.299999999999</v>
+        <v>2922.1</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H284" s="12" t="n">
-        <v>6990</v>
+        <v>621</v>
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
@@ -13629,12 +13629,12 @@
       </c>
       <c r="B285" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Metabolomics</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D285" s="12" t="n">
@@ -13644,13 +13644,13 @@
         <v>184</v>
       </c>
       <c r="F285" s="12" t="n">
-        <v>9925.200000000001</v>
+        <v>9808.6</v>
       </c>
       <c r="G285" s="12" t="n">
-        <v>7678</v>
+        <v>13750</v>
       </c>
       <c r="H285" s="12" t="n">
-        <v>12830</v>
+        <v>6997</v>
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
@@ -13664,28 +13664,28 @@
       </c>
       <c r="B286" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>Prevention / DPP</t>
+          <t>Metabolomics</t>
         </is>
       </c>
       <c r="D286" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E286" s="12" t="n">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="F286" s="12" t="n">
-        <v>7135</v>
+        <v>9932.4</v>
       </c>
       <c r="G286" s="12" t="n">
-        <v>621</v>
+        <v>7685</v>
       </c>
       <c r="H286" s="12" t="n">
-        <v>81977</v>
+        <v>12837</v>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
@@ -13714,13 +13714,13 @@
         <v>204</v>
       </c>
       <c r="F287" s="12" t="n">
-        <v>10869.7</v>
+        <v>10878</v>
       </c>
       <c r="G287" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I287" s="13" t="inlineStr">
         <is>
@@ -13749,13 +13749,13 @@
         <v>252</v>
       </c>
       <c r="F288" s="12" t="n">
-        <v>13587.7</v>
+        <v>13602</v>
       </c>
       <c r="G288" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H288" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I288" s="13" t="inlineStr">
         <is>
@@ -13784,13 +13784,13 @@
         <v>79</v>
       </c>
       <c r="F289" s="12" t="n">
-        <v>4104</v>
+        <v>4106</v>
       </c>
       <c r="G289" s="12" t="n">
         <v>2061</v>
       </c>
       <c r="H289" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I289" s="13" t="inlineStr">
         <is>
@@ -13819,13 +13819,13 @@
         <v>68</v>
       </c>
       <c r="F290" s="12" t="n">
-        <v>3410.1</v>
+        <v>3412.1</v>
       </c>
       <c r="G290" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H290" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
@@ -13854,13 +13854,13 @@
         <v>213</v>
       </c>
       <c r="F291" s="12" t="n">
-        <v>10604.6</v>
+        <v>10609.6</v>
       </c>
       <c r="G291" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H291" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="I291" s="13" t="inlineStr">
         <is>
@@ -13889,13 +13889,13 @@
         <v>159</v>
       </c>
       <c r="F292" s="12" t="n">
-        <v>7764.5</v>
+        <v>7769.1</v>
       </c>
       <c r="G292" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H292" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I292" s="13" t="inlineStr">
         <is>
@@ -13924,13 +13924,13 @@
         <v>154</v>
       </c>
       <c r="F293" s="12" t="n">
-        <v>7621.6</v>
+        <v>7623.4</v>
       </c>
       <c r="G293" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H293" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
@@ -13959,13 +13959,13 @@
         <v>190</v>
       </c>
       <c r="F294" s="12" t="n">
-        <v>9700.9</v>
+        <v>9704.299999999999</v>
       </c>
       <c r="G294" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H294" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
@@ -13994,13 +13994,13 @@
         <v>119</v>
       </c>
       <c r="F295" s="12" t="n">
-        <v>5817</v>
+        <v>5822.9</v>
       </c>
       <c r="G295" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H295" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I295" s="13" t="inlineStr">
         <is>
@@ -14029,10 +14029,10 @@
         <v>21</v>
       </c>
       <c r="F296" s="12" t="n">
-        <v>1072.4</v>
+        <v>1073.9</v>
       </c>
       <c r="G296" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H296" s="12" t="n">
         <v>621</v>
@@ -14064,10 +14064,10 @@
         <v>75</v>
       </c>
       <c r="F297" s="12" t="n">
-        <v>3795.6</v>
+        <v>3797.5</v>
       </c>
       <c r="G297" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H297" s="12" t="n">
         <v>2061</v>
@@ -14099,13 +14099,13 @@
         <v>25</v>
       </c>
       <c r="F298" s="12" t="n">
-        <v>1213.1</v>
+        <v>1214.7</v>
       </c>
       <c r="G298" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H298" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I298" s="13" t="inlineStr">
         <is>
@@ -14134,13 +14134,13 @@
         <v>258</v>
       </c>
       <c r="F299" s="12" t="n">
-        <v>12006.8</v>
+        <v>12014.4</v>
       </c>
       <c r="G299" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H299" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I299" s="13" t="inlineStr">
         <is>
@@ -14169,13 +14169,13 @@
         <v>245</v>
       </c>
       <c r="F300" s="12" t="n">
-        <v>11077.9</v>
+        <v>11085</v>
       </c>
       <c r="G300" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H300" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I300" s="13" t="inlineStr">
         <is>
@@ -14204,10 +14204,10 @@
         <v>24</v>
       </c>
       <c r="F301" s="12" t="n">
-        <v>1090.3</v>
+        <v>1090.7</v>
       </c>
       <c r="G301" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H301" s="12" t="n">
         <v>253</v>
@@ -14239,10 +14239,10 @@
         <v>50</v>
       </c>
       <c r="F302" s="12" t="n">
-        <v>2320.2</v>
+        <v>2320.8</v>
       </c>
       <c r="G302" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H302" s="12" t="n">
         <v>693</v>
@@ -14274,13 +14274,13 @@
         <v>112</v>
       </c>
       <c r="F303" s="12" t="n">
-        <v>4837.5</v>
+        <v>4839.5</v>
       </c>
       <c r="G303" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H303" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I303" s="13" t="inlineStr">
         <is>
@@ -14309,13 +14309,13 @@
         <v>212</v>
       </c>
       <c r="F304" s="12" t="n">
-        <v>9230.6</v>
+        <v>9234.700000000001</v>
       </c>
       <c r="G304" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H304" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I304" s="13" t="inlineStr">
         <is>
@@ -14344,13 +14344,13 @@
         <v>48</v>
       </c>
       <c r="F305" s="12" t="n">
-        <v>2089.7</v>
+        <v>2093.4</v>
       </c>
       <c r="G305" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H305" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I305" s="13" t="inlineStr">
         <is>
@@ -14379,13 +14379,13 @@
         <v>338</v>
       </c>
       <c r="F306" s="12" t="n">
-        <v>14873.3</v>
+        <v>14881.2</v>
       </c>
       <c r="G306" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H306" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I306" s="13" t="inlineStr">
         <is>
@@ -14414,13 +14414,13 @@
         <v>148</v>
       </c>
       <c r="F307" s="12" t="n">
-        <v>6196.8</v>
+        <v>6201.8</v>
       </c>
       <c r="G307" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H307" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I307" s="13" t="inlineStr">
         <is>
@@ -14449,13 +14449,13 @@
         <v>139</v>
       </c>
       <c r="F308" s="12" t="n">
-        <v>5850.9</v>
+        <v>5855.8</v>
       </c>
       <c r="G308" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H308" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I308" s="13" t="inlineStr">
         <is>
@@ -14484,13 +14484,13 @@
         <v>219</v>
       </c>
       <c r="F309" s="12" t="n">
-        <v>9266.299999999999</v>
+        <v>9269.700000000001</v>
       </c>
       <c r="G309" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H309" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I309" s="13" t="inlineStr">
         <is>
@@ -14519,13 +14519,13 @@
         <v>254</v>
       </c>
       <c r="F310" s="12" t="n">
-        <v>10446.1</v>
+        <v>10455</v>
       </c>
       <c r="G310" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H310" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I310" s="13" t="inlineStr">
         <is>
@@ -14554,13 +14554,13 @@
         <v>221</v>
       </c>
       <c r="F311" s="12" t="n">
-        <v>8883.200000000001</v>
+        <v>8886.5</v>
       </c>
       <c r="G311" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H311" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I311" s="13" t="inlineStr">
         <is>
@@ -14589,13 +14589,13 @@
         <v>289</v>
       </c>
       <c r="F312" s="12" t="n">
-        <v>11573.1</v>
+        <v>11579.1</v>
       </c>
       <c r="G312" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H312" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I312" s="13" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         <v>87</v>
       </c>
       <c r="F313" s="12" t="n">
-        <v>3426.8</v>
+        <v>3428.6</v>
       </c>
       <c r="G313" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H313" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I313" s="13" t="inlineStr">
         <is>
@@ -14659,13 +14659,13 @@
         <v>221</v>
       </c>
       <c r="F314" s="12" t="n">
-        <v>8976.799999999999</v>
+        <v>8988.700000000001</v>
       </c>
       <c r="G314" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H314" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I314" s="13" t="inlineStr">
         <is>
@@ -14691,16 +14691,16 @@
         <v>97.5</v>
       </c>
       <c r="E315" s="12" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F315" s="12" t="n">
-        <v>13274.8</v>
+        <v>13285.7</v>
       </c>
       <c r="G315" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H315" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I315" s="13" t="inlineStr">
         <is>
@@ -14726,16 +14726,16 @@
         <v>97.5</v>
       </c>
       <c r="E316" s="12" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F316" s="12" t="n">
-        <v>12669.3</v>
+        <v>12676.4</v>
       </c>
       <c r="G316" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H316" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I316" s="13" t="inlineStr">
         <is>
@@ -14764,13 +14764,13 @@
         <v>164</v>
       </c>
       <c r="F317" s="12" t="n">
-        <v>6376.3</v>
+        <v>6380.6</v>
       </c>
       <c r="G317" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H317" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I317" s="13" t="inlineStr">
         <is>
@@ -14796,16 +14796,16 @@
         <v>97.40000000000001</v>
       </c>
       <c r="E318" s="12" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F318" s="12" t="n">
-        <v>7921.1</v>
+        <v>7928.6</v>
       </c>
       <c r="G318" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H318" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I318" s="13" t="inlineStr">
         <is>
@@ -14831,16 +14831,16 @@
         <v>97.40000000000001</v>
       </c>
       <c r="E319" s="12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F319" s="12" t="n">
-        <v>16766.4</v>
+        <v>16778</v>
       </c>
       <c r="G319" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H319" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I319" s="13" t="inlineStr">
         <is>
@@ -14869,13 +14869,13 @@
         <v>57</v>
       </c>
       <c r="F320" s="12" t="n">
-        <v>2200.9</v>
+        <v>2202</v>
       </c>
       <c r="G320" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H320" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I320" s="13" t="inlineStr">
         <is>
@@ -14904,13 +14904,13 @@
         <v>294</v>
       </c>
       <c r="F321" s="12" t="n">
-        <v>11468.9</v>
+        <v>11476.4</v>
       </c>
       <c r="G321" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H321" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I321" s="13" t="inlineStr">
         <is>
@@ -14939,13 +14939,13 @@
         <v>270</v>
       </c>
       <c r="F322" s="12" t="n">
-        <v>10239.5</v>
+        <v>10247.3</v>
       </c>
       <c r="G322" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H322" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I322" s="13" t="inlineStr">
         <is>
@@ -14974,13 +14974,13 @@
         <v>349</v>
       </c>
       <c r="F323" s="12" t="n">
-        <v>13652.7</v>
+        <v>13665.5</v>
       </c>
       <c r="G323" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H323" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I323" s="13" t="inlineStr">
         <is>
@@ -15006,16 +15006,16 @@
         <v>97.3</v>
       </c>
       <c r="E324" s="12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F324" s="12" t="n">
-        <v>7967.4</v>
+        <v>7973.4</v>
       </c>
       <c r="G324" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H324" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I324" s="13" t="inlineStr">
         <is>
@@ -15041,16 +15041,16 @@
         <v>97.2</v>
       </c>
       <c r="E325" s="12" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F325" s="12" t="n">
-        <v>9326</v>
+        <v>9331.9</v>
       </c>
       <c r="G325" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H325" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I325" s="13" t="inlineStr">
         <is>
@@ -15076,16 +15076,16 @@
         <v>97.2</v>
       </c>
       <c r="E326" s="12" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F326" s="12" t="n">
-        <v>9222.200000000001</v>
+        <v>9233</v>
       </c>
       <c r="G326" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H326" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I326" s="13" t="inlineStr">
         <is>
@@ -15111,16 +15111,16 @@
         <v>97.09999999999999</v>
       </c>
       <c r="E327" s="12" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F327" s="12" t="n">
-        <v>6177.3</v>
+        <v>6188</v>
       </c>
       <c r="G327" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H327" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I327" s="13" t="inlineStr">
         <is>
@@ -15149,13 +15149,13 @@
         <v>178</v>
       </c>
       <c r="F328" s="12" t="n">
-        <v>6041.7</v>
+        <v>6045.2</v>
       </c>
       <c r="G328" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H328" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="I328" s="13" t="inlineStr">
         <is>
@@ -15184,13 +15184,13 @@
         <v>235</v>
       </c>
       <c r="F329" s="12" t="n">
-        <v>8072.7</v>
+        <v>8078.2</v>
       </c>
       <c r="G329" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H329" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I329" s="13" t="inlineStr">
         <is>
@@ -15219,10 +15219,10 @@
         <v>53</v>
       </c>
       <c r="F330" s="12" t="n">
-        <v>1841</v>
+        <v>1841.2</v>
       </c>
       <c r="G330" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H330" s="12" t="n">
         <v>621</v>
@@ -15254,13 +15254,13 @@
         <v>138</v>
       </c>
       <c r="F331" s="12" t="n">
-        <v>4835.1</v>
+        <v>4839.2</v>
       </c>
       <c r="G331" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H331" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I331" s="13" t="inlineStr">
         <is>
@@ -15289,13 +15289,13 @@
         <v>627</v>
       </c>
       <c r="F332" s="12" t="n">
-        <v>21340.4</v>
+        <v>21357.7</v>
       </c>
       <c r="G332" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H332" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I332" s="13" t="inlineStr">
         <is>
@@ -15324,13 +15324,13 @@
         <v>325</v>
       </c>
       <c r="F333" s="12" t="n">
-        <v>11294.8</v>
+        <v>11304.3</v>
       </c>
       <c r="G333" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="H333" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I333" s="13" t="inlineStr">
         <is>
@@ -15359,13 +15359,13 @@
         <v>221</v>
       </c>
       <c r="F334" s="12" t="n">
-        <v>7280.3</v>
+        <v>7282</v>
       </c>
       <c r="G334" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H334" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I334" s="13" t="inlineStr">
         <is>
@@ -15394,13 +15394,13 @@
         <v>334</v>
       </c>
       <c r="F335" s="12" t="n">
-        <v>11272.9</v>
+        <v>11281.1</v>
       </c>
       <c r="G335" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H335" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I335" s="13" t="inlineStr">
         <is>
@@ -15429,13 +15429,13 @@
         <v>373</v>
       </c>
       <c r="F336" s="12" t="n">
-        <v>12321.6</v>
+        <v>12342</v>
       </c>
       <c r="G336" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H336" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I336" s="13" t="inlineStr">
         <is>
@@ -15461,16 +15461,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="E337" s="12" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F337" s="12" t="n">
-        <v>17934.6</v>
+        <v>17947.9</v>
       </c>
       <c r="G337" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H337" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I337" s="13" t="inlineStr">
         <is>
@@ -15499,13 +15499,13 @@
         <v>153</v>
       </c>
       <c r="F338" s="12" t="n">
-        <v>4904.4</v>
+        <v>4907.7</v>
       </c>
       <c r="G338" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H338" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I338" s="13" t="inlineStr">
         <is>
@@ -15534,13 +15534,13 @@
         <v>439</v>
       </c>
       <c r="F339" s="12" t="n">
-        <v>14324</v>
+        <v>14335.5</v>
       </c>
       <c r="G339" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H339" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I339" s="13" t="inlineStr">
         <is>
@@ -15569,13 +15569,13 @@
         <v>389</v>
       </c>
       <c r="F340" s="12" t="n">
-        <v>12404.7</v>
+        <v>12409.9</v>
       </c>
       <c r="G340" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H340" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I340" s="13" t="inlineStr">
         <is>
@@ -15604,13 +15604,13 @@
         <v>91</v>
       </c>
       <c r="F341" s="12" t="n">
-        <v>2981.8</v>
+        <v>2982.6</v>
       </c>
       <c r="G341" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H341" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I341" s="13" t="inlineStr">
         <is>
@@ -15639,13 +15639,13 @@
         <v>573</v>
       </c>
       <c r="F342" s="12" t="n">
-        <v>18408.7</v>
+        <v>18423.8</v>
       </c>
       <c r="G342" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H342" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I342" s="13" t="inlineStr">
         <is>
@@ -15674,13 +15674,13 @@
         <v>232</v>
       </c>
       <c r="F343" s="12" t="n">
-        <v>7519.4</v>
+        <v>7525.7</v>
       </c>
       <c r="G343" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H343" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I343" s="13" t="inlineStr">
         <is>
@@ -15709,13 +15709,13 @@
         <v>160</v>
       </c>
       <c r="F344" s="12" t="n">
-        <v>5174.6</v>
+        <v>5183</v>
       </c>
       <c r="G344" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H344" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I344" s="13" t="inlineStr">
         <is>
@@ -15741,16 +15741,16 @@
         <v>96.8</v>
       </c>
       <c r="E345" s="12" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F345" s="12" t="n">
-        <v>13903.3</v>
+        <v>13913.4</v>
       </c>
       <c r="G345" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H345" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I345" s="13" t="inlineStr">
         <is>
@@ -15779,13 +15779,13 @@
         <v>243</v>
       </c>
       <c r="F346" s="12" t="n">
-        <v>7557.9</v>
+        <v>7565.4</v>
       </c>
       <c r="G346" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H346" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I346" s="13" t="inlineStr">
         <is>
@@ -15814,13 +15814,13 @@
         <v>96</v>
       </c>
       <c r="F347" s="12" t="n">
-        <v>2876.5</v>
+        <v>2878.2</v>
       </c>
       <c r="G347" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H347" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I347" s="13" t="inlineStr">
         <is>
@@ -15849,13 +15849,13 @@
         <v>584</v>
       </c>
       <c r="F348" s="12" t="n">
-        <v>17758.7</v>
+        <v>17778.9</v>
       </c>
       <c r="G348" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H348" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I348" s="13" t="inlineStr">
         <is>
@@ -15881,16 +15881,16 @@
         <v>96.7</v>
       </c>
       <c r="E349" s="12" t="n">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="F349" s="12" t="n">
-        <v>20306</v>
+        <v>20324.3</v>
       </c>
       <c r="G349" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H349" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I349" s="13" t="inlineStr">
         <is>
@@ -15919,13 +15919,13 @@
         <v>342</v>
       </c>
       <c r="F350" s="12" t="n">
-        <v>10129.6</v>
+        <v>10134.5</v>
       </c>
       <c r="G350" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H350" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I350" s="13" t="inlineStr">
         <is>
@@ -15954,13 +15954,13 @@
         <v>113</v>
       </c>
       <c r="F351" s="12" t="n">
-        <v>3328.7</v>
+        <v>3331.2</v>
       </c>
       <c r="G351" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H351" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I351" s="13" t="inlineStr">
         <is>
@@ -15986,16 +15986,16 @@
         <v>96.59999999999999</v>
       </c>
       <c r="E352" s="12" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F352" s="12" t="n">
-        <v>14091.9</v>
+        <v>14103.5</v>
       </c>
       <c r="G352" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H352" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I352" s="13" t="inlineStr">
         <is>
@@ -16024,13 +16024,13 @@
         <v>458</v>
       </c>
       <c r="F353" s="12" t="n">
-        <v>12976</v>
+        <v>12987.4</v>
       </c>
       <c r="G353" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H353" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I353" s="13" t="inlineStr">
         <is>
@@ -16059,13 +16059,13 @@
         <v>112</v>
       </c>
       <c r="F354" s="12" t="n">
-        <v>3234.5</v>
+        <v>3238.3</v>
       </c>
       <c r="G354" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H354" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I354" s="13" t="inlineStr">
         <is>
@@ -16094,13 +16094,13 @@
         <v>40</v>
       </c>
       <c r="F355" s="12" t="n">
-        <v>1132.9</v>
+        <v>1134.4</v>
       </c>
       <c r="G355" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H355" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I355" s="13" t="inlineStr">
         <is>
@@ -16126,16 +16126,16 @@
         <v>96.5</v>
       </c>
       <c r="E356" s="12" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F356" s="12" t="n">
-        <v>10789</v>
+        <v>10801</v>
       </c>
       <c r="G356" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H356" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
@@ -16164,13 +16164,13 @@
         <v>276</v>
       </c>
       <c r="F357" s="12" t="n">
-        <v>7711.1</v>
+        <v>7716.4</v>
       </c>
       <c r="G357" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H357" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I357" s="13" t="inlineStr">
         <is>
@@ -16199,13 +16199,13 @@
         <v>578</v>
       </c>
       <c r="F358" s="12" t="n">
-        <v>16247</v>
+        <v>16262.1</v>
       </c>
       <c r="G358" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="H358" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I358" s="13" t="inlineStr">
         <is>
@@ -16234,13 +16234,13 @@
         <v>48</v>
       </c>
       <c r="F359" s="12" t="n">
-        <v>1297.6</v>
+        <v>1298</v>
       </c>
       <c r="G359" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H359" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I359" s="13" t="inlineStr">
         <is>
@@ -16269,13 +16269,13 @@
         <v>319</v>
       </c>
       <c r="F360" s="12" t="n">
-        <v>8368.200000000001</v>
+        <v>8371.200000000001</v>
       </c>
       <c r="G360" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H360" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
@@ -16304,13 +16304,13 @@
         <v>533</v>
       </c>
       <c r="F361" s="12" t="n">
-        <v>14152.4</v>
+        <v>14161.2</v>
       </c>
       <c r="G361" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H361" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I361" s="13" t="inlineStr">
         <is>
@@ -16339,13 +16339,13 @@
         <v>663</v>
       </c>
       <c r="F362" s="12" t="n">
-        <v>16822.5</v>
+        <v>16838.2</v>
       </c>
       <c r="G362" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H362" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
@@ -16374,13 +16374,13 @@
         <v>166</v>
       </c>
       <c r="F363" s="12" t="n">
-        <v>4279.8</v>
+        <v>4282.7</v>
       </c>
       <c r="G363" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H363" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I363" s="13" t="inlineStr">
         <is>
@@ -16406,16 +16406,16 @@
         <v>96.09999999999999</v>
       </c>
       <c r="E364" s="12" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F364" s="12" t="n">
-        <v>6219.7</v>
+        <v>6221.9</v>
       </c>
       <c r="G364" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H364" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
@@ -16444,13 +16444,13 @@
         <v>429</v>
       </c>
       <c r="F365" s="12" t="n">
-        <v>11012.1</v>
+        <v>11018.8</v>
       </c>
       <c r="G365" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H365" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I365" s="13" t="inlineStr">
         <is>
@@ -16476,16 +16476,16 @@
         <v>96.09999999999999</v>
       </c>
       <c r="E366" s="12" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F366" s="12" t="n">
-        <v>13138.8</v>
+        <v>13150.2</v>
       </c>
       <c r="G366" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H366" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I366" s="13" t="inlineStr">
         <is>
@@ -16514,13 +16514,13 @@
         <v>521</v>
       </c>
       <c r="F367" s="12" t="n">
-        <v>12889.8</v>
+        <v>12896.2</v>
       </c>
       <c r="G367" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H367" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="I367" s="13" t="inlineStr">
         <is>
@@ -16549,13 +16549,13 @@
         <v>271</v>
       </c>
       <c r="F368" s="12" t="n">
-        <v>6848.6</v>
+        <v>6853.5</v>
       </c>
       <c r="G368" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H368" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I368" s="13" t="inlineStr">
         <is>
@@ -16581,16 +16581,16 @@
         <v>96</v>
       </c>
       <c r="E369" s="12" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F369" s="12" t="n">
-        <v>12377</v>
+        <v>12387.6</v>
       </c>
       <c r="G369" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H369" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I369" s="13" t="inlineStr">
         <is>
@@ -16619,13 +16619,13 @@
         <v>317</v>
       </c>
       <c r="F370" s="12" t="n">
-        <v>7780.1</v>
+        <v>7788.8</v>
       </c>
       <c r="G370" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H370" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I370" s="13" t="inlineStr">
         <is>
@@ -16651,16 +16651,16 @@
         <v>95.8</v>
       </c>
       <c r="E371" s="12" t="n">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F371" s="12" t="n">
-        <v>23328.4</v>
+        <v>23350.2</v>
       </c>
       <c r="G371" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H371" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I371" s="13" t="inlineStr">
         <is>
@@ -16689,13 +16689,13 @@
         <v>294</v>
       </c>
       <c r="F372" s="12" t="n">
-        <v>7071.9</v>
+        <v>7075.1</v>
       </c>
       <c r="G372" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H372" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I372" s="13" t="inlineStr">
         <is>
@@ -16724,13 +16724,13 @@
         <v>358</v>
       </c>
       <c r="F373" s="12" t="n">
-        <v>8485.299999999999</v>
+        <v>8488.5</v>
       </c>
       <c r="G373" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H373" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I373" s="13" t="inlineStr">
         <is>
@@ -16759,13 +16759,13 @@
         <v>66</v>
       </c>
       <c r="F374" s="12" t="n">
-        <v>1522.5</v>
+        <v>1524.7</v>
       </c>
       <c r="G374" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="H374" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I374" s="13" t="inlineStr">
         <is>
@@ -16794,13 +16794,13 @@
         <v>868</v>
       </c>
       <c r="F375" s="12" t="n">
-        <v>20205.1</v>
+        <v>20213.3</v>
       </c>
       <c r="G375" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H375" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I375" s="13" t="inlineStr">
         <is>
@@ -16826,16 +16826,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="E376" s="12" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F376" s="12" t="n">
-        <v>12090.6</v>
+        <v>12098.9</v>
       </c>
       <c r="G376" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H376" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I376" s="13" t="inlineStr">
         <is>
@@ -16864,13 +16864,13 @@
         <v>401</v>
       </c>
       <c r="F377" s="12" t="n">
-        <v>9135.700000000001</v>
+        <v>9145.6</v>
       </c>
       <c r="G377" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H377" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
@@ -16899,13 +16899,13 @@
         <v>230</v>
       </c>
       <c r="F378" s="12" t="n">
-        <v>5064.3</v>
+        <v>5066.4</v>
       </c>
       <c r="G378" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H378" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="I378" s="13" t="inlineStr">
         <is>
@@ -16934,13 +16934,13 @@
         <v>341</v>
       </c>
       <c r="F379" s="12" t="n">
-        <v>7537.2</v>
+        <v>7539.5</v>
       </c>
       <c r="G379" s="12" t="n">
         <v>693</v>
       </c>
       <c r="H379" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I379" s="13" t="inlineStr">
         <is>
@@ -16969,13 +16969,13 @@
         <v>338</v>
       </c>
       <c r="F380" s="12" t="n">
-        <v>7451.1</v>
+        <v>7457.7</v>
       </c>
       <c r="G380" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H380" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I380" s="13" t="inlineStr">
         <is>
@@ -17004,13 +17004,13 @@
         <v>310</v>
       </c>
       <c r="F381" s="12" t="n">
-        <v>6678.5</v>
+        <v>6682.4</v>
       </c>
       <c r="G381" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H381" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I381" s="13" t="inlineStr">
         <is>
@@ -17036,16 +17036,16 @@
         <v>95.40000000000001</v>
       </c>
       <c r="E382" s="12" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F382" s="12" t="n">
-        <v>10597.6</v>
+        <v>10603.3</v>
       </c>
       <c r="G382" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H382" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I382" s="13" t="inlineStr">
         <is>
@@ -17071,16 +17071,16 @@
         <v>95.3</v>
       </c>
       <c r="E383" s="12" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F383" s="12" t="n">
-        <v>10594.5</v>
+        <v>10605.4</v>
       </c>
       <c r="G383" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H383" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I383" s="13" t="inlineStr">
         <is>
@@ -17109,13 +17109,13 @@
         <v>318</v>
       </c>
       <c r="F384" s="12" t="n">
-        <v>6823.1</v>
+        <v>6829.2</v>
       </c>
       <c r="G384" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H384" s="12" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="I384" s="13" t="inlineStr">
         <is>
@@ -17144,13 +17144,13 @@
         <v>1127</v>
       </c>
       <c r="F385" s="12" t="n">
-        <v>23937.8</v>
+        <v>23957.1</v>
       </c>
       <c r="G385" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="H385" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I385" s="13" t="inlineStr">
         <is>
@@ -17179,13 +17179,13 @@
         <v>283</v>
       </c>
       <c r="F386" s="12" t="n">
-        <v>6001.2</v>
+        <v>6007.5</v>
       </c>
       <c r="G386" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="H386" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I386" s="13" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>95.2</v>
       </c>
       <c r="E387" s="12" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F387" s="12" t="n">
-        <v>12651.2</v>
+        <v>12659.3</v>
       </c>
       <c r="G387" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H387" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="I387" s="13" t="inlineStr">
         <is>
@@ -17249,13 +17249,13 @@
         <v>653</v>
       </c>
       <c r="F388" s="12" t="n">
-        <v>13619.7</v>
+        <v>13627.2</v>
       </c>
       <c r="G388" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H388" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I388" s="13" t="inlineStr">
         <is>
@@ -17284,13 +17284,13 @@
         <v>176</v>
       </c>
       <c r="F389" s="12" t="n">
-        <v>3587.5</v>
+        <v>3589.3</v>
       </c>
       <c r="G389" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H389" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I389" s="13" t="inlineStr">
         <is>
@@ -17319,13 +17319,13 @@
         <v>255</v>
       </c>
       <c r="F390" s="12" t="n">
-        <v>5213.5</v>
+        <v>5214.5</v>
       </c>
       <c r="G390" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H390" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="I390" s="13" t="inlineStr">
         <is>
@@ -17354,13 +17354,13 @@
         <v>442</v>
       </c>
       <c r="F391" s="12" t="n">
-        <v>9092.6</v>
+        <v>9096.200000000001</v>
       </c>
       <c r="G391" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H391" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I391" s="13" t="inlineStr">
         <is>
@@ -17389,13 +17389,13 @@
         <v>714</v>
       </c>
       <c r="F392" s="12" t="n">
-        <v>14691.7</v>
+        <v>14707</v>
       </c>
       <c r="G392" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H392" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="I392" s="13" t="inlineStr">
         <is>
@@ -17424,13 +17424,13 @@
         <v>1030</v>
       </c>
       <c r="F393" s="12" t="n">
-        <v>19626.8</v>
+        <v>19639</v>
       </c>
       <c r="G393" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H393" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I393" s="13" t="inlineStr">
         <is>
@@ -17459,13 +17459,13 @@
         <v>128</v>
       </c>
       <c r="F394" s="12" t="n">
-        <v>2451.8</v>
+        <v>2453</v>
       </c>
       <c r="G394" s="12" t="n">
         <v>860</v>
       </c>
       <c r="H394" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I394" s="13" t="inlineStr">
         <is>
@@ -17491,16 +17491,16 @@
         <v>94.8</v>
       </c>
       <c r="E395" s="12" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F395" s="12" t="n">
-        <v>19007.2</v>
+        <v>19023.8</v>
       </c>
       <c r="G395" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="H395" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I395" s="13" t="inlineStr">
         <is>
@@ -17529,13 +17529,13 @@
         <v>100</v>
       </c>
       <c r="F396" s="12" t="n">
-        <v>1878.8</v>
+        <v>1880.2</v>
       </c>
       <c r="G396" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H396" s="12" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="I396" s="13" t="inlineStr">
         <is>
@@ -17564,13 +17564,13 @@
         <v>507</v>
       </c>
       <c r="F397" s="12" t="n">
-        <v>9529</v>
+        <v>9538.1</v>
       </c>
       <c r="G397" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H397" s="12" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
       <c r="I397" s="13" t="inlineStr">
         <is>
@@ -17599,13 +17599,13 @@
         <v>728</v>
       </c>
       <c r="F398" s="12" t="n">
-        <v>12998.3</v>
+        <v>13002.2</v>
       </c>
       <c r="G398" s="12" t="n">
         <v>2061</v>
       </c>
       <c r="H398" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I398" s="13" t="inlineStr">
         <is>
@@ -17634,10 +17634,10 @@
         <v>36</v>
       </c>
       <c r="F399" s="12" t="n">
-        <v>615.4</v>
+        <v>615.6</v>
       </c>
       <c r="G399" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H399" s="12" t="n">
         <v>253</v>
@@ -17669,10 +17669,10 @@
         <v>158</v>
       </c>
       <c r="F400" s="12" t="n">
-        <v>2715.8</v>
+        <v>2716.2</v>
       </c>
       <c r="G400" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H400" s="12" t="n">
         <v>693</v>
@@ -17704,13 +17704,13 @@
         <v>1563</v>
       </c>
       <c r="F401" s="12" t="n">
-        <v>25234.8</v>
+        <v>25249</v>
       </c>
       <c r="G401" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H401" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I401" s="13" t="inlineStr">
         <is>
@@ -17739,13 +17739,13 @@
         <v>985</v>
       </c>
       <c r="F402" s="12" t="n">
-        <v>15788.8</v>
+        <v>15797.2</v>
       </c>
       <c r="G402" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H402" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="I402" s="13" t="inlineStr">
         <is>
@@ -17774,13 +17774,13 @@
         <v>1359</v>
       </c>
       <c r="F403" s="12" t="n">
-        <v>21152.6</v>
+        <v>21160.9</v>
       </c>
       <c r="G403" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H403" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I403" s="13" t="inlineStr">
         <is>
@@ -17806,16 +17806,16 @@
         <v>93.5</v>
       </c>
       <c r="E404" s="12" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F404" s="12" t="n">
-        <v>4702.4</v>
+        <v>4711.5</v>
       </c>
       <c r="G404" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="H404" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="I404" s="13" t="inlineStr">
         <is>
@@ -17844,13 +17844,13 @@
         <v>1309</v>
       </c>
       <c r="F405" s="12" t="n">
-        <v>19541.7</v>
+        <v>19557.9</v>
       </c>
       <c r="G405" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H405" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I405" s="13" t="inlineStr">
         <is>
@@ -17876,16 +17876,16 @@
         <v>93.09999999999999</v>
       </c>
       <c r="E406" s="12" t="n">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="F406" s="12" t="n">
-        <v>41098.1</v>
+        <v>41126.6</v>
       </c>
       <c r="G406" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H406" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I406" s="13" t="inlineStr">
         <is>
@@ -17911,16 +17911,16 @@
         <v>93</v>
       </c>
       <c r="E407" s="12" t="n">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F407" s="12" t="n">
-        <v>9983.200000000001</v>
+        <v>9988.5</v>
       </c>
       <c r="G407" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="H407" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I407" s="13" t="inlineStr">
         <is>
@@ -17949,13 +17949,13 @@
         <v>230</v>
       </c>
       <c r="F408" s="12" t="n">
-        <v>3179.3</v>
+        <v>3183.9</v>
       </c>
       <c r="G408" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H408" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I408" s="13" t="inlineStr">
         <is>
@@ -17984,13 +17984,13 @@
         <v>1239</v>
       </c>
       <c r="F409" s="12" t="n">
-        <v>16258.8</v>
+        <v>16269.6</v>
       </c>
       <c r="G409" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H409" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I409" s="13" t="inlineStr">
         <is>
@@ -18004,28 +18004,28 @@
       </c>
       <c r="B410" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C410" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D410" s="12" t="n">
         <v>92.40000000000001</v>
       </c>
       <c r="E410" s="12" t="n">
-        <v>289</v>
+        <v>806</v>
       </c>
       <c r="F410" s="12" t="n">
-        <v>3792.9</v>
+        <v>10543.8</v>
       </c>
       <c r="G410" s="12" t="n">
-        <v>7768</v>
+        <v>7685</v>
       </c>
       <c r="H410" s="12" t="n">
-        <v>1852</v>
+        <v>14466</v>
       </c>
       <c r="I410" s="13" t="inlineStr">
         <is>
@@ -18039,28 +18039,28 @@
       </c>
       <c r="B411" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="C411" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D411" s="12" t="n">
         <v>92.40000000000001</v>
       </c>
       <c r="E411" s="12" t="n">
-        <v>805</v>
+        <v>2386</v>
       </c>
       <c r="F411" s="12" t="n">
-        <v>10536.1</v>
+        <v>31313.7</v>
       </c>
       <c r="G411" s="12" t="n">
-        <v>7678</v>
+        <v>11954</v>
       </c>
       <c r="H411" s="12" t="n">
-        <v>14458</v>
+        <v>82027</v>
       </c>
       <c r="I411" s="13" t="inlineStr">
         <is>
@@ -18074,28 +18074,28 @@
       </c>
       <c r="B412" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C412" s="12" t="inlineStr">
         <is>
-          <t>Prevention / DPP</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D412" s="12" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="E412" s="12" t="n">
-        <v>2384</v>
+        <v>291</v>
       </c>
       <c r="F412" s="12" t="n">
-        <v>31285.9</v>
+        <v>3799</v>
       </c>
       <c r="G412" s="12" t="n">
-        <v>11940</v>
+        <v>7772</v>
       </c>
       <c r="H412" s="12" t="n">
-        <v>81977</v>
+        <v>1857</v>
       </c>
       <c r="I412" s="13" t="inlineStr">
         <is>
@@ -18121,16 +18121,16 @@
         <v>92.3</v>
       </c>
       <c r="E413" s="12" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="F413" s="12" t="n">
-        <v>25088.2</v>
+        <v>25107.3</v>
       </c>
       <c r="G413" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H413" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I413" s="13" t="inlineStr">
         <is>
@@ -18156,16 +18156,16 @@
         <v>92.09999999999999</v>
       </c>
       <c r="E414" s="12" t="n">
-        <v>2958</v>
+        <v>2960</v>
       </c>
       <c r="F414" s="12" t="n">
-        <v>37595.8</v>
+        <v>37617.1</v>
       </c>
       <c r="G414" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="H414" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I414" s="13" t="inlineStr">
         <is>
@@ -18194,13 +18194,13 @@
         <v>533</v>
       </c>
       <c r="F415" s="12" t="n">
-        <v>6511.4</v>
+        <v>6513.6</v>
       </c>
       <c r="G415" s="12" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
       <c r="H415" s="12" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
       <c r="I415" s="13" t="inlineStr">
         <is>
@@ -18226,16 +18226,16 @@
         <v>91.7</v>
       </c>
       <c r="E416" s="12" t="n">
-        <v>2776</v>
+        <v>2783</v>
       </c>
       <c r="F416" s="12" t="n">
-        <v>33555.2</v>
+        <v>33583.8</v>
       </c>
       <c r="G416" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H416" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I416" s="13" t="inlineStr">
         <is>
@@ -18264,13 +18264,13 @@
         <v>2849</v>
       </c>
       <c r="F417" s="12" t="n">
-        <v>34427.1</v>
+        <v>34447.1</v>
       </c>
       <c r="G417" s="12" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
       <c r="H417" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I417" s="13" t="inlineStr">
         <is>
@@ -18296,16 +18296,16 @@
         <v>91.7</v>
       </c>
       <c r="E418" s="12" t="n">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="F418" s="12" t="n">
-        <v>25882.7</v>
+        <v>25903.3</v>
       </c>
       <c r="G418" s="12" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
       <c r="H418" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I418" s="13" t="inlineStr">
         <is>
@@ -18331,16 +18331,16 @@
         <v>91.59999999999999</v>
       </c>
       <c r="E419" s="12" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="F419" s="12" t="n">
-        <v>32430.9</v>
+        <v>32449.7</v>
       </c>
       <c r="G419" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H419" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I419" s="13" t="inlineStr">
         <is>
@@ -18369,13 +18369,13 @@
         <v>1278</v>
       </c>
       <c r="F420" s="12" t="n">
-        <v>14808.4</v>
+        <v>14816.2</v>
       </c>
       <c r="G420" s="12" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
       <c r="H420" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="I420" s="13" t="inlineStr">
         <is>
@@ -18404,13 +18404,13 @@
         <v>240</v>
       </c>
       <c r="F421" s="12" t="n">
-        <v>2652.2</v>
+        <v>2654</v>
       </c>
       <c r="G421" s="12" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H421" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="I421" s="13" t="inlineStr">
         <is>
@@ -18436,16 +18436,16 @@
         <v>90.3</v>
       </c>
       <c r="E422" s="12" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F422" s="12" t="n">
-        <v>4439.7</v>
+        <v>4446.3</v>
       </c>
       <c r="G422" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H422" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I422" s="13" t="inlineStr">
         <is>
@@ -18471,16 +18471,16 @@
         <v>90.3</v>
       </c>
       <c r="E423" s="12" t="n">
-        <v>2854</v>
+        <v>2855</v>
       </c>
       <c r="F423" s="12" t="n">
-        <v>29537.8</v>
+        <v>29551</v>
       </c>
       <c r="G423" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H423" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I423" s="13" t="inlineStr">
         <is>
@@ -18506,16 +18506,16 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E424" s="12" t="n">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="F424" s="12" t="n">
-        <v>19046.9</v>
+        <v>19067.7</v>
       </c>
       <c r="G424" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H424" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I424" s="13" t="inlineStr">
         <is>
@@ -18541,16 +18541,16 @@
         <v>89.8</v>
       </c>
       <c r="E425" s="12" t="n">
-        <v>3632</v>
+        <v>3636</v>
       </c>
       <c r="F425" s="12" t="n">
-        <v>35773.5</v>
+        <v>35797</v>
       </c>
       <c r="G425" s="12" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
       <c r="H425" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I425" s="14" t="inlineStr">
         <is>
@@ -18579,13 +18579,13 @@
         <v>1608</v>
       </c>
       <c r="F426" s="12" t="n">
-        <v>14240.8</v>
+        <v>14255.1</v>
       </c>
       <c r="G426" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="H426" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="I426" s="14" t="inlineStr">
         <is>
@@ -18611,16 +18611,16 @@
         <v>87.8</v>
       </c>
       <c r="E427" s="12" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F427" s="12" t="n">
-        <v>1681.9</v>
+        <v>1683.8</v>
       </c>
       <c r="G427" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H427" s="12" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I427" s="14" t="inlineStr">
         <is>
@@ -18646,16 +18646,16 @@
         <v>86.3</v>
       </c>
       <c r="E428" s="12" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F428" s="12" t="n">
-        <v>7993.3</v>
+        <v>7996.3</v>
       </c>
       <c r="G428" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H428" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I428" s="14" t="inlineStr">
         <is>
@@ -18681,16 +18681,16 @@
         <v>85.5</v>
       </c>
       <c r="E429" s="12" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F429" s="12" t="n">
-        <v>3036.9</v>
+        <v>3041.3</v>
       </c>
       <c r="G429" s="12" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
       <c r="H429" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I429" s="14" t="inlineStr">
         <is>
@@ -18716,16 +18716,16 @@
         <v>85.5</v>
       </c>
       <c r="E430" s="12" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="F430" s="12" t="n">
-        <v>14348.2</v>
+        <v>14360.3</v>
       </c>
       <c r="G430" s="12" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
       <c r="H430" s="12" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
       <c r="I430" s="14" t="inlineStr">
         <is>
@@ -18751,16 +18751,16 @@
         <v>85.3</v>
       </c>
       <c r="E431" s="12" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F431" s="12" t="n">
-        <v>2149.2</v>
+        <v>2152.1</v>
       </c>
       <c r="G431" s="12" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
       <c r="H431" s="12" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="I431" s="14" t="inlineStr">
         <is>
@@ -18786,16 +18786,16 @@
         <v>85.3</v>
       </c>
       <c r="E432" s="12" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F432" s="12" t="n">
-        <v>4874.5</v>
+        <v>4882.4</v>
       </c>
       <c r="G432" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="H432" s="12" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
       <c r="I432" s="14" t="inlineStr">
         <is>
@@ -18821,16 +18821,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="E433" s="12" t="n">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="F433" s="12" t="n">
-        <v>10269.2</v>
+        <v>10279.5</v>
       </c>
       <c r="G433" s="12" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
       <c r="H433" s="12" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
       <c r="I433" s="14" t="inlineStr">
         <is>
@@ -18856,16 +18856,16 @@
         <v>82.3</v>
       </c>
       <c r="E434" s="12" t="n">
-        <v>8244</v>
+        <v>8257</v>
       </c>
       <c r="F434" s="12" t="n">
-        <v>46532.3</v>
+        <v>46572.1</v>
       </c>
       <c r="G434" s="12" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
       <c r="H434" s="12" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
       <c r="I434" s="14" t="inlineStr">
         <is>
@@ -18891,16 +18891,16 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E435" s="12" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F435" s="12" t="n">
-        <v>3699.5</v>
+        <v>3702.3</v>
       </c>
       <c r="G435" s="12" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="H435" s="12" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
       <c r="I435" s="14" t="inlineStr">
         <is>
@@ -18923,19 +18923,19 @@
         </is>
       </c>
       <c r="D436" s="12" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E436" s="12" t="n">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="F436" s="12" t="n">
-        <v>11685.4</v>
+        <v>11690.3</v>
       </c>
       <c r="G436" s="12" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
       <c r="H436" s="12" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
       <c r="I436" s="14" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>81977</v>
+        <v>82027</v>
       </c>
     </row>
     <row r="3">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>26413</v>
+        <v>26442</v>
       </c>
     </row>
     <row r="4">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>20604</v>
+        <v>20620</v>
       </c>
     </row>
     <row r="5">
@@ -19011,7 +19011,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>17242</v>
+        <v>17251</v>
       </c>
     </row>
     <row r="6">
@@ -19021,7 +19021,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>15611</v>
+        <v>15622</v>
       </c>
     </row>
     <row r="7">
@@ -19031,7 +19031,7 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>14458</v>
+        <v>14466</v>
       </c>
     </row>
     <row r="8">
@@ -19041,7 +19041,7 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>13735</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="9">
@@ -19051,7 +19051,7 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>12830</v>
+        <v>12837</v>
       </c>
     </row>
     <row r="10">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>11940</v>
+        <v>11954</v>
       </c>
     </row>
     <row r="11">
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>10643</v>
+        <v>10646</v>
       </c>
     </row>
     <row r="12">
@@ -19081,7 +19081,7 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>8172</v>
+        <v>8180</v>
       </c>
     </row>
     <row r="13">
@@ -19091,7 +19091,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>7768</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="14">
@@ -19101,7 +19101,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>7678</v>
+        <v>7685</v>
       </c>
     </row>
     <row r="15">
@@ -19111,7 +19111,7 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>6990</v>
+        <v>6997</v>
       </c>
     </row>
     <row r="16">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5458</v>
+        <v>5459</v>
       </c>
     </row>
     <row r="17">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>4980</v>
+        <v>4981</v>
       </c>
     </row>
     <row r="18">
@@ -19141,7 +19141,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4699</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="19">
@@ -19151,7 +19151,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>4407</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="20">
@@ -19161,7 +19161,7 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="21">
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>2358</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="22">
@@ -19191,7 +19191,7 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="24">
@@ -19201,7 +19201,7 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>1852</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="25">
@@ -19211,7 +19211,7 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="26">
@@ -19221,7 +19221,7 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="27">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="31">

--- a/Analysis/Results/literature_gap_matrix.xlsx
+++ b/Analysis/Results/literature_gap_matrix.xlsx
@@ -843,7 +843,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>72</v>
@@ -855,7 +855,7 @@
         <v>213</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>105</v>
@@ -873,7 +873,7 @@
         <v>53</v>
       </c>
       <c r="M3" s="10" t="n">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="N3" s="5" t="n">
         <v>51</v>
@@ -882,10 +882,10 @@
         <v>344</v>
       </c>
       <c r="P3" s="10" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>128</v>
@@ -921,7 +921,7 @@
         <v>13</v>
       </c>
       <c r="AC3" s="6" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AD3" s="10" t="n">
         <v>2874</v>
@@ -943,7 +943,7 @@
         <v>72</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>24</v>
@@ -958,7 +958,7 @@
         <v>113</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>58</v>
@@ -970,7 +970,7 @@
         <v>10</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N4" s="8" t="n">
         <v>2</v>
@@ -1015,13 +1015,13 @@
         <v>148</v>
       </c>
       <c r="AB4" s="6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AC4" s="7" t="n">
         <v>31</v>
       </c>
       <c r="AD4" s="10" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="AE4" s="7" t="n">
         <v>22</v>
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>177</v>
@@ -1155,7 +1155,7 @@
         <v>25</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>23</v>
@@ -1215,7 +1215,7 @@
         <v>213</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="AE6" s="5" t="n">
         <v>153</v>
@@ -1231,7 +1231,7 @@
         <v>68</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>179</v>
@@ -1240,10 +1240,10 @@
         <v>6</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>166</v>
@@ -1252,7 +1252,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>130</v>
@@ -1261,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>242</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>296</v>
@@ -1303,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="AA7" s="6" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AB7" s="8" t="n">
         <v>3</v>
@@ -1312,7 +1312,7 @@
         <v>432</v>
       </c>
       <c r="AD7" s="10" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="AE7" s="5" t="n">
         <v>140</v>
@@ -1343,16 +1343,16 @@
         <v>166</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>66</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>9</v>
@@ -1370,7 +1370,7 @@
         <v>98</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>51</v>
@@ -1409,7 +1409,7 @@
         <v>12</v>
       </c>
       <c r="AD8" s="6" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AE8" s="7" t="n">
         <v>27</v>
@@ -1428,7 +1428,7 @@
         <v>30</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E9" s="8" t="n">
         <v>7</v>
@@ -1443,7 +1443,7 @@
         <v>66</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>15</v>
@@ -1531,43 +1531,43 @@
         <v>4</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>34</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O10" s="5" t="n">
         <v>111</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="S10" s="5" t="n">
         <v>56</v>
@@ -1582,7 +1582,7 @@
         <v>35</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>29</v>
@@ -1594,7 +1594,7 @@
         <v>48</v>
       </c>
       <c r="AA10" s="6" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>16</v>
@@ -1603,10 +1603,10 @@
         <v>70</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>2805</v>
+        <v>2810</v>
       </c>
       <c r="AE10" s="6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -1634,16 +1634,16 @@
         <v>130</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>4</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>13</v>
@@ -1658,10 +1658,10 @@
         <v>50</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>80</v>
@@ -1700,7 +1700,7 @@
         <v>17</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="AE11" s="5" t="n">
         <v>120</v>
@@ -1743,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>8</v>
@@ -1782,7 +1782,7 @@
         <v>48</v>
       </c>
       <c r="Y12" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Z12" s="9" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>21</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E13" s="8" t="n">
         <v>1</v>
@@ -1825,7 +1825,7 @@
         <v>155</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>51</v>
@@ -1834,7 +1834,7 @@
         <v>112</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>91</v>
@@ -1843,22 +1843,22 @@
         <v>8</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="S13" s="7" t="n">
         <v>14</v>
@@ -1867,7 +1867,7 @@
         <v>141</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="V13" s="7" t="n">
         <v>38</v>
@@ -1891,10 +1891,10 @@
         <v>9</v>
       </c>
       <c r="AC13" s="6" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AD13" s="10" t="n">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="AE13" s="6" t="n">
         <v>274</v>
@@ -1922,7 +1922,7 @@
         <v>25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>2</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>2</v>
@@ -1940,16 +1940,16 @@
         <v>1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>14</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q14" s="7" t="n">
         <v>40</v>
@@ -1964,7 +1964,7 @@
         <v>8</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>1</v>
@@ -1991,7 +1991,7 @@
         <v>25</v>
       </c>
       <c r="AD14" s="6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AE14" s="7" t="n">
         <v>17</v>
@@ -2037,19 +2037,19 @@
         <v>7</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>14</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="R15" s="6" t="n">
         <v>279</v>
@@ -2061,7 +2061,7 @@
         <v>220</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="V15" s="7" t="n">
         <v>33</v>
@@ -2104,7 +2104,7 @@
         <v>30</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>159</v>
@@ -2116,7 +2116,7 @@
         <v>320</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>98</v>
@@ -2125,31 +2125,31 @@
         <v>56</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>31</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S16" s="7" t="n">
         <v>18</v>
@@ -2158,7 +2158,7 @@
         <v>340</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="V16" s="5" t="n">
         <v>81</v>
@@ -2201,7 +2201,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>49</v>
@@ -2216,37 +2216,37 @@
         <v>296</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>25</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L17" s="8" t="n">
         <v>2</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>40</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="S17" s="7" t="n">
         <v>21</v>
@@ -2255,7 +2255,7 @@
         <v>78</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="V17" s="7" t="n">
         <v>12</v>
@@ -2282,10 +2282,10 @@
         <v>72</v>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AE17" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -2319,7 +2319,7 @@
         <v>17</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>80</v>
@@ -2328,7 +2328,7 @@
         <v>23</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>96</v>
@@ -2337,31 +2337,31 @@
         <v>279</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="S18" s="5" t="n">
         <v>50</v>
       </c>
       <c r="T18" s="10" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="V18" s="5" t="n">
         <v>69</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="X18" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y18" s="6" t="n">
         <v>406</v>
@@ -2370,16 +2370,16 @@
         <v>80</v>
       </c>
       <c r="AA18" s="5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AB18" s="8" t="n">
         <v>5</v>
       </c>
       <c r="AC18" s="6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="AE18" s="5" t="n">
         <v>58</v>
@@ -2537,16 +2537,16 @@
         <v>78</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="S20" s="7" t="n">
         <v>14</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="V20" s="6" t="n">
         <v>338</v>
@@ -2573,7 +2573,7 @@
         <v>49</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="AE20" s="5" t="n">
         <v>58</v>
@@ -2619,31 +2619,31 @@
         <v>11</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="S21" s="7" t="n">
         <v>20</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="V21" s="6" t="n">
         <v>318</v>
@@ -2804,7 +2804,7 @@
         <v>17</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>1615</v>
@@ -2828,7 +2828,7 @@
         <v>88</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="S23" s="7" t="n">
         <v>31</v>
@@ -2843,7 +2843,7 @@
         <v>256</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>26</v>
@@ -2864,7 +2864,7 @@
         <v>672</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>8286</v>
+        <v>8292</v>
       </c>
       <c r="AE23" s="6" t="n">
         <v>380</v>
@@ -2925,7 +2925,7 @@
         <v>4</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="S24" s="9" t="n">
         <v>0</v>
@@ -2943,10 +2943,10 @@
         <v>26</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Z24" s="7" t="n">
         <v>12</v>
@@ -2961,7 +2961,7 @@
         <v>14</v>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AE24" s="8" t="n">
         <v>6</v>
@@ -3004,7 +3004,7 @@
         <v>79</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>67</v>
@@ -3040,10 +3040,10 @@
         <v>252</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="Z25" s="5" t="n">
         <v>75</v>
@@ -3058,7 +3058,7 @@
         <v>257</v>
       </c>
       <c r="AD25" s="10" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AE25" s="5" t="n">
         <v>51</v>
@@ -3183,7 +3183,7 @@
         <v>311</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>43</v>
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>208</v>
@@ -3216,7 +3216,7 @@
         <v>56</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S27" s="7" t="n">
         <v>11</v>
@@ -3243,7 +3243,7 @@
         <v>79</v>
       </c>
       <c r="AA27" s="4" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="AB27" s="7" t="n">
         <v>30</v>
@@ -3252,10 +3252,10 @@
         <v>327</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28">
@@ -3271,7 +3271,7 @@
         <v>13</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E28" s="8" t="n">
         <v>1</v>
@@ -3343,7 +3343,7 @@
         <v>30</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AC28" s="7" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>31</v>
@@ -3395,7 +3395,7 @@
         <v>33</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N29" s="7" t="n">
         <v>25</v>
@@ -3410,7 +3410,7 @@
         <v>72</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>2</v>
@@ -3443,7 +3443,7 @@
         <v>10</v>
       </c>
       <c r="AC29" s="4" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="AD29" s="10" t="n">
         <v>3652</v>
@@ -3465,37 +3465,37 @@
         <v>2874</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>39</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>223</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2805</v>
+        <v>2810</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>116</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O30" s="6" t="n">
         <v>873</v>
@@ -3504,16 +3504,16 @@
         <v>2731</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="S30" s="5" t="n">
         <v>132</v>
       </c>
       <c r="T30" s="10" t="n">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="U30" s="10" t="n">
         <v>2862</v>
@@ -3522,19 +3522,19 @@
         <v>578</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>8286</v>
+        <v>8292</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Y30" s="10" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="Z30" s="6" t="n">
         <v>735</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="AB30" s="7" t="n">
         <v>45</v>
@@ -3543,7 +3543,7 @@
         <v>3652</v>
       </c>
       <c r="AD30" s="4" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="AE30" s="6" t="n">
         <v>987</v>
@@ -3580,7 +3580,7 @@
         <v>7</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K31" s="5" t="n">
         <v>120</v>
@@ -3601,7 +3601,7 @@
         <v>233</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R31" s="5" t="n">
         <v>58</v>
@@ -3631,7 +3631,7 @@
         <v>5</v>
       </c>
       <c r="AA31" s="6" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB31" s="8" t="n">
         <v>4</v>
@@ -3643,7 +3643,7 @@
         <v>987</v>
       </c>
       <c r="AE31" s="4" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
     </row>
   </sheetData>
@@ -3774,10 +3774,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>2289.9</v>
+        <v>2291</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>253</v>
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>1177.1</v>
+        <v>1178.1</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -3844,13 +3844,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>419.6</v>
+        <v>420.5</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>3283.9</v>
+        <v>3290</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -3984,13 +3984,13 @@
         <v>3</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>6211.7</v>
+        <v>6220.4</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H9" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1199.9</v>
+        <v>1201.7</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -4054,13 +4054,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>924.6</v>
+        <v>925.7</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -4089,13 +4089,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>2644.9</v>
+        <v>2647.8</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -4124,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>731.8</v>
+        <v>732.2</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>622</v>
@@ -4159,10 +4159,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1336.3</v>
+        <v>1337.1</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>2074</v>
@@ -4194,13 +4194,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>722.9</v>
+        <v>723.9</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -4229,13 +4229,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>1170.7</v>
+        <v>1174.4</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
@@ -4264,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>650</v>
+        <v>651.9</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -4299,13 +4299,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>1106.7</v>
+        <v>1107.8</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -4334,13 +4334,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>2093.3</v>
+        <v>2094.5</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -4404,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>614.5</v>
+        <v>615</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1122</v>
+        <v>1122.9</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>2074</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>1</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1022.8</v>
+        <v>1025</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -4509,13 +4509,13 @@
         <v>5</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>5103.9</v>
+        <v>5106.3</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -4579,13 +4579,13 @@
         <v>4</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>6388.2</v>
+        <v>6397.6</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
         <v>8</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>6556.3</v>
+        <v>6559.4</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>2074</v>
@@ -4649,13 +4649,13 @@
         <v>2</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>1812.9</v>
+        <v>1817.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -4684,10 +4684,10 @@
         <v>3</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>3129.4</v>
+        <v>3131.4</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>2074</v>
@@ -4719,13 +4719,13 @@
         <v>2</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>1398.5</v>
+        <v>1399.1</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -4754,13 +4754,13 @@
         <v>1</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>1645.5</v>
+        <v>1646.6</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4789,13 +4789,13 @@
         <v>1</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>689.8</v>
+        <v>690.9</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -4824,13 +4824,13 @@
         <v>2</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         <v>2</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1917.8</v>
+        <v>1918.6</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4929,13 +4929,13 @@
         <v>1</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1992.9</v>
+        <v>1993.8</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -4964,13 +4964,13 @@
         <v>3</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2177.4</v>
+        <v>2180.5</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4999,13 +4999,13 @@
         <v>4</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>2770.5</v>
+        <v>2773.2</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -5034,13 +5034,13 @@
         <v>1</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>831.3</v>
+        <v>833.6</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>1792.6</v>
+        <v>1793.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>3236</v>
@@ -5104,10 +5104,10 @@
         <v>1</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>1435.1</v>
+        <v>1435.8</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>2074</v>
@@ -5139,13 +5139,13 @@
         <v>2</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>2319.5</v>
+        <v>2325.5</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -5174,13 +5174,13 @@
         <v>1</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>774.1</v>
+        <v>776.2</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -5209,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1669.2</v>
+        <v>1670.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>3236</v>
@@ -5244,10 +5244,10 @@
         <v>1</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1500.8</v>
+        <v>1504</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>3236</v>
@@ -5279,13 +5279,13 @@
         <v>4</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3139.2</v>
+        <v>3144</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -5314,13 +5314,13 @@
         <v>4</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>2796.1</v>
+        <v>2799.6</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -5349,13 +5349,13 @@
         <v>1</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1068.5</v>
+        <v>1071.1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -5384,13 +5384,13 @@
         <v>2</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3124.8</v>
+        <v>3126.3</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -5454,13 +5454,13 @@
         <v>4</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>7127.3</v>
+        <v>7130.7</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -5489,13 +5489,13 @@
         <v>11</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>4674.3</v>
+        <v>4676.2</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -5524,13 +5524,13 @@
         <v>14</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>6318.6</v>
+        <v>6320.7</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -5559,13 +5559,13 @@
         <v>14</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>6041.6</v>
+        <v>6048.2</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>4</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1873.1</v>
+        <v>1874.9</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5629,13 +5629,13 @@
         <v>1</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>466.7</v>
+        <v>467</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -5664,13 +5664,13 @@
         <v>4</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1805.2</v>
+        <v>1805.9</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -5699,13 +5699,13 @@
         <v>3</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1745</v>
+        <v>1746.4</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5734,13 +5734,13 @@
         <v>3</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1441.5</v>
+        <v>1442.1</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -5769,13 +5769,13 @@
         <v>2</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1058.8</v>
+        <v>1059.3</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -5804,13 +5804,13 @@
         <v>8</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>3921.7</v>
+        <v>3928</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
         <v>7</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>4024.9</v>
+        <v>4027.2</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>2074</v>
@@ -5874,13 +5874,13 @@
         <v>2</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1284.9</v>
+        <v>1288.5</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -5909,10 +5909,10 @@
         <v>3</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1214.7</v>
+        <v>1215.4</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>622</v>
@@ -5944,10 +5944,10 @@
         <v>5</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2218</v>
+        <v>2219.4</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>2074</v>
@@ -5979,13 +5979,13 @@
         <v>12</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>6102.1</v>
+        <v>6108.9</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -6014,13 +6014,13 @@
         <v>17</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>11015.7</v>
+        <v>11025.9</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -6049,13 +6049,13 @@
         <v>2</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1272.6</v>
+        <v>1275.4</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -6084,13 +6084,13 @@
         <v>6</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>3863</v>
+        <v>3867</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -6119,13 +6119,13 @@
         <v>10</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>4590.5</v>
+        <v>4598.1</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         <v>9</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>4711.3</v>
+        <v>4714.3</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>2074</v>
@@ -6189,10 +6189,10 @@
         <v>1</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>658</v>
+        <v>659.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>622</v>
@@ -6224,13 +6224,13 @@
         <v>8</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>3473.2</v>
+        <v>3482.3</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -6256,16 +6256,16 @@
         <v>99.8</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>3180.8</v>
+        <v>3189</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         <v>7</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>3221.9</v>
+        <v>3223.5</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>2074</v>
@@ -6329,13 +6329,13 @@
         <v>4</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1743</v>
+        <v>1745.3</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -6364,13 +6364,13 @@
         <v>12</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>5035.9</v>
+        <v>5043.2</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         <v>8</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>5168.5</v>
+        <v>5170.7</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>2074</v>
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1924.5</v>
+        <v>1929.5</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -6469,10 +6469,10 @@
         <v>3</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1975.1</v>
+        <v>1978.3</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>2074</v>
@@ -6504,13 +6504,13 @@
         <v>5</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2702.8</v>
+        <v>2707.3</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -6539,13 +6539,13 @@
         <v>10</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>5350.1</v>
+        <v>5357.7</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -6574,13 +6574,13 @@
         <v>24</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>15106.4</v>
+        <v>15119.8</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -6609,13 +6609,13 @@
         <v>3</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1401.5</v>
+        <v>1402.7</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -6644,13 +6644,13 @@
         <v>6</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2953.7</v>
+        <v>2958.1</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -6679,13 +6679,13 @@
         <v>5</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>3031.5</v>
+        <v>3032.9</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>2074</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -6714,13 +6714,13 @@
         <v>4</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1640</v>
+        <v>1642.1</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -6749,13 +6749,13 @@
         <v>14</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>4253.1</v>
+        <v>4256.6</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -6784,13 +6784,13 @@
         <v>13</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>4857.4</v>
+        <v>4859.7</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -6819,13 +6819,13 @@
         <v>37</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>12083.7</v>
+        <v>12096.1</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -6854,13 +6854,13 @@
         <v>8</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>2592.4</v>
+        <v>2593.3</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -6889,13 +6889,13 @@
         <v>1</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>391.9</v>
+        <v>392.2</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -6924,13 +6924,13 @@
         <v>11</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>4087.9</v>
+        <v>4092.8</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         <v>2</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>785.9</v>
+        <v>786.3</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H94" s="12" t="n">
         <v>622</v>
@@ -6994,13 +6994,13 @@
         <v>17</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>5135.9</v>
+        <v>5140.2</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -7029,13 +7029,13 @@
         <v>4</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1398.3</v>
+        <v>1400.4</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -7064,13 +7064,13 @@
         <v>8</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>2855.8</v>
+        <v>2858.4</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H97" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -7099,13 +7099,13 @@
         <v>7</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>2097.6</v>
+        <v>2099.6</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -7134,10 +7134,10 @@
         <v>12</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>4004</v>
+        <v>4005.8</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H99" s="12" t="n">
         <v>2074</v>
@@ -7169,13 +7169,13 @@
         <v>8</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>3035.5</v>
+        <v>3039.3</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -7204,13 +7204,13 @@
         <v>7</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>2075.9</v>
+        <v>2078.1</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -7239,13 +7239,13 @@
         <v>11</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>3537.8</v>
+        <v>3541.4</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -7274,13 +7274,13 @@
         <v>15</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>5938</v>
+        <v>5944.4</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -7309,13 +7309,13 @@
         <v>15</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>5841.8</v>
+        <v>5850.4</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -7344,13 +7344,13 @@
         <v>9</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>3243.5</v>
+        <v>3247.7</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H105" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -7379,13 +7379,13 @@
         <v>49</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>16494.8</v>
+        <v>16510.3</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -7414,10 +7414,10 @@
         <v>15</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>5490.9</v>
+        <v>5493.1</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H107" s="12" t="n">
         <v>2074</v>
@@ -7449,13 +7449,13 @@
         <v>8</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>2970.5</v>
+        <v>2974.2</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -7484,13 +7484,13 @@
         <v>14</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>5559.6</v>
+        <v>5567.9</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H109" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -7519,13 +7519,13 @@
         <v>10</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>3086.9</v>
+        <v>3090.9</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -7554,13 +7554,13 @@
         <v>15</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>3408.5</v>
+        <v>3410.1</v>
       </c>
       <c r="G111" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -7624,13 +7624,13 @@
         <v>4</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>955.2</v>
+        <v>955.9</v>
       </c>
       <c r="G113" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -7659,13 +7659,13 @@
         <v>13</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>3546.9</v>
+        <v>3551.5</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -7694,13 +7694,13 @@
         <v>34</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>9046.6</v>
+        <v>9056.6</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -7729,10 +7729,10 @@
         <v>17</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>3909</v>
+        <v>3911.5</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H116" s="12" t="n">
         <v>3236</v>
@@ -7764,13 +7764,13 @@
         <v>31</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>8609.6</v>
+        <v>8619.200000000001</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -7799,13 +7799,13 @@
         <v>6</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1405.8</v>
+        <v>1406.6</v>
       </c>
       <c r="G118" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         <v>23</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>6506.7</v>
+        <v>6515</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         <v>14</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>3370.4</v>
+        <v>3373.1</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H120" s="12" t="n">
         <v>2074</v>
@@ -7904,13 +7904,13 @@
         <v>26</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>7418.1</v>
+        <v>7426.6</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H121" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -7939,13 +7939,13 @@
         <v>15</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3710.9</v>
+        <v>3716.4</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -7974,13 +7974,13 @@
         <v>16</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>3901.3</v>
+        <v>3907.1</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -8009,13 +8009,13 @@
         <v>9</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>2548.7</v>
+        <v>2552.5</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -8044,13 +8044,13 @@
         <v>14</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>3283.4</v>
+        <v>3284.9</v>
       </c>
       <c r="G125" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -8079,13 +8079,13 @@
         <v>9</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>2524.2</v>
+        <v>2526.8</v>
       </c>
       <c r="G126" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -8114,13 +8114,13 @@
         <v>18</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>4774.7</v>
+        <v>4777.4</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -8149,13 +8149,13 @@
         <v>26</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>7232</v>
+        <v>7241.8</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>4</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>1093.2</v>
+        <v>1095.3</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -8219,13 +8219,13 @@
         <v>21</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>4010.6</v>
+        <v>4013.2</v>
       </c>
       <c r="G130" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -8254,13 +8254,13 @@
         <v>87</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>18953.2</v>
+        <v>18970.6</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H131" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -8289,13 +8289,13 @@
         <v>10</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>2016.3</v>
+        <v>2018.8</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -8324,13 +8324,13 @@
         <v>42</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>8285.200000000001</v>
+        <v>8293.799999999999</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H133" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -8359,13 +8359,13 @@
         <v>22</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>4574.2</v>
+        <v>4579.2</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -8394,13 +8394,13 @@
         <v>6</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>1125.3</v>
+        <v>1125.8</v>
       </c>
       <c r="G135" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H135" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -8429,13 +8429,13 @@
         <v>11</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>2161.1</v>
+        <v>2164.7</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -8464,13 +8464,13 @@
         <v>17</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>3457</v>
+        <v>3461.6</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H137" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
@@ -8499,13 +8499,13 @@
         <v>21</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>4148.6</v>
+        <v>4152.6</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -8534,13 +8534,13 @@
         <v>4</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>776.4</v>
+        <v>777.4</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H139" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -8566,16 +8566,16 @@
         <v>99.5</v>
       </c>
       <c r="E140" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>3106.8</v>
+        <v>3116.5</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H140" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         <v>35</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>6699</v>
+        <v>6705.5</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H141" s="12" t="n">
         <v>3236</v>
@@ -8639,13 +8639,13 @@
         <v>70</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>14754.7</v>
+        <v>14776.1</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -8674,13 +8674,13 @@
         <v>13</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>2579.8</v>
+        <v>2582.5</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H143" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -8709,10 +8709,10 @@
         <v>23</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>5001.4</v>
+        <v>5003.7</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H144" s="12" t="n">
         <v>3236</v>
@@ -8744,13 +8744,13 @@
         <v>22</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>4782.3</v>
+        <v>4786.7</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H145" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -8779,10 +8779,10 @@
         <v>14</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>2580</v>
+        <v>2581.7</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H146" s="12" t="n">
         <v>622</v>
@@ -8814,10 +8814,10 @@
         <v>6</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>1201.5</v>
+        <v>1204</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H147" s="12" t="n">
         <v>2074</v>
@@ -8849,10 +8849,10 @@
         <v>12</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>2467.2</v>
+        <v>2471.1</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H148" s="12" t="n">
         <v>3236</v>
@@ -8884,13 +8884,13 @@
         <v>19</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>3640.3</v>
+        <v>3648.2</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H149" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -8919,13 +8919,13 @@
         <v>11</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>2260.2</v>
+        <v>2261.2</v>
       </c>
       <c r="G150" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -8954,13 +8954,13 @@
         <v>38</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>8340.1</v>
+        <v>8347.9</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="H151" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -8989,10 +8989,10 @@
         <v>46</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>8189.6</v>
+        <v>8193.299999999999</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H152" s="12" t="n">
         <v>3236</v>
@@ -9024,13 +9024,13 @@
         <v>11</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>1823.3</v>
+        <v>1826.3</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H153" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -9059,13 +9059,13 @@
         <v>9</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>1429.1</v>
+        <v>1430.8</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -9094,13 +9094,13 @@
         <v>13</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>2229.3</v>
+        <v>2231.6</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H155" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -9129,13 +9129,13 @@
         <v>24</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>3799.4</v>
+        <v>3802.9</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -9164,13 +9164,13 @@
         <v>22</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>3948.2</v>
+        <v>3952.1</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H157" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -9199,13 +9199,13 @@
         <v>29</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>5225.5</v>
+        <v>5235.9</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -9234,13 +9234,13 @@
         <v>16</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>2901.4</v>
+        <v>2906.6</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H159" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -9269,13 +9269,13 @@
         <v>12</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2166.1</v>
+        <v>2168.9</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -9304,10 +9304,10 @@
         <v>38</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>5884.9</v>
+        <v>5888.7</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H161" s="12" t="n">
         <v>3236</v>
@@ -9339,10 +9339,10 @@
         <v>18</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>2830.4</v>
+        <v>2831.6</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H162" s="12" t="n">
         <v>622</v>
@@ -9409,13 +9409,13 @@
         <v>10</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>1660.1</v>
+        <v>1660.9</v>
       </c>
       <c r="G164" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -9444,13 +9444,13 @@
         <v>65</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>10119.9</v>
+        <v>10129.9</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H165" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -9479,13 +9479,13 @@
         <v>24</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>4015.4</v>
+        <v>4020.1</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
         <v>12</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>2020.8</v>
+        <v>2022.9</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H167" s="12" t="n">
         <v>2074</v>
@@ -9549,13 +9549,13 @@
         <v>45</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>7069.8</v>
+        <v>7078.6</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -9584,13 +9584,13 @@
         <v>8</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>1137.6</v>
+        <v>1138.2</v>
       </c>
       <c r="G169" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H169" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -9619,13 +9619,13 @@
         <v>30</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>4399.8</v>
+        <v>4401.7</v>
       </c>
       <c r="G170" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -9654,13 +9654,13 @@
         <v>23</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>3254</v>
+        <v>3255.9</v>
       </c>
       <c r="G171" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H171" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -9689,13 +9689,13 @@
         <v>72</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>9892.799999999999</v>
+        <v>9903.700000000001</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="I172" s="13" t="inlineStr">
         <is>
@@ -9724,13 +9724,13 @@
         <v>30</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>4536.6</v>
+        <v>4541</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H173" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -9759,13 +9759,13 @@
         <v>58</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>8092.3</v>
+        <v>8105.3</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -9791,16 +9791,16 @@
         <v>99.3</v>
       </c>
       <c r="E175" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F175" s="12" t="n">
-        <v>8715.200000000001</v>
+        <v>8730.9</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H175" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I175" s="13" t="inlineStr">
         <is>
@@ -9829,13 +9829,13 @@
         <v>17</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>2593.3</v>
+        <v>2596.3</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -9861,16 +9861,16 @@
         <v>99.3</v>
       </c>
       <c r="E177" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F177" s="12" t="n">
-        <v>4282</v>
+        <v>4286.7</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H177" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -9899,10 +9899,10 @@
         <v>20</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>2770.5</v>
+        <v>2772.3</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H178" s="12" t="n">
         <v>3236</v>
@@ -9934,13 +9934,13 @@
         <v>82</v>
       </c>
       <c r="F179" s="12" t="n">
-        <v>11574.8</v>
+        <v>11585.4</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H179" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I179" s="13" t="inlineStr">
         <is>
@@ -9969,13 +9969,13 @@
         <v>23</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>3219</v>
+        <v>3223.6</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I180" s="13" t="inlineStr">
         <is>
@@ -10004,13 +10004,13 @@
         <v>14</v>
       </c>
       <c r="F181" s="12" t="n">
-        <v>1953.2</v>
+        <v>1955.2</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H181" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -10024,28 +10024,28 @@
       </c>
       <c r="B182" s="12" t="inlineStr">
         <is>
-          <t>Metabolomics</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="C182" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="D182" s="12" t="n">
         <v>99.3</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>9525.700000000001</v>
+        <v>1871.4</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>12880</v>
+        <v>699</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>7045</v>
+        <v>5010</v>
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
@@ -10059,28 +10059,28 @@
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Metabolomics</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D183" s="12" t="n">
         <v>99.3</v>
       </c>
       <c r="E183" s="12" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F183" s="12" t="n">
-        <v>3007</v>
+        <v>9535.200000000001</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>622</v>
+        <v>12891</v>
       </c>
       <c r="H183" s="12" t="n">
-        <v>14537</v>
+        <v>7053</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -10094,28 +10094,28 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>Retinopathy</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D184" s="12" t="n">
         <v>99.3</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>8763.5</v>
+        <v>3008.2</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>17332</v>
+        <v>622</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>4431</v>
+        <v>14549</v>
       </c>
       <c r="I184" s="13" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>Neuropathy</t>
+          <t>Retinopathy</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
@@ -10141,16 +10141,16 @@
         <v>99.3</v>
       </c>
       <c r="E185" s="12" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F185" s="12" t="n">
-        <v>3786.6</v>
+        <v>8771.5</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>3236</v>
+        <v>17348</v>
       </c>
       <c r="H185" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -10164,28 +10164,28 @@
       </c>
       <c r="B186" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Neuropathy</t>
         </is>
       </c>
       <c r="C186" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D186" s="12" t="n">
         <v>99.3</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>7422.4</v>
+        <v>3788.4</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>26563</v>
+        <v>3236</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>2074</v>
+        <v>4435</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -10199,28 +10199,28 @@
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>Beta Cell Regen</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D187" s="12" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="E187" s="12" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F187" s="12" t="n">
-        <v>1681.4</v>
+        <v>7424.9</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>1503</v>
+        <v>26581</v>
       </c>
       <c r="H187" s="12" t="n">
-        <v>1881</v>
+        <v>2074</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -10234,28 +10234,28 @@
       </c>
       <c r="B188" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Beta Cell Regen</t>
         </is>
       </c>
       <c r="C188" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D188" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E188" s="12" t="n">
-        <v>128</v>
+        <v>14</v>
       </c>
       <c r="F188" s="12" t="n">
-        <v>15793.6</v>
+        <v>1684.1</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>20726</v>
+        <v>1503</v>
       </c>
       <c r="H188" s="12" t="n">
-        <v>12035</v>
+        <v>1887</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -10269,28 +10269,28 @@
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Autoimmunity T1D</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D189" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E189" s="12" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F189" s="12" t="n">
-        <v>1713.8</v>
+        <v>15813.9</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>4722</v>
+        <v>20745</v>
       </c>
       <c r="H189" s="12" t="n">
-        <v>622</v>
+        <v>12055</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -10309,23 +10309,23 @@
       </c>
       <c r="C190" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D190" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E190" s="12" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="F190" s="12" t="n">
-        <v>11199.6</v>
+        <v>1714.9</v>
       </c>
       <c r="G190" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H190" s="12" t="n">
-        <v>26563</v>
+        <v>622</v>
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
@@ -10339,28 +10339,28 @@
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>Gene Therapy</t>
+          <t>Autoimmunity T1D</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="D191" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E191" s="12" t="n">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="F191" s="12" t="n">
-        <v>3242</v>
+        <v>11210.5</v>
       </c>
       <c r="G191" s="12" t="n">
-        <v>2372</v>
+        <v>4728</v>
       </c>
       <c r="H191" s="12" t="n">
-        <v>4431</v>
+        <v>26581</v>
       </c>
       <c r="I191" s="13" t="inlineStr">
         <is>
@@ -10374,28 +10374,28 @@
       </c>
       <c r="B192" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Gene Therapy</t>
         </is>
       </c>
       <c r="C192" s="12" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D192" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E192" s="12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F192" s="12" t="n">
-        <v>6220</v>
+        <v>3245.5</v>
       </c>
       <c r="G192" s="12" t="n">
-        <v>7730</v>
+        <v>2375</v>
       </c>
       <c r="H192" s="12" t="n">
-        <v>5005</v>
+        <v>4435</v>
       </c>
       <c r="I192" s="13" t="inlineStr">
         <is>
@@ -10414,23 +10414,23 @@
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="D193" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E193" s="12" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F193" s="12" t="n">
-        <v>9645.200000000001</v>
+        <v>6225.9</v>
       </c>
       <c r="G193" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H193" s="12" t="n">
-        <v>12035</v>
+        <v>5010</v>
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
@@ -10444,28 +10444,28 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t>Microbiome Gut</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D194" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E194" s="12" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F194" s="12" t="n">
-        <v>8683.1</v>
+        <v>9657.6</v>
       </c>
       <c r="G194" s="12" t="n">
-        <v>10702</v>
+        <v>7737</v>
       </c>
       <c r="H194" s="12" t="n">
-        <v>7045</v>
+        <v>12055</v>
       </c>
       <c r="I194" s="13" t="inlineStr">
         <is>
@@ -10479,28 +10479,28 @@
       </c>
       <c r="B195" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Microbiome Gut</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D195" s="12" t="n">
         <v>99.2</v>
       </c>
       <c r="E195" s="12" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F195" s="12" t="n">
-        <v>1866.4</v>
+        <v>8693.700000000001</v>
       </c>
       <c r="G195" s="12" t="n">
-        <v>696</v>
+        <v>10716</v>
       </c>
       <c r="H195" s="12" t="n">
-        <v>5005</v>
+        <v>7053</v>
       </c>
       <c r="I195" s="13" t="inlineStr">
         <is>
@@ -10529,13 +10529,13 @@
         <v>20</v>
       </c>
       <c r="F196" s="12" t="n">
-        <v>2390.9</v>
+        <v>2397</v>
       </c>
       <c r="G196" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H196" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I196" s="13" t="inlineStr">
         <is>
@@ -10564,13 +10564,13 @@
         <v>25</v>
       </c>
       <c r="F197" s="12" t="n">
-        <v>3305.4</v>
+        <v>3314.1</v>
       </c>
       <c r="G197" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H197" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I197" s="13" t="inlineStr">
         <is>
@@ -10599,10 +10599,10 @@
         <v>33</v>
       </c>
       <c r="F198" s="12" t="n">
-        <v>4024.4</v>
+        <v>4026.5</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H198" s="12" t="n">
         <v>3236</v>
@@ -10634,13 +10634,13 @@
         <v>58</v>
       </c>
       <c r="F199" s="12" t="n">
-        <v>7302.5</v>
+        <v>7311.9</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H199" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I199" s="13" t="inlineStr">
         <is>
@@ -10669,13 +10669,13 @@
         <v>31</v>
       </c>
       <c r="F200" s="12" t="n">
-        <v>4064.7</v>
+        <v>4066.1</v>
       </c>
       <c r="G200" s="12" t="n">
         <v>622</v>
       </c>
       <c r="H200" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I200" s="13" t="inlineStr">
         <is>
@@ -10704,13 +10704,13 @@
         <v>91</v>
       </c>
       <c r="F201" s="12" t="n">
-        <v>11050.1</v>
+        <v>11061.4</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H201" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I201" s="13" t="inlineStr">
         <is>
@@ -10739,10 +10739,10 @@
         <v>45</v>
       </c>
       <c r="F202" s="12" t="n">
-        <v>5995.5</v>
+        <v>5998.3</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H202" s="12" t="n">
         <v>2074</v>
@@ -10774,13 +10774,13 @@
         <v>42</v>
       </c>
       <c r="F203" s="12" t="n">
-        <v>5155.3</v>
+        <v>5157.5</v>
       </c>
       <c r="G203" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H203" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I203" s="13" t="inlineStr">
         <is>
@@ -10809,13 +10809,13 @@
         <v>32</v>
       </c>
       <c r="F204" s="12" t="n">
-        <v>4021.4</v>
+        <v>4027.2</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H204" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I204" s="13" t="inlineStr">
         <is>
@@ -10844,13 +10844,13 @@
         <v>27</v>
       </c>
       <c r="F205" s="12" t="n">
-        <v>2869.1</v>
+        <v>2871.5</v>
       </c>
       <c r="G205" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H205" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="I205" s="13" t="inlineStr">
         <is>
@@ -10879,13 +10879,13 @@
         <v>12</v>
       </c>
       <c r="F206" s="12" t="n">
-        <v>1335.1</v>
+        <v>1335.8</v>
       </c>
       <c r="G206" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H206" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I206" s="13" t="inlineStr">
         <is>
@@ -10914,13 +10914,13 @@
         <v>39</v>
       </c>
       <c r="F207" s="12" t="n">
-        <v>4564.3</v>
+        <v>4566.2</v>
       </c>
       <c r="G207" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H207" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I207" s="13" t="inlineStr">
         <is>
@@ -10949,10 +10949,10 @@
         <v>48</v>
       </c>
       <c r="F208" s="12" t="n">
-        <v>5363</v>
+        <v>5368.3</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H208" s="12" t="n">
         <v>2074</v>
@@ -10984,13 +10984,13 @@
         <v>31</v>
       </c>
       <c r="F209" s="12" t="n">
-        <v>3330.1</v>
+        <v>3333.5</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H209" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I209" s="13" t="inlineStr">
         <is>
@@ -11019,13 +11019,13 @@
         <v>33</v>
       </c>
       <c r="F210" s="12" t="n">
-        <v>3676.4</v>
+        <v>3680.3</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H210" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I210" s="13" t="inlineStr">
         <is>
@@ -11054,13 +11054,13 @@
         <v>18</v>
       </c>
       <c r="F211" s="12" t="n">
-        <v>2067.9</v>
+        <v>2070.8</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="H211" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I211" s="13" t="inlineStr">
         <is>
@@ -11089,13 +11089,13 @@
         <v>51</v>
       </c>
       <c r="F212" s="12" t="n">
-        <v>5587.2</v>
+        <v>5592.9</v>
       </c>
       <c r="G212" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="H212" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I212" s="13" t="inlineStr">
         <is>
@@ -11124,13 +11124,13 @@
         <v>36</v>
       </c>
       <c r="F213" s="12" t="n">
-        <v>3513.4</v>
+        <v>3514.9</v>
       </c>
       <c r="G213" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H213" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I213" s="13" t="inlineStr">
         <is>
@@ -11159,13 +11159,13 @@
         <v>72</v>
       </c>
       <c r="F214" s="12" t="n">
-        <v>7538.5</v>
+        <v>7549.6</v>
       </c>
       <c r="G214" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H214" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I214" s="13" t="inlineStr">
         <is>
@@ -11194,13 +11194,13 @@
         <v>8</v>
       </c>
       <c r="F215" s="12" t="n">
-        <v>774.7</v>
+        <v>775.2</v>
       </c>
       <c r="G215" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H215" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I215" s="13" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         <v>51</v>
       </c>
       <c r="F216" s="12" t="n">
-        <v>5038.4</v>
+        <v>5044.8</v>
       </c>
       <c r="G216" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H216" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I216" s="13" t="inlineStr">
         <is>
@@ -11264,13 +11264,13 @@
         <v>51</v>
       </c>
       <c r="F217" s="12" t="n">
-        <v>5342.9</v>
+        <v>5350.8</v>
       </c>
       <c r="G217" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H217" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I217" s="13" t="inlineStr">
         <is>
@@ -11299,13 +11299,13 @@
         <v>43</v>
       </c>
       <c r="F218" s="12" t="n">
-        <v>4413.8</v>
+        <v>4418.4</v>
       </c>
       <c r="G218" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H218" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I218" s="13" t="inlineStr">
         <is>
@@ -11334,13 +11334,13 @@
         <v>34</v>
       </c>
       <c r="F219" s="12" t="n">
-        <v>3455.5</v>
+        <v>3460.9</v>
       </c>
       <c r="G219" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H219" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I219" s="13" t="inlineStr">
         <is>
@@ -11369,13 +11369,13 @@
         <v>91</v>
       </c>
       <c r="F220" s="12" t="n">
-        <v>9095.4</v>
+        <v>9105.5</v>
       </c>
       <c r="G220" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H220" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I220" s="13" t="inlineStr">
         <is>
@@ -11404,13 +11404,13 @@
         <v>141</v>
       </c>
       <c r="F221" s="12" t="n">
-        <v>13619.4</v>
+        <v>13634.6</v>
       </c>
       <c r="G221" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H221" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I221" s="13" t="inlineStr">
         <is>
@@ -11439,13 +11439,13 @@
         <v>42</v>
       </c>
       <c r="F222" s="12" t="n">
-        <v>4299.7</v>
+        <v>4310.5</v>
       </c>
       <c r="G222" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H222" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I222" s="13" t="inlineStr">
         <is>
@@ -11474,13 +11474,13 @@
         <v>17</v>
       </c>
       <c r="F223" s="12" t="n">
-        <v>1756.1</v>
+        <v>1760.7</v>
       </c>
       <c r="G223" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H223" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I223" s="13" t="inlineStr">
         <is>
@@ -11494,28 +11494,28 @@
       </c>
       <c r="B224" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C224" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D224" s="12" t="n">
-        <v>99</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E224" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F224" s="12" t="n">
-        <v>2887</v>
+        <v>3592.1</v>
       </c>
       <c r="G224" s="12" t="n">
-        <v>1881</v>
+        <v>20745</v>
       </c>
       <c r="H224" s="12" t="n">
-        <v>4431</v>
+        <v>622</v>
       </c>
       <c r="I224" s="13" t="inlineStr">
         <is>
@@ -11529,28 +11529,28 @@
       </c>
       <c r="B225" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Islet Transplant</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Closed Loop / AP</t>
         </is>
       </c>
       <c r="D225" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E225" s="12" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F225" s="12" t="n">
-        <v>3590.5</v>
+        <v>706.5</v>
       </c>
       <c r="G225" s="12" t="n">
-        <v>20726</v>
+        <v>253</v>
       </c>
       <c r="H225" s="12" t="n">
-        <v>622</v>
+        <v>1973</v>
       </c>
       <c r="I225" s="13" t="inlineStr">
         <is>
@@ -11564,28 +11564,28 @@
       </c>
       <c r="B226" s="12" t="inlineStr">
         <is>
-          <t>Islet Transplant</t>
+          <t>GWAS / Polygenic</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>Closed Loop / AP</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="D226" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E226" s="12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F226" s="12" t="n">
-        <v>705.8</v>
+        <v>2335.2</v>
       </c>
       <c r="G226" s="12" t="n">
-        <v>253</v>
+        <v>5486</v>
       </c>
       <c r="H226" s="12" t="n">
-        <v>1969</v>
+        <v>994</v>
       </c>
       <c r="I226" s="13" t="inlineStr">
         <is>
@@ -11604,23 +11604,23 @@
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>Glucokinase</t>
         </is>
       </c>
       <c r="D227" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E227" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F227" s="12" t="n">
-        <v>2332.1</v>
+        <v>2174.6</v>
       </c>
       <c r="G227" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H227" s="12" t="n">
-        <v>993</v>
+        <v>862</v>
       </c>
       <c r="I227" s="13" t="inlineStr">
         <is>
@@ -11639,23 +11639,23 @@
       </c>
       <c r="C228" s="12" t="inlineStr">
         <is>
-          <t>Glucokinase</t>
+          <t>Neuropathy</t>
         </is>
       </c>
       <c r="D228" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E228" s="12" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F228" s="12" t="n">
-        <v>2171.6</v>
+        <v>4213.4</v>
       </c>
       <c r="G228" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H228" s="12" t="n">
-        <v>861</v>
+        <v>3236</v>
       </c>
       <c r="I228" s="13" t="inlineStr">
         <is>
@@ -11669,28 +11669,28 @@
       </c>
       <c r="B229" s="12" t="inlineStr">
         <is>
-          <t>GWAS / Polygenic</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Neuropathy</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D229" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E229" s="12" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F229" s="12" t="n">
-        <v>4209.9</v>
+        <v>2205.5</v>
       </c>
       <c r="G229" s="12" t="n">
-        <v>5477</v>
+        <v>7820</v>
       </c>
       <c r="H229" s="12" t="n">
-        <v>3236</v>
+        <v>622</v>
       </c>
       <c r="I229" s="13" t="inlineStr">
         <is>
@@ -11704,28 +11704,28 @@
       </c>
       <c r="B230" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D230" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E230" s="12" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F230" s="12" t="n">
-        <v>2204.2</v>
+        <v>5120.5</v>
       </c>
       <c r="G230" s="12" t="n">
-        <v>7811</v>
+        <v>13895</v>
       </c>
       <c r="H230" s="12" t="n">
-        <v>622</v>
+        <v>1887</v>
       </c>
       <c r="I230" s="13" t="inlineStr">
         <is>
@@ -11739,28 +11739,28 @@
       </c>
       <c r="B231" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D231" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E231" s="12" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="F231" s="12" t="n">
-        <v>5107.4</v>
+        <v>7387.1</v>
       </c>
       <c r="G231" s="12" t="n">
-        <v>13868</v>
+        <v>7737</v>
       </c>
       <c r="H231" s="12" t="n">
-        <v>1881</v>
+        <v>7053</v>
       </c>
       <c r="I231" s="13" t="inlineStr">
         <is>
@@ -11774,28 +11774,28 @@
       </c>
       <c r="B232" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="C232" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D232" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
       <c r="E232" s="12" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="F232" s="12" t="n">
-        <v>7379.6</v>
+        <v>2892.9</v>
       </c>
       <c r="G232" s="12" t="n">
-        <v>7730</v>
+        <v>1887</v>
       </c>
       <c r="H232" s="12" t="n">
-        <v>7045</v>
+        <v>4435</v>
       </c>
       <c r="I232" s="13" t="inlineStr">
         <is>
@@ -11824,10 +11824,10 @@
         <v>69</v>
       </c>
       <c r="F233" s="12" t="n">
-        <v>6240.6</v>
+        <v>6245.8</v>
       </c>
       <c r="G233" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H233" s="12" t="n">
         <v>3236</v>
@@ -11859,13 +11859,13 @@
         <v>32</v>
       </c>
       <c r="F234" s="12" t="n">
-        <v>2580.7</v>
+        <v>2581.8</v>
       </c>
       <c r="G234" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H234" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I234" s="13" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>37</v>
       </c>
       <c r="F235" s="12" t="n">
-        <v>3049.2</v>
+        <v>3054.2</v>
       </c>
       <c r="G235" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H235" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I235" s="13" t="inlineStr">
         <is>
@@ -11926,16 +11926,16 @@
         <v>98.8</v>
       </c>
       <c r="E236" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F236" s="12" t="n">
-        <v>5735.4</v>
+        <v>5744.6</v>
       </c>
       <c r="G236" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H236" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I236" s="13" t="inlineStr">
         <is>
@@ -11964,13 +11964,13 @@
         <v>71</v>
       </c>
       <c r="F237" s="12" t="n">
-        <v>5872.1</v>
+        <v>5878.3</v>
       </c>
       <c r="G237" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H237" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I237" s="13" t="inlineStr">
         <is>
@@ -11999,13 +11999,13 @@
         <v>92</v>
       </c>
       <c r="F238" s="12" t="n">
-        <v>7937.7</v>
+        <v>7945.4</v>
       </c>
       <c r="G238" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H238" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I238" s="13" t="inlineStr">
         <is>
@@ -12031,16 +12031,16 @@
         <v>98.8</v>
       </c>
       <c r="E239" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F239" s="12" t="n">
-        <v>3813.2</v>
+        <v>3821</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H239" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I239" s="13" t="inlineStr">
         <is>
@@ -12069,13 +12069,13 @@
         <v>88</v>
       </c>
       <c r="F240" s="12" t="n">
-        <v>7068.6</v>
+        <v>7082.3</v>
       </c>
       <c r="G240" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H240" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I240" s="13" t="inlineStr">
         <is>
@@ -12104,13 +12104,13 @@
         <v>75</v>
       </c>
       <c r="F241" s="12" t="n">
-        <v>5581.3</v>
+        <v>5583.9</v>
       </c>
       <c r="G241" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H241" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="I241" s="13" t="inlineStr">
         <is>
@@ -12139,13 +12139,13 @@
         <v>53</v>
       </c>
       <c r="F242" s="12" t="n">
-        <v>4224.3</v>
+        <v>4228.7</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H242" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="I242" s="13" t="inlineStr">
         <is>
@@ -12174,13 +12174,13 @@
         <v>51</v>
       </c>
       <c r="F243" s="12" t="n">
-        <v>3798.1</v>
+        <v>3808</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H243" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I243" s="13" t="inlineStr">
         <is>
@@ -12209,13 +12209,13 @@
         <v>25</v>
       </c>
       <c r="F244" s="12" t="n">
-        <v>1952.4</v>
+        <v>1958.2</v>
       </c>
       <c r="G244" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H244" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I244" s="13" t="inlineStr">
         <is>
@@ -12244,13 +12244,13 @@
         <v>111</v>
       </c>
       <c r="F245" s="12" t="n">
-        <v>8331.200000000001</v>
+        <v>8343.5</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H245" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I245" s="13" t="inlineStr">
         <is>
@@ -12276,16 +12276,16 @@
         <v>98.7</v>
       </c>
       <c r="E246" s="12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F246" s="12" t="n">
-        <v>12919</v>
+        <v>12942.3</v>
       </c>
       <c r="G246" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H246" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I246" s="13" t="inlineStr">
         <is>
@@ -12314,13 +12314,13 @@
         <v>116</v>
       </c>
       <c r="F247" s="12" t="n">
-        <v>8863.9</v>
+        <v>8872.5</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H247" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I247" s="13" t="inlineStr">
         <is>
@@ -12349,10 +12349,10 @@
         <v>81</v>
       </c>
       <c r="F248" s="12" t="n">
-        <v>6456</v>
+        <v>6458.7</v>
       </c>
       <c r="G248" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H248" s="12" t="n">
         <v>3236</v>
@@ -12384,13 +12384,13 @@
         <v>72</v>
       </c>
       <c r="F249" s="12" t="n">
-        <v>5434</v>
+        <v>5445.2</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H249" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I249" s="13" t="inlineStr">
         <is>
@@ -12419,13 +12419,13 @@
         <v>74</v>
       </c>
       <c r="F250" s="12" t="n">
-        <v>5705.9</v>
+        <v>5708.7</v>
       </c>
       <c r="G250" s="12" t="n">
         <v>2074</v>
       </c>
       <c r="H250" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I250" s="13" t="inlineStr">
         <is>
@@ -12454,13 +12454,13 @@
         <v>30</v>
       </c>
       <c r="F251" s="12" t="n">
-        <v>2232.8</v>
+        <v>2235.6</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="H251" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I251" s="13" t="inlineStr">
         <is>
@@ -12489,13 +12489,13 @@
         <v>7</v>
       </c>
       <c r="F252" s="12" t="n">
-        <v>501.2</v>
+        <v>501.5</v>
       </c>
       <c r="G252" s="12" t="n">
         <v>253</v>
       </c>
       <c r="H252" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I252" s="13" t="inlineStr">
         <is>
@@ -12521,16 +12521,16 @@
         <v>98.59999999999999</v>
       </c>
       <c r="E253" s="12" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F253" s="12" t="n">
-        <v>10407.8</v>
+        <v>10424</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H253" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I253" s="13" t="inlineStr">
         <is>
@@ -12559,13 +12559,13 @@
         <v>213</v>
       </c>
       <c r="F254" s="12" t="n">
-        <v>15503.6</v>
+        <v>15525.8</v>
       </c>
       <c r="G254" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H254" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
@@ -12594,13 +12594,13 @@
         <v>116</v>
       </c>
       <c r="F255" s="12" t="n">
-        <v>8420.1</v>
+        <v>8428.4</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H255" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I255" s="13" t="inlineStr">
         <is>
@@ -12629,10 +12629,10 @@
         <v>25</v>
       </c>
       <c r="F256" s="12" t="n">
-        <v>1764.4</v>
+        <v>1765.3</v>
       </c>
       <c r="G256" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H256" s="12" t="n">
         <v>622</v>
@@ -12664,13 +12664,13 @@
         <v>78</v>
       </c>
       <c r="F257" s="12" t="n">
-        <v>5709.8</v>
+        <v>5721.5</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H257" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I257" s="13" t="inlineStr">
         <is>
@@ -12699,13 +12699,13 @@
         <v>56</v>
       </c>
       <c r="F258" s="12" t="n">
-        <v>3930.5</v>
+        <v>3938.4</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H258" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I258" s="13" t="inlineStr">
         <is>
@@ -12734,13 +12734,13 @@
         <v>169</v>
       </c>
       <c r="F259" s="12" t="n">
-        <v>11931</v>
+        <v>11941.5</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H259" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I259" s="13" t="inlineStr">
         <is>
@@ -12769,13 +12769,13 @@
         <v>105</v>
       </c>
       <c r="F260" s="12" t="n">
-        <v>7011.6</v>
+        <v>7019.2</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H260" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I260" s="13" t="inlineStr">
         <is>
@@ -12804,13 +12804,13 @@
         <v>97</v>
       </c>
       <c r="F261" s="12" t="n">
-        <v>6411.4</v>
+        <v>6417.3</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H261" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
@@ -12839,13 +12839,13 @@
         <v>27</v>
       </c>
       <c r="F262" s="12" t="n">
-        <v>1720.3</v>
+        <v>1722</v>
       </c>
       <c r="G262" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H262" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I262" s="13" t="inlineStr">
         <is>
@@ -12874,13 +12874,13 @@
         <v>49</v>
       </c>
       <c r="F263" s="12" t="n">
-        <v>2980.3</v>
+        <v>2986.9</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H263" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I263" s="13" t="inlineStr">
         <is>
@@ -12909,13 +12909,13 @@
         <v>92</v>
       </c>
       <c r="F264" s="12" t="n">
-        <v>5767.7</v>
+        <v>5774.7</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H264" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I264" s="13" t="inlineStr">
         <is>
@@ -12944,10 +12944,10 @@
         <v>79</v>
       </c>
       <c r="F265" s="12" t="n">
-        <v>5027.6</v>
+        <v>5030.5</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H265" s="12" t="n">
         <v>3236</v>
@@ -12979,13 +12979,13 @@
         <v>56</v>
       </c>
       <c r="F266" s="12" t="n">
-        <v>3576.3</v>
+        <v>3579.6</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H266" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I266" s="13" t="inlineStr">
         <is>
@@ -13014,10 +13014,10 @@
         <v>80</v>
       </c>
       <c r="F267" s="12" t="n">
-        <v>4996.1</v>
+        <v>5000.2</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H267" s="12" t="n">
         <v>2074</v>
@@ -13049,13 +13049,13 @@
         <v>78</v>
       </c>
       <c r="F268" s="12" t="n">
-        <v>4565.5</v>
+        <v>4569.9</v>
       </c>
       <c r="G268" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H268" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I268" s="13" t="inlineStr">
         <is>
@@ -13084,13 +13084,13 @@
         <v>47</v>
       </c>
       <c r="F269" s="12" t="n">
-        <v>2742.7</v>
+        <v>2744.1</v>
       </c>
       <c r="G269" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H269" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I269" s="13" t="inlineStr">
         <is>
@@ -13119,13 +13119,13 @@
         <v>297</v>
       </c>
       <c r="F270" s="12" t="n">
-        <v>17357.8</v>
+        <v>17372.9</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H270" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
@@ -13154,13 +13154,13 @@
         <v>130</v>
       </c>
       <c r="F271" s="12" t="n">
-        <v>7770.4</v>
+        <v>7778.4</v>
       </c>
       <c r="G271" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H271" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I271" s="13" t="inlineStr">
         <is>
@@ -13189,10 +13189,10 @@
         <v>37</v>
       </c>
       <c r="F272" s="12" t="n">
-        <v>2192.7</v>
+        <v>2193.7</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H272" s="12" t="n">
         <v>622</v>
@@ -13224,13 +13224,13 @@
         <v>80</v>
       </c>
       <c r="F273" s="12" t="n">
-        <v>4709.3</v>
+        <v>4713.7</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H273" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I273" s="13" t="inlineStr">
         <is>
@@ -13256,16 +13256,16 @@
         <v>98.3</v>
       </c>
       <c r="E274" s="12" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F274" s="12" t="n">
-        <v>9942</v>
+        <v>9954.5</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H274" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
@@ -13294,13 +13294,13 @@
         <v>135</v>
       </c>
       <c r="F275" s="12" t="n">
-        <v>8025.8</v>
+        <v>8032.7</v>
       </c>
       <c r="G275" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H275" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I275" s="13" t="inlineStr">
         <is>
@@ -13329,13 +13329,13 @@
         <v>229</v>
       </c>
       <c r="F276" s="12" t="n">
-        <v>12657.5</v>
+        <v>12669</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H276" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I276" s="13" t="inlineStr">
         <is>
@@ -13364,13 +13364,13 @@
         <v>98</v>
       </c>
       <c r="F277" s="12" t="n">
-        <v>5527.3</v>
+        <v>5533.2</v>
       </c>
       <c r="G277" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H277" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I277" s="13" t="inlineStr">
         <is>
@@ -13399,13 +13399,13 @@
         <v>25</v>
       </c>
       <c r="F278" s="12" t="n">
-        <v>1366.7</v>
+        <v>1369.6</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H278" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
@@ -13419,28 +13419,28 @@
       </c>
       <c r="B279" s="12" t="inlineStr">
         <is>
-          <t>Glucokinase</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Youth Diabetes</t>
+          <t>Metabolomics</t>
         </is>
       </c>
       <c r="D279" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E279" s="12" t="n">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="F279" s="12" t="n">
-        <v>2659.2</v>
+        <v>9986.9</v>
       </c>
       <c r="G279" s="12" t="n">
-        <v>861</v>
+        <v>7737</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>8213</v>
+        <v>12891</v>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
@@ -13454,28 +13454,28 @@
       </c>
       <c r="B280" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Glucokinase</t>
         </is>
       </c>
       <c r="C280" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Youth Diabetes</t>
         </is>
       </c>
       <c r="D280" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E280" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F280" s="12" t="n">
-        <v>2736</v>
+        <v>2661.9</v>
       </c>
       <c r="G280" s="12" t="n">
-        <v>12035</v>
+        <v>862</v>
       </c>
       <c r="H280" s="12" t="n">
-        <v>622</v>
+        <v>8220</v>
       </c>
       <c r="I280" s="13" t="inlineStr">
         <is>
@@ -13489,28 +13489,28 @@
       </c>
       <c r="B281" s="12" t="inlineStr">
         <is>
+          <t>AI / ML Predict</t>
+        </is>
+      </c>
+      <c r="C281" s="12" t="inlineStr">
+        <is>
           <t>Drug Repurposing</t>
-        </is>
-      </c>
-      <c r="C281" s="12" t="inlineStr">
-        <is>
-          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D281" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E281" s="12" t="n">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="F281" s="12" t="n">
-        <v>7156.6</v>
+        <v>2738.3</v>
       </c>
       <c r="G281" s="12" t="n">
+        <v>12055</v>
+      </c>
+      <c r="H281" s="12" t="n">
         <v>622</v>
-      </c>
-      <c r="H281" s="12" t="n">
-        <v>82343</v>
       </c>
       <c r="I281" s="13" t="inlineStr">
         <is>
@@ -13524,28 +13524,28 @@
       </c>
       <c r="B282" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D282" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E282" s="12" t="n">
-        <v>252</v>
+        <v>132</v>
       </c>
       <c r="F282" s="12" t="n">
-        <v>13679.8</v>
+        <v>7159.6</v>
       </c>
       <c r="G282" s="12" t="n">
-        <v>26563</v>
+        <v>622</v>
       </c>
       <c r="H282" s="12" t="n">
-        <v>7045</v>
+        <v>82411</v>
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
@@ -13559,28 +13559,28 @@
       </c>
       <c r="B283" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D283" s="12" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="E283" s="12" t="n">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="F283" s="12" t="n">
-        <v>9695.6</v>
+        <v>13692.2</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>7811</v>
+        <v>26581</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>12035</v>
+        <v>7053</v>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
@@ -13594,28 +13594,28 @@
       </c>
       <c r="B284" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D284" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E284" s="12" t="n">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c r="F284" s="12" t="n">
-        <v>2937</v>
+        <v>9709.299999999999</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>13868</v>
+        <v>7820</v>
       </c>
       <c r="H284" s="12" t="n">
-        <v>622</v>
+        <v>12055</v>
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
@@ -13634,23 +13634,23 @@
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D285" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E285" s="12" t="n">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="F285" s="12" t="n">
-        <v>9884.299999999999</v>
+        <v>2939.8</v>
       </c>
       <c r="G285" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H285" s="12" t="n">
-        <v>7045</v>
+        <v>622</v>
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
@@ -13664,28 +13664,28 @@
       </c>
       <c r="B286" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>Metabolomics</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D286" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E286" s="12" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F286" s="12" t="n">
-        <v>9978.1</v>
+        <v>9899.6</v>
       </c>
       <c r="G286" s="12" t="n">
-        <v>7730</v>
+        <v>13895</v>
       </c>
       <c r="H286" s="12" t="n">
-        <v>12880</v>
+        <v>7053</v>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
@@ -13714,10 +13714,10 @@
         <v>21</v>
       </c>
       <c r="F287" s="12" t="n">
-        <v>1081.7</v>
+        <v>1083.4</v>
       </c>
       <c r="G287" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H287" s="12" t="n">
         <v>622</v>
@@ -13749,13 +13749,13 @@
         <v>205</v>
       </c>
       <c r="F288" s="12" t="n">
-        <v>10926.7</v>
+        <v>10935.8</v>
       </c>
       <c r="G288" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H288" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I288" s="13" t="inlineStr">
         <is>
@@ -13784,13 +13784,13 @@
         <v>79</v>
       </c>
       <c r="F289" s="12" t="n">
-        <v>4127.2</v>
+        <v>4129</v>
       </c>
       <c r="G289" s="12" t="n">
         <v>2074</v>
       </c>
       <c r="H289" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I289" s="13" t="inlineStr">
         <is>
@@ -13819,13 +13819,13 @@
         <v>68</v>
       </c>
       <c r="F290" s="12" t="n">
-        <v>3426.4</v>
+        <v>3428.3</v>
       </c>
       <c r="G290" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H290" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
@@ -13854,13 +13854,13 @@
         <v>213</v>
       </c>
       <c r="F291" s="12" t="n">
-        <v>10654.4</v>
+        <v>10668</v>
       </c>
       <c r="G291" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H291" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="I291" s="13" t="inlineStr">
         <is>
@@ -13889,13 +13889,13 @@
         <v>159</v>
       </c>
       <c r="F292" s="12" t="n">
-        <v>7798.7</v>
+        <v>7807</v>
       </c>
       <c r="G292" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H292" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I292" s="13" t="inlineStr">
         <is>
@@ -13924,13 +13924,13 @@
         <v>155</v>
       </c>
       <c r="F293" s="12" t="n">
-        <v>7656</v>
+        <v>7667.3</v>
       </c>
       <c r="G293" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H293" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
@@ -13959,13 +13959,13 @@
         <v>191</v>
       </c>
       <c r="F294" s="12" t="n">
-        <v>9743.1</v>
+        <v>9755.6</v>
       </c>
       <c r="G294" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H294" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
@@ -13994,13 +13994,13 @@
         <v>55</v>
       </c>
       <c r="F295" s="12" t="n">
-        <v>2785</v>
+        <v>2788</v>
       </c>
       <c r="G295" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H295" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I295" s="13" t="inlineStr">
         <is>
@@ -14014,28 +14014,28 @@
       </c>
       <c r="B296" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>SGLT2 Inhibitors</t>
         </is>
       </c>
       <c r="C296" s="12" t="inlineStr">
         <is>
-          <t>Health Equity</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D296" s="12" t="n">
         <v>98</v>
       </c>
       <c r="E296" s="12" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F296" s="12" t="n">
-        <v>3822.5</v>
+        <v>5857.8</v>
       </c>
       <c r="G296" s="12" t="n">
-        <v>7045</v>
+        <v>7737</v>
       </c>
       <c r="H296" s="12" t="n">
-        <v>2074</v>
+        <v>4435</v>
       </c>
       <c r="I296" s="13" t="inlineStr">
         <is>
@@ -14049,28 +14049,28 @@
       </c>
       <c r="B297" s="12" t="inlineStr">
         <is>
-          <t>Beta Cell Regen</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>Health Equity</t>
         </is>
       </c>
       <c r="D297" s="12" t="n">
-        <v>97.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="E297" s="12" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="F297" s="12" t="n">
-        <v>1221.7</v>
+        <v>3824.6</v>
       </c>
       <c r="G297" s="12" t="n">
-        <v>1503</v>
+        <v>7053</v>
       </c>
       <c r="H297" s="12" t="n">
-        <v>993</v>
+        <v>2074</v>
       </c>
       <c r="I297" s="13" t="inlineStr">
         <is>
@@ -14084,28 +14084,28 @@
       </c>
       <c r="B298" s="12" t="inlineStr">
         <is>
-          <t>GWAS / Polygenic</t>
+          <t>Beta Cell Regen</t>
         </is>
       </c>
       <c r="C298" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="D298" s="12" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="E298" s="12" t="n">
-        <v>258</v>
+        <v>26</v>
       </c>
       <c r="F298" s="12" t="n">
-        <v>12061.7</v>
+        <v>1222.3</v>
       </c>
       <c r="G298" s="12" t="n">
-        <v>5477</v>
+        <v>1503</v>
       </c>
       <c r="H298" s="12" t="n">
-        <v>26563</v>
+        <v>994</v>
       </c>
       <c r="I298" s="13" t="inlineStr">
         <is>
@@ -14119,28 +14119,28 @@
       </c>
       <c r="B299" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>GWAS / Polygenic</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="D299" s="12" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="E299" s="12" t="n">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="F299" s="12" t="n">
-        <v>2331.6</v>
+        <v>12075.7</v>
       </c>
       <c r="G299" s="12" t="n">
-        <v>7811</v>
+        <v>5486</v>
       </c>
       <c r="H299" s="12" t="n">
-        <v>696</v>
+        <v>26581</v>
       </c>
       <c r="I299" s="13" t="inlineStr">
         <is>
@@ -14154,28 +14154,28 @@
       </c>
       <c r="B300" s="12" t="inlineStr">
         <is>
-          <t>SGLT2 Inhibitors</t>
+          <t>Beta Cell Regen</t>
         </is>
       </c>
       <c r="C300" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D300" s="12" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="E300" s="12" t="n">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="F300" s="12" t="n">
-        <v>5852.5</v>
+        <v>11129.4</v>
       </c>
       <c r="G300" s="12" t="n">
-        <v>7730</v>
+        <v>1503</v>
       </c>
       <c r="H300" s="12" t="n">
-        <v>4431</v>
+        <v>82411</v>
       </c>
       <c r="I300" s="13" t="inlineStr">
         <is>
@@ -14189,28 +14189,28 @@
       </c>
       <c r="B301" s="12" t="inlineStr">
         <is>
-          <t>Beta Cell Regen</t>
+          <t>Autoimmunity T1D</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>Prevention / DPP</t>
+          <t>Islet Transplant</t>
         </is>
       </c>
       <c r="D301" s="12" t="n">
         <v>97.8</v>
       </c>
       <c r="E301" s="12" t="n">
-        <v>245</v>
+        <v>24</v>
       </c>
       <c r="F301" s="12" t="n">
-        <v>11124.8</v>
+        <v>1093.7</v>
       </c>
       <c r="G301" s="12" t="n">
-        <v>1503</v>
+        <v>4728</v>
       </c>
       <c r="H301" s="12" t="n">
-        <v>82343</v>
+        <v>253</v>
       </c>
       <c r="I301" s="13" t="inlineStr">
         <is>
@@ -14224,28 +14224,28 @@
       </c>
       <c r="B302" s="12" t="inlineStr">
         <is>
-          <t>Autoimmunity T1D</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C302" s="12" t="inlineStr">
         <is>
-          <t>Islet Transplant</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="D302" s="12" t="n">
         <v>97.8</v>
       </c>
       <c r="E302" s="12" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="F302" s="12" t="n">
-        <v>1093</v>
+        <v>2338</v>
       </c>
       <c r="G302" s="12" t="n">
-        <v>4722</v>
+        <v>7820</v>
       </c>
       <c r="H302" s="12" t="n">
-        <v>253</v>
+        <v>699</v>
       </c>
       <c r="I302" s="13" t="inlineStr">
         <is>
@@ -14274,13 +14274,13 @@
         <v>112</v>
       </c>
       <c r="F303" s="12" t="n">
-        <v>4861.4</v>
+        <v>4867</v>
       </c>
       <c r="G303" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H303" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I303" s="13" t="inlineStr">
         <is>
@@ -14309,13 +14309,13 @@
         <v>213</v>
       </c>
       <c r="F304" s="12" t="n">
-        <v>9272.4</v>
+        <v>9284.5</v>
       </c>
       <c r="G304" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H304" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I304" s="13" t="inlineStr">
         <is>
@@ -14341,16 +14341,16 @@
         <v>97.7</v>
       </c>
       <c r="E305" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F305" s="12" t="n">
-        <v>2112.3</v>
+        <v>2117</v>
       </c>
       <c r="G305" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H305" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I305" s="13" t="inlineStr">
         <is>
@@ -14379,13 +14379,13 @@
         <v>340</v>
       </c>
       <c r="F306" s="12" t="n">
-        <v>14941.1</v>
+        <v>14954.4</v>
       </c>
       <c r="G306" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H306" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I306" s="13" t="inlineStr">
         <is>
@@ -14414,13 +14414,13 @@
         <v>148</v>
       </c>
       <c r="F307" s="12" t="n">
-        <v>6227.5</v>
+        <v>6234.1</v>
       </c>
       <c r="G307" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H307" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I307" s="13" t="inlineStr">
         <is>
@@ -14449,13 +14449,13 @@
         <v>140</v>
       </c>
       <c r="F308" s="12" t="n">
-        <v>5883.1</v>
+        <v>5889.1</v>
       </c>
       <c r="G308" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H308" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I308" s="13" t="inlineStr">
         <is>
@@ -14484,13 +14484,13 @@
         <v>220</v>
       </c>
       <c r="F309" s="12" t="n">
-        <v>9313.799999999999</v>
+        <v>9322.700000000001</v>
       </c>
       <c r="G309" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H309" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I309" s="13" t="inlineStr">
         <is>
@@ -14519,13 +14519,13 @@
         <v>257</v>
       </c>
       <c r="F310" s="12" t="n">
-        <v>10516.3</v>
+        <v>10527.3</v>
       </c>
       <c r="G310" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="H310" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I310" s="13" t="inlineStr">
         <is>
@@ -14554,13 +14554,13 @@
         <v>224</v>
       </c>
       <c r="F311" s="12" t="n">
-        <v>8923</v>
+        <v>8934</v>
       </c>
       <c r="G311" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H311" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I311" s="13" t="inlineStr">
         <is>
@@ -14589,13 +14589,13 @@
         <v>291</v>
       </c>
       <c r="F312" s="12" t="n">
-        <v>11635.3</v>
+        <v>11647.4</v>
       </c>
       <c r="G312" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H312" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I312" s="13" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         <v>223</v>
       </c>
       <c r="F313" s="12" t="n">
-        <v>9042.5</v>
+        <v>9050.799999999999</v>
       </c>
       <c r="G313" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H313" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I313" s="13" t="inlineStr">
         <is>
@@ -14656,16 +14656,16 @@
         <v>97.5</v>
       </c>
       <c r="E314" s="12" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F314" s="12" t="n">
-        <v>13364.9</v>
+        <v>13383.6</v>
       </c>
       <c r="G314" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H314" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I314" s="13" t="inlineStr">
         <is>
@@ -14691,16 +14691,16 @@
         <v>97.5</v>
       </c>
       <c r="E315" s="12" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F315" s="12" t="n">
-        <v>12733.2</v>
+        <v>12751.3</v>
       </c>
       <c r="G315" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H315" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I315" s="13" t="inlineStr">
         <is>
@@ -14729,13 +14729,13 @@
         <v>88</v>
       </c>
       <c r="F316" s="12" t="n">
-        <v>3445.6</v>
+        <v>3449.5</v>
       </c>
       <c r="G316" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H316" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I316" s="13" t="inlineStr">
         <is>
@@ -14764,13 +14764,13 @@
         <v>164</v>
       </c>
       <c r="F317" s="12" t="n">
-        <v>6411.8</v>
+        <v>6418.8</v>
       </c>
       <c r="G317" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H317" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I317" s="13" t="inlineStr">
         <is>
@@ -14799,13 +14799,13 @@
         <v>208</v>
       </c>
       <c r="F318" s="12" t="n">
-        <v>7967.8</v>
+        <v>7974.8</v>
       </c>
       <c r="G318" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H318" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I318" s="13" t="inlineStr">
         <is>
@@ -14834,13 +14834,13 @@
         <v>443</v>
       </c>
       <c r="F319" s="12" t="n">
-        <v>16860.5</v>
+        <v>16877.3</v>
       </c>
       <c r="G319" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H319" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I319" s="13" t="inlineStr">
         <is>
@@ -14869,13 +14869,13 @@
         <v>57</v>
       </c>
       <c r="F320" s="12" t="n">
-        <v>2214.3</v>
+        <v>2220.4</v>
       </c>
       <c r="G320" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H320" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I320" s="13" t="inlineStr">
         <is>
@@ -14904,13 +14904,13 @@
         <v>296</v>
       </c>
       <c r="F321" s="12" t="n">
-        <v>11530.3</v>
+        <v>11540</v>
       </c>
       <c r="G321" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H321" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I321" s="13" t="inlineStr">
         <is>
@@ -14939,13 +14939,13 @@
         <v>270</v>
       </c>
       <c r="F322" s="12" t="n">
-        <v>10285.1</v>
+        <v>10293.9</v>
       </c>
       <c r="G322" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H322" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I322" s="13" t="inlineStr">
         <is>
@@ -14971,16 +14971,16 @@
         <v>97.40000000000001</v>
       </c>
       <c r="E323" s="12" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F323" s="12" t="n">
-        <v>13745</v>
+        <v>13763</v>
       </c>
       <c r="G323" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H323" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I323" s="13" t="inlineStr">
         <is>
@@ -15006,16 +15006,16 @@
         <v>97.3</v>
       </c>
       <c r="E324" s="12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F324" s="12" t="n">
-        <v>8009.5</v>
+        <v>8017.5</v>
       </c>
       <c r="G324" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H324" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I324" s="13" t="inlineStr">
         <is>
@@ -15044,13 +15044,13 @@
         <v>263</v>
       </c>
       <c r="F325" s="12" t="n">
-        <v>9375.299999999999</v>
+        <v>9385.4</v>
       </c>
       <c r="G325" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H325" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I325" s="13" t="inlineStr">
         <is>
@@ -15079,13 +15079,13 @@
         <v>256</v>
       </c>
       <c r="F326" s="12" t="n">
-        <v>9271.299999999999</v>
+        <v>9274.5</v>
       </c>
       <c r="G326" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H326" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I326" s="13" t="inlineStr">
         <is>
@@ -15099,28 +15099,28 @@
       </c>
       <c r="B327" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Autoimmunity T1D</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="D327" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E327" s="12" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F327" s="12" t="n">
-        <v>6243.8</v>
+        <v>6080.5</v>
       </c>
       <c r="G327" s="12" t="n">
-        <v>20726</v>
+        <v>4728</v>
       </c>
       <c r="H327" s="12" t="n">
-        <v>1881</v>
+        <v>7820</v>
       </c>
       <c r="I327" s="13" t="inlineStr">
         <is>
@@ -15134,28 +15134,28 @@
       </c>
       <c r="B328" s="12" t="inlineStr">
         <is>
-          <t>Autoimmunity T1D</t>
+          <t>GWAS / Polygenic</t>
         </is>
       </c>
       <c r="C328" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D328" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E328" s="12" t="n">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="F328" s="12" t="n">
-        <v>6073.2</v>
+        <v>8132.3</v>
       </c>
       <c r="G328" s="12" t="n">
-        <v>4722</v>
+        <v>5486</v>
       </c>
       <c r="H328" s="12" t="n">
-        <v>7811</v>
+        <v>12055</v>
       </c>
       <c r="I328" s="13" t="inlineStr">
         <is>
@@ -15174,23 +15174,23 @@
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D329" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E329" s="12" t="n">
-        <v>236</v>
+        <v>53</v>
       </c>
       <c r="F329" s="12" t="n">
-        <v>8118.8</v>
+        <v>1847.2</v>
       </c>
       <c r="G329" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H329" s="12" t="n">
-        <v>12035</v>
+        <v>622</v>
       </c>
       <c r="I329" s="13" t="inlineStr">
         <is>
@@ -15204,28 +15204,28 @@
       </c>
       <c r="B330" s="12" t="inlineStr">
         <is>
-          <t>GWAS / Polygenic</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Closed Loop / AP</t>
         </is>
       </c>
       <c r="D330" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E330" s="12" t="n">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="F330" s="12" t="n">
-        <v>1845.7</v>
+        <v>4876.9</v>
       </c>
       <c r="G330" s="12" t="n">
-        <v>5477</v>
+        <v>12055</v>
       </c>
       <c r="H330" s="12" t="n">
-        <v>622</v>
+        <v>1973</v>
       </c>
       <c r="I330" s="13" t="inlineStr">
         <is>
@@ -15239,28 +15239,28 @@
       </c>
       <c r="B331" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Retinopathy</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>Closed Loop / AP</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="D331" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E331" s="12" t="n">
-        <v>140</v>
+        <v>631</v>
       </c>
       <c r="F331" s="12" t="n">
-        <v>4867.9</v>
+        <v>21473.9</v>
       </c>
       <c r="G331" s="12" t="n">
-        <v>12035</v>
+        <v>17348</v>
       </c>
       <c r="H331" s="12" t="n">
-        <v>1969</v>
+        <v>26581</v>
       </c>
       <c r="I331" s="13" t="inlineStr">
         <is>
@@ -15274,28 +15274,28 @@
       </c>
       <c r="B332" s="12" t="inlineStr">
         <is>
-          <t>Retinopathy</t>
+          <t>Youth Diabetes</t>
         </is>
       </c>
       <c r="C332" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Gestational DM</t>
         </is>
       </c>
       <c r="D332" s="12" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="E332" s="12" t="n">
-        <v>631</v>
+        <v>327</v>
       </c>
       <c r="F332" s="12" t="n">
-        <v>21456.7</v>
+        <v>11364.9</v>
       </c>
       <c r="G332" s="12" t="n">
-        <v>17332</v>
+        <v>8220</v>
       </c>
       <c r="H332" s="12" t="n">
-        <v>26563</v>
+        <v>15713</v>
       </c>
       <c r="I332" s="13" t="inlineStr">
         <is>
@@ -15309,28 +15309,28 @@
       </c>
       <c r="B333" s="12" t="inlineStr">
         <is>
-          <t>Youth Diabetes</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>Gestational DM</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="D333" s="12" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="E333" s="12" t="n">
-        <v>327</v>
+        <v>185</v>
       </c>
       <c r="F333" s="12" t="n">
-        <v>11354.6</v>
+        <v>6256.7</v>
       </c>
       <c r="G333" s="12" t="n">
-        <v>8213</v>
+        <v>20745</v>
       </c>
       <c r="H333" s="12" t="n">
-        <v>15698</v>
+        <v>1887</v>
       </c>
       <c r="I333" s="13" t="inlineStr">
         <is>
@@ -15356,16 +15356,16 @@
         <v>97</v>
       </c>
       <c r="E334" s="12" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F334" s="12" t="n">
-        <v>7318.7</v>
+        <v>7327.2</v>
       </c>
       <c r="G334" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H334" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I334" s="13" t="inlineStr">
         <is>
@@ -15391,16 +15391,16 @@
         <v>97</v>
       </c>
       <c r="E335" s="12" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F335" s="12" t="n">
-        <v>11348.9</v>
+        <v>11365.8</v>
       </c>
       <c r="G335" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H335" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I335" s="13" t="inlineStr">
         <is>
@@ -15414,28 +15414,28 @@
       </c>
       <c r="B336" s="12" t="inlineStr">
         <is>
-          <t>Personalized Nutr</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="C336" s="12" t="inlineStr">
         <is>
-          <t>Metabolomics</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D336" s="12" t="n">
         <v>97</v>
       </c>
       <c r="E336" s="12" t="n">
-        <v>91</v>
+        <v>380</v>
       </c>
       <c r="F336" s="12" t="n">
-        <v>2994.1</v>
+        <v>12470.3</v>
       </c>
       <c r="G336" s="12" t="n">
-        <v>696</v>
+        <v>1887</v>
       </c>
       <c r="H336" s="12" t="n">
-        <v>12880</v>
+        <v>82411</v>
       </c>
       <c r="I336" s="13" t="inlineStr">
         <is>
@@ -15449,28 +15449,28 @@
       </c>
       <c r="B337" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>Prevention / DPP</t>
+          <t>Gestational DM</t>
         </is>
       </c>
       <c r="D337" s="12" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E337" s="12" t="n">
-        <v>379</v>
+        <v>553</v>
       </c>
       <c r="F337" s="12" t="n">
-        <v>12445.4</v>
+        <v>18054.5</v>
       </c>
       <c r="G337" s="12" t="n">
-        <v>1881</v>
+        <v>20745</v>
       </c>
       <c r="H337" s="12" t="n">
-        <v>82343</v>
+        <v>15713</v>
       </c>
       <c r="I337" s="13" t="inlineStr">
         <is>
@@ -15484,28 +15484,28 @@
       </c>
       <c r="B338" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>GWAS / Polygenic</t>
         </is>
       </c>
       <c r="C338" s="12" t="inlineStr">
         <is>
-          <t>Gestational DM</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D338" s="12" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="E338" s="12" t="n">
-        <v>552</v>
+        <v>153</v>
       </c>
       <c r="F338" s="12" t="n">
-        <v>18037.6</v>
+        <v>4932.6</v>
       </c>
       <c r="G338" s="12" t="n">
-        <v>20726</v>
+        <v>5486</v>
       </c>
       <c r="H338" s="12" t="n">
-        <v>15698</v>
+        <v>4435</v>
       </c>
       <c r="I338" s="13" t="inlineStr">
         <is>
@@ -15519,28 +15519,28 @@
       </c>
       <c r="B339" s="12" t="inlineStr">
         <is>
-          <t>GWAS / Polygenic</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="D339" s="12" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="E339" s="12" t="n">
-        <v>153</v>
+        <v>442</v>
       </c>
       <c r="F339" s="12" t="n">
-        <v>4926.3</v>
+        <v>14417.5</v>
       </c>
       <c r="G339" s="12" t="n">
-        <v>5477</v>
+        <v>7820</v>
       </c>
       <c r="H339" s="12" t="n">
-        <v>4431</v>
+        <v>26581</v>
       </c>
       <c r="I339" s="13" t="inlineStr">
         <is>
@@ -15554,28 +15554,28 @@
       </c>
       <c r="B340" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>Microbiome Gut</t>
         </is>
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D340" s="12" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="E340" s="12" t="n">
-        <v>442</v>
+        <v>393</v>
       </c>
       <c r="F340" s="12" t="n">
-        <v>14404.3</v>
+        <v>12486.3</v>
       </c>
       <c r="G340" s="12" t="n">
-        <v>7811</v>
+        <v>10716</v>
       </c>
       <c r="H340" s="12" t="n">
-        <v>26563</v>
+        <v>14549</v>
       </c>
       <c r="I340" s="13" t="inlineStr">
         <is>
@@ -15589,28 +15589,28 @@
       </c>
       <c r="B341" s="12" t="inlineStr">
         <is>
-          <t>Microbiome Gut</t>
+          <t>Personalized Nutr</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Metabolomics</t>
         </is>
       </c>
       <c r="D341" s="12" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="E341" s="12" t="n">
-        <v>391</v>
+        <v>92</v>
       </c>
       <c r="F341" s="12" t="n">
-        <v>12473</v>
+        <v>3001.8</v>
       </c>
       <c r="G341" s="12" t="n">
-        <v>10702</v>
+        <v>699</v>
       </c>
       <c r="H341" s="12" t="n">
-        <v>14537</v>
+        <v>12891</v>
       </c>
       <c r="I341" s="13" t="inlineStr">
         <is>
@@ -15639,13 +15639,13 @@
         <v>574</v>
       </c>
       <c r="F342" s="12" t="n">
-        <v>18496.8</v>
+        <v>18511</v>
       </c>
       <c r="G342" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H342" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I342" s="13" t="inlineStr">
         <is>
@@ -15674,13 +15674,13 @@
         <v>233</v>
       </c>
       <c r="F343" s="12" t="n">
-        <v>7554.6</v>
+        <v>7561.2</v>
       </c>
       <c r="G343" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H343" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I343" s="13" t="inlineStr">
         <is>
@@ -15706,16 +15706,16 @@
         <v>96.8</v>
       </c>
       <c r="E344" s="12" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F344" s="12" t="n">
-        <v>13975.6</v>
+        <v>13990.2</v>
       </c>
       <c r="G344" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="H344" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I344" s="13" t="inlineStr">
         <is>
@@ -15741,16 +15741,16 @@
         <v>96.8</v>
       </c>
       <c r="E345" s="12" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F345" s="12" t="n">
-        <v>5229.2</v>
+        <v>5239.7</v>
       </c>
       <c r="G345" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H345" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I345" s="13" t="inlineStr">
         <is>
@@ -15779,13 +15779,13 @@
         <v>243</v>
       </c>
       <c r="F346" s="12" t="n">
-        <v>7606.6</v>
+        <v>7614.2</v>
       </c>
       <c r="G346" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="H346" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I346" s="13" t="inlineStr">
         <is>
@@ -15814,13 +15814,13 @@
         <v>96</v>
       </c>
       <c r="F347" s="12" t="n">
-        <v>2894.2</v>
+        <v>2902.8</v>
       </c>
       <c r="G347" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H347" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I347" s="13" t="inlineStr">
         <is>
@@ -15846,16 +15846,16 @@
         <v>96.7</v>
       </c>
       <c r="E348" s="12" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F348" s="12" t="n">
-        <v>17879.8</v>
+        <v>17900.7</v>
       </c>
       <c r="G348" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H348" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I348" s="13" t="inlineStr">
         <is>
@@ -15884,13 +15884,13 @@
         <v>672</v>
       </c>
       <c r="F349" s="12" t="n">
-        <v>20420.2</v>
+        <v>20436.9</v>
       </c>
       <c r="G349" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H349" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I349" s="13" t="inlineStr">
         <is>
@@ -15919,13 +15919,13 @@
         <v>344</v>
       </c>
       <c r="F350" s="12" t="n">
-        <v>10185</v>
+        <v>10194.7</v>
       </c>
       <c r="G350" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H350" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I350" s="13" t="inlineStr">
         <is>
@@ -15954,13 +15954,13 @@
         <v>113</v>
       </c>
       <c r="F351" s="12" t="n">
-        <v>3346.7</v>
+        <v>3351</v>
       </c>
       <c r="G351" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H351" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I351" s="13" t="inlineStr">
         <is>
@@ -15989,13 +15989,13 @@
         <v>112</v>
       </c>
       <c r="F352" s="12" t="n">
-        <v>3259.9</v>
+        <v>3263.7</v>
       </c>
       <c r="G352" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H352" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I352" s="13" t="inlineStr">
         <is>
@@ -16009,28 +16009,28 @@
       </c>
       <c r="B353" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>Youth Diabetes</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D353" s="12" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E353" s="12" t="n">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="F353" s="12" t="n">
-        <v>13046.9</v>
+        <v>14218.2</v>
       </c>
       <c r="G353" s="12" t="n">
-        <v>20726</v>
+        <v>13895</v>
       </c>
       <c r="H353" s="12" t="n">
-        <v>8213</v>
+        <v>14549</v>
       </c>
       <c r="I353" s="13" t="inlineStr">
         <is>
@@ -16044,28 +16044,28 @@
       </c>
       <c r="B354" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C354" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Youth Diabetes</t>
         </is>
       </c>
       <c r="D354" s="12" t="n">
         <v>96.5</v>
       </c>
       <c r="E354" s="12" t="n">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="F354" s="12" t="n">
-        <v>14198.6</v>
+        <v>13058.5</v>
       </c>
       <c r="G354" s="12" t="n">
-        <v>13868</v>
+        <v>20745</v>
       </c>
       <c r="H354" s="12" t="n">
-        <v>14537</v>
+        <v>8220</v>
       </c>
       <c r="I354" s="13" t="inlineStr">
         <is>
@@ -16094,13 +16094,13 @@
         <v>40</v>
       </c>
       <c r="F355" s="12" t="n">
-        <v>1144.2</v>
+        <v>1148.5</v>
       </c>
       <c r="G355" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H355" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I355" s="13" t="inlineStr">
         <is>
@@ -16129,13 +16129,13 @@
         <v>578</v>
       </c>
       <c r="F356" s="12" t="n">
-        <v>16323.7</v>
+        <v>16330.4</v>
       </c>
       <c r="G356" s="12" t="n">
         <v>3236</v>
       </c>
       <c r="H356" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
@@ -16164,13 +16164,13 @@
         <v>380</v>
       </c>
       <c r="F357" s="12" t="n">
-        <v>10849</v>
+        <v>10857.6</v>
       </c>
       <c r="G357" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H357" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I357" s="13" t="inlineStr">
         <is>
@@ -16199,13 +16199,13 @@
         <v>279</v>
       </c>
       <c r="F358" s="12" t="n">
-        <v>7761.1</v>
+        <v>7771.5</v>
       </c>
       <c r="G358" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H358" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I358" s="13" t="inlineStr">
         <is>
@@ -16234,13 +16234,13 @@
         <v>48</v>
       </c>
       <c r="F359" s="12" t="n">
-        <v>1302</v>
+        <v>1304.1</v>
       </c>
       <c r="G359" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H359" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="I359" s="13" t="inlineStr">
         <is>
@@ -16269,13 +16269,13 @@
         <v>320</v>
       </c>
       <c r="F360" s="12" t="n">
-        <v>8399</v>
+        <v>8409.5</v>
       </c>
       <c r="G360" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H360" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
@@ -16304,13 +16304,13 @@
         <v>536</v>
       </c>
       <c r="F361" s="12" t="n">
-        <v>14219.4</v>
+        <v>14232.2</v>
       </c>
       <c r="G361" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H361" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I361" s="13" t="inlineStr">
         <is>
@@ -16339,13 +16339,13 @@
         <v>166</v>
       </c>
       <c r="F362" s="12" t="n">
-        <v>4304.4</v>
+        <v>4309.6</v>
       </c>
       <c r="G362" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H362" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
@@ -16374,13 +16374,13 @@
         <v>242</v>
       </c>
       <c r="F363" s="12" t="n">
-        <v>6252.5</v>
+        <v>6259.2</v>
       </c>
       <c r="G363" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H363" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I363" s="13" t="inlineStr">
         <is>
@@ -16409,13 +16409,13 @@
         <v>432</v>
       </c>
       <c r="F364" s="12" t="n">
-        <v>11073.3</v>
+        <v>11084.9</v>
       </c>
       <c r="G364" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H364" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
@@ -16441,16 +16441,16 @@
         <v>96.09999999999999</v>
       </c>
       <c r="E365" s="12" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F365" s="12" t="n">
-        <v>13227</v>
+        <v>13243.4</v>
       </c>
       <c r="G365" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H365" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I365" s="13" t="inlineStr">
         <is>
@@ -16479,13 +16479,13 @@
         <v>675</v>
       </c>
       <c r="F366" s="12" t="n">
-        <v>16953.7</v>
+        <v>16978</v>
       </c>
       <c r="G366" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H366" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="I366" s="13" t="inlineStr">
         <is>
@@ -16511,16 +16511,16 @@
         <v>96</v>
       </c>
       <c r="E367" s="12" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F367" s="12" t="n">
-        <v>12961.5</v>
+        <v>12976.2</v>
       </c>
       <c r="G367" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H367" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="I367" s="13" t="inlineStr">
         <is>
@@ -16549,13 +16549,13 @@
         <v>274</v>
       </c>
       <c r="F368" s="12" t="n">
-        <v>6886.3</v>
+        <v>6893.9</v>
       </c>
       <c r="G368" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H368" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I368" s="13" t="inlineStr">
         <is>
@@ -16581,16 +16581,16 @@
         <v>96</v>
       </c>
       <c r="E369" s="12" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F369" s="12" t="n">
-        <v>12450.3</v>
+        <v>12466</v>
       </c>
       <c r="G369" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H369" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I369" s="13" t="inlineStr">
         <is>
@@ -16604,28 +16604,28 @@
       </c>
       <c r="B370" s="12" t="inlineStr">
         <is>
-          <t>Autoimmunity T1D</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C370" s="12" t="inlineStr">
         <is>
-          <t>Microbiome Gut</t>
+          <t>Remission T2D</t>
         </is>
       </c>
       <c r="D370" s="12" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="E370" s="12" t="n">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="F370" s="12" t="n">
-        <v>7108.8</v>
+        <v>7850.1</v>
       </c>
       <c r="G370" s="12" t="n">
-        <v>4722</v>
+        <v>13895</v>
       </c>
       <c r="H370" s="12" t="n">
-        <v>10702</v>
+        <v>4435</v>
       </c>
       <c r="I370" s="13" t="inlineStr">
         <is>
@@ -16639,28 +16639,28 @@
       </c>
       <c r="B371" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Insulin Resistance</t>
         </is>
       </c>
       <c r="C371" s="12" t="inlineStr">
         <is>
-          <t>Remission T2D</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="D371" s="12" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="E371" s="12" t="n">
-        <v>319</v>
+        <v>985</v>
       </c>
       <c r="F371" s="12" t="n">
-        <v>7838.9</v>
+        <v>23482.4</v>
       </c>
       <c r="G371" s="12" t="n">
-        <v>13868</v>
+        <v>20745</v>
       </c>
       <c r="H371" s="12" t="n">
-        <v>4431</v>
+        <v>26581</v>
       </c>
       <c r="I371" s="13" t="inlineStr">
         <is>
@@ -16674,28 +16674,28 @@
       </c>
       <c r="B372" s="12" t="inlineStr">
         <is>
-          <t>Insulin Resistance</t>
+          <t>Autoimmunity T1D</t>
         </is>
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Microbiome Gut</t>
         </is>
       </c>
       <c r="D372" s="12" t="n">
         <v>95.8</v>
       </c>
       <c r="E372" s="12" t="n">
-        <v>985</v>
+        <v>296</v>
       </c>
       <c r="F372" s="12" t="n">
-        <v>23463.7</v>
+        <v>7118</v>
       </c>
       <c r="G372" s="12" t="n">
-        <v>20726</v>
+        <v>4728</v>
       </c>
       <c r="H372" s="12" t="n">
-        <v>26563</v>
+        <v>10716</v>
       </c>
       <c r="I372" s="13" t="inlineStr">
         <is>
@@ -16709,28 +16709,28 @@
       </c>
       <c r="B373" s="12" t="inlineStr">
         <is>
-          <t>Proteomics</t>
+          <t>Gene Therapy</t>
         </is>
       </c>
       <c r="C373" s="12" t="inlineStr">
         <is>
-          <t>Nephropathy DKD</t>
+          <t>Treg / CAR-T</t>
         </is>
       </c>
       <c r="D373" s="12" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="E373" s="12" t="n">
-        <v>362</v>
+        <v>66</v>
       </c>
       <c r="F373" s="12" t="n">
-        <v>8529.799999999999</v>
+        <v>1536.5</v>
       </c>
       <c r="G373" s="12" t="n">
-        <v>5005</v>
+        <v>2375</v>
       </c>
       <c r="H373" s="12" t="n">
-        <v>14537</v>
+        <v>994</v>
       </c>
       <c r="I373" s="13" t="inlineStr">
         <is>
@@ -16744,28 +16744,28 @@
       </c>
       <c r="B374" s="12" t="inlineStr">
         <is>
-          <t>Gene Therapy</t>
+          <t>Proteomics</t>
         </is>
       </c>
       <c r="C374" s="12" t="inlineStr">
         <is>
-          <t>Treg / CAR-T</t>
+          <t>Nephropathy DKD</t>
         </is>
       </c>
       <c r="D374" s="12" t="n">
         <v>95.7</v>
       </c>
       <c r="E374" s="12" t="n">
-        <v>66</v>
+        <v>364</v>
       </c>
       <c r="F374" s="12" t="n">
-        <v>1534.7</v>
+        <v>8537.6</v>
       </c>
       <c r="G374" s="12" t="n">
-        <v>2372</v>
+        <v>5010</v>
       </c>
       <c r="H374" s="12" t="n">
-        <v>993</v>
+        <v>14549</v>
       </c>
       <c r="I374" s="13" t="inlineStr">
         <is>
@@ -16794,13 +16794,13 @@
         <v>873</v>
       </c>
       <c r="F375" s="12" t="n">
-        <v>20300.9</v>
+        <v>20319.4</v>
       </c>
       <c r="G375" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H375" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I375" s="13" t="inlineStr">
         <is>
@@ -16826,16 +16826,16 @@
         <v>95.59999999999999</v>
       </c>
       <c r="E376" s="12" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F376" s="12" t="n">
-        <v>12182.6</v>
+        <v>12202.4</v>
       </c>
       <c r="G376" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H376" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I376" s="13" t="inlineStr">
         <is>
@@ -16864,13 +16864,13 @@
         <v>406</v>
       </c>
       <c r="F377" s="12" t="n">
-        <v>9208</v>
+        <v>9220.799999999999</v>
       </c>
       <c r="G377" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H377" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
@@ -16899,13 +16899,13 @@
         <v>231</v>
       </c>
       <c r="F378" s="12" t="n">
-        <v>5085.5</v>
+        <v>5092.9</v>
       </c>
       <c r="G378" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H378" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="I378" s="13" t="inlineStr">
         <is>
@@ -16931,16 +16931,16 @@
         <v>95.5</v>
       </c>
       <c r="E379" s="12" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F379" s="12" t="n">
-        <v>7570.4</v>
+        <v>7589.8</v>
       </c>
       <c r="G379" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="H379" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I379" s="13" t="inlineStr">
         <is>
@@ -16969,10 +16969,10 @@
         <v>338</v>
       </c>
       <c r="F380" s="12" t="n">
-        <v>7489.1</v>
+        <v>7492.5</v>
       </c>
       <c r="G380" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H380" s="12" t="n">
         <v>3236</v>
@@ -17004,13 +17004,13 @@
         <v>311</v>
       </c>
       <c r="F381" s="12" t="n">
-        <v>6706.9</v>
+        <v>6715.3</v>
       </c>
       <c r="G381" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H381" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I381" s="13" t="inlineStr">
         <is>
@@ -17039,13 +17039,13 @@
         <v>487</v>
       </c>
       <c r="F382" s="12" t="n">
-        <v>10655.9</v>
+        <v>10666.5</v>
       </c>
       <c r="G382" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H382" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I382" s="13" t="inlineStr">
         <is>
@@ -17074,10 +17074,10 @@
         <v>318</v>
       </c>
       <c r="F383" s="12" t="n">
-        <v>6858.7</v>
+        <v>6861.5</v>
       </c>
       <c r="G383" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H383" s="12" t="n">
         <v>3236</v>
@@ -17106,16 +17106,16 @@
         <v>95.3</v>
       </c>
       <c r="E384" s="12" t="n">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="F384" s="12" t="n">
-        <v>24085.4</v>
+        <v>24109</v>
       </c>
       <c r="G384" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="H384" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I384" s="13" t="inlineStr">
         <is>
@@ -17141,16 +17141,16 @@
         <v>95.3</v>
       </c>
       <c r="E385" s="12" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F385" s="12" t="n">
-        <v>6032.6</v>
+        <v>6037.9</v>
       </c>
       <c r="G385" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="H385" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I385" s="13" t="inlineStr">
         <is>
@@ -17176,16 +17176,16 @@
         <v>95.2</v>
       </c>
       <c r="E386" s="12" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F386" s="12" t="n">
-        <v>12723.6</v>
+        <v>12736.8</v>
       </c>
       <c r="G386" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H386" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="I386" s="13" t="inlineStr">
         <is>
@@ -17211,16 +17211,16 @@
         <v>95.2</v>
       </c>
       <c r="E387" s="12" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F387" s="12" t="n">
-        <v>10672.3</v>
+        <v>10687.2</v>
       </c>
       <c r="G387" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H387" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I387" s="13" t="inlineStr">
         <is>
@@ -17246,16 +17246,16 @@
         <v>95.2</v>
       </c>
       <c r="E388" s="12" t="n">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F388" s="12" t="n">
-        <v>13683.4</v>
+        <v>13694.9</v>
       </c>
       <c r="G388" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H388" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I388" s="13" t="inlineStr">
         <is>
@@ -17284,13 +17284,13 @@
         <v>716</v>
       </c>
       <c r="F389" s="12" t="n">
-        <v>14770.3</v>
+        <v>14781.6</v>
       </c>
       <c r="G389" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H389" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="I389" s="13" t="inlineStr">
         <is>
@@ -17319,13 +17319,13 @@
         <v>177</v>
       </c>
       <c r="F390" s="12" t="n">
-        <v>3604.4</v>
+        <v>3609.6</v>
       </c>
       <c r="G390" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H390" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I390" s="13" t="inlineStr">
         <is>
@@ -17354,13 +17354,13 @@
         <v>257</v>
       </c>
       <c r="F391" s="12" t="n">
-        <v>5235.7</v>
+        <v>5242.6</v>
       </c>
       <c r="G391" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H391" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="I391" s="13" t="inlineStr">
         <is>
@@ -17386,16 +17386,16 @@
         <v>95.09999999999999</v>
       </c>
       <c r="E392" s="12" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F392" s="12" t="n">
-        <v>9142.9</v>
+        <v>9154.200000000001</v>
       </c>
       <c r="G392" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H392" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I392" s="13" t="inlineStr">
         <is>
@@ -17421,16 +17421,16 @@
         <v>94.8</v>
       </c>
       <c r="E393" s="12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F393" s="12" t="n">
-        <v>2462.9</v>
+        <v>2465.7</v>
       </c>
       <c r="G393" s="12" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H393" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I393" s="13" t="inlineStr">
         <is>
@@ -17459,13 +17459,13 @@
         <v>987</v>
       </c>
       <c r="F394" s="12" t="n">
-        <v>19101.4</v>
+        <v>19117.9</v>
       </c>
       <c r="G394" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="H394" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I394" s="13" t="inlineStr">
         <is>
@@ -17494,13 +17494,13 @@
         <v>100</v>
       </c>
       <c r="F395" s="12" t="n">
-        <v>1888.2</v>
+        <v>1889.3</v>
       </c>
       <c r="G395" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H395" s="12" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="I395" s="13" t="inlineStr">
         <is>
@@ -17529,13 +17529,13 @@
         <v>510</v>
       </c>
       <c r="F396" s="12" t="n">
-        <v>9583.200000000001</v>
+        <v>9591.9</v>
       </c>
       <c r="G396" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H396" s="12" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
       <c r="I396" s="13" t="inlineStr">
         <is>
@@ -17561,16 +17561,16 @@
         <v>94.7</v>
       </c>
       <c r="E397" s="12" t="n">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="F397" s="12" t="n">
-        <v>19718.6</v>
+        <v>19739.3</v>
       </c>
       <c r="G397" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H397" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I397" s="13" t="inlineStr">
         <is>
@@ -17599,13 +17599,13 @@
         <v>735</v>
       </c>
       <c r="F398" s="12" t="n">
-        <v>13068.3</v>
+        <v>13073.7</v>
       </c>
       <c r="G398" s="12" t="n">
         <v>2074</v>
       </c>
       <c r="H398" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I398" s="13" t="inlineStr">
         <is>
@@ -17666,16 +17666,16 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E400" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F400" s="12" t="n">
-        <v>2729.2</v>
+        <v>2736.9</v>
       </c>
       <c r="G400" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H400" s="12" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I400" s="13" t="inlineStr">
         <is>
@@ -17701,16 +17701,16 @@
         <v>93.8</v>
       </c>
       <c r="E401" s="12" t="n">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="F401" s="12" t="n">
-        <v>25361</v>
+        <v>25386.1</v>
       </c>
       <c r="G401" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H401" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I401" s="13" t="inlineStr">
         <is>
@@ -17736,16 +17736,16 @@
         <v>93.8</v>
       </c>
       <c r="E402" s="12" t="n">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="F402" s="12" t="n">
-        <v>15873.1</v>
+        <v>15887</v>
       </c>
       <c r="G402" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H402" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I402" s="13" t="inlineStr">
         <is>
@@ -17771,16 +17771,16 @@
         <v>93.59999999999999</v>
       </c>
       <c r="E403" s="12" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="F403" s="12" t="n">
-        <v>21236.6</v>
+        <v>21262.8</v>
       </c>
       <c r="G403" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H403" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I403" s="13" t="inlineStr">
         <is>
@@ -17806,16 +17806,16 @@
         <v>93.5</v>
       </c>
       <c r="E404" s="12" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F404" s="12" t="n">
-        <v>4757.9</v>
+        <v>4769.5</v>
       </c>
       <c r="G404" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="H404" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="I404" s="13" t="inlineStr">
         <is>
@@ -17844,13 +17844,13 @@
         <v>1315</v>
       </c>
       <c r="F405" s="12" t="n">
-        <v>19650.6</v>
+        <v>19665.4</v>
       </c>
       <c r="G405" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H405" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I405" s="13" t="inlineStr">
         <is>
@@ -17879,13 +17879,13 @@
         <v>2874</v>
       </c>
       <c r="F406" s="12" t="n">
-        <v>41311.5</v>
+        <v>41347.5</v>
       </c>
       <c r="G406" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H406" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I406" s="13" t="inlineStr">
         <is>
@@ -17911,16 +17911,16 @@
         <v>93</v>
       </c>
       <c r="E407" s="12" t="n">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="F407" s="12" t="n">
-        <v>10030.2</v>
+        <v>10040.3</v>
       </c>
       <c r="G407" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H407" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I407" s="13" t="inlineStr">
         <is>
@@ -17949,13 +17949,13 @@
         <v>231</v>
       </c>
       <c r="F408" s="12" t="n">
-        <v>3209.7</v>
+        <v>3217.5</v>
       </c>
       <c r="G408" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H408" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I408" s="13" t="inlineStr">
         <is>
@@ -17981,16 +17981,16 @@
         <v>92.40000000000001</v>
       </c>
       <c r="E409" s="12" t="n">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F409" s="12" t="n">
-        <v>16338.6</v>
+        <v>16353.1</v>
       </c>
       <c r="G409" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H409" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I409" s="13" t="inlineStr">
         <is>
@@ -18019,13 +18019,13 @@
         <v>810</v>
       </c>
       <c r="F410" s="12" t="n">
-        <v>10600.5</v>
+        <v>10609.7</v>
       </c>
       <c r="G410" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H410" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="I410" s="13" t="inlineStr">
         <is>
@@ -18051,16 +18051,16 @@
         <v>92.40000000000001</v>
       </c>
       <c r="E411" s="12" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="F411" s="12" t="n">
-        <v>31480.1</v>
+        <v>31519.3</v>
       </c>
       <c r="G411" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H411" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I411" s="13" t="inlineStr">
         <is>
@@ -18089,13 +18089,13 @@
         <v>296</v>
       </c>
       <c r="F412" s="12" t="n">
-        <v>3833.1</v>
+        <v>3841.4</v>
       </c>
       <c r="G412" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="H412" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I412" s="13" t="inlineStr">
         <is>
@@ -18121,16 +18121,16 @@
         <v>92.3</v>
       </c>
       <c r="E413" s="12" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="F413" s="12" t="n">
-        <v>25229.2</v>
+        <v>25251</v>
       </c>
       <c r="G413" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H413" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I413" s="13" t="inlineStr">
         <is>
@@ -18156,16 +18156,16 @@
         <v>92.09999999999999</v>
       </c>
       <c r="E414" s="12" t="n">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="F414" s="12" t="n">
-        <v>37777.9</v>
+        <v>37810.9</v>
       </c>
       <c r="G414" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="H414" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I414" s="13" t="inlineStr">
         <is>
@@ -18191,16 +18191,16 @@
         <v>91.8</v>
       </c>
       <c r="E415" s="12" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F415" s="12" t="n">
-        <v>6540.7</v>
+        <v>6549.8</v>
       </c>
       <c r="G415" s="12" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
       <c r="H415" s="12" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
       <c r="I415" s="13" t="inlineStr">
         <is>
@@ -18226,16 +18226,16 @@
         <v>91.7</v>
       </c>
       <c r="E416" s="12" t="n">
-        <v>2805</v>
+        <v>2810</v>
       </c>
       <c r="F416" s="12" t="n">
-        <v>33792.5</v>
+        <v>33839.3</v>
       </c>
       <c r="G416" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H416" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I416" s="13" t="inlineStr">
         <is>
@@ -18264,13 +18264,13 @@
         <v>2862</v>
       </c>
       <c r="F417" s="12" t="n">
-        <v>34598</v>
+        <v>34626.5</v>
       </c>
       <c r="G417" s="12" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
       <c r="H417" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I417" s="13" t="inlineStr">
         <is>
@@ -18296,16 +18296,16 @@
         <v>91.7</v>
       </c>
       <c r="E418" s="12" t="n">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="F418" s="12" t="n">
-        <v>26005.4</v>
+        <v>26027.3</v>
       </c>
       <c r="G418" s="12" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
       <c r="H418" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I418" s="13" t="inlineStr">
         <is>
@@ -18334,13 +18334,13 @@
         <v>2731</v>
       </c>
       <c r="F419" s="12" t="n">
-        <v>32566.5</v>
+        <v>32593.9</v>
       </c>
       <c r="G419" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H419" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I419" s="13" t="inlineStr">
         <is>
@@ -18366,16 +18366,16 @@
         <v>91.40000000000001</v>
       </c>
       <c r="E420" s="12" t="n">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F420" s="12" t="n">
-        <v>14893.3</v>
+        <v>14909.8</v>
       </c>
       <c r="G420" s="12" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
       <c r="H420" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="I420" s="13" t="inlineStr">
         <is>
@@ -18404,13 +18404,13 @@
         <v>242</v>
       </c>
       <c r="F421" s="12" t="n">
-        <v>2664.1</v>
+        <v>2665.7</v>
       </c>
       <c r="G421" s="12" t="n">
         <v>1503</v>
       </c>
       <c r="H421" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="I421" s="13" t="inlineStr">
         <is>
@@ -18436,16 +18436,16 @@
         <v>90.3</v>
       </c>
       <c r="E422" s="12" t="n">
-        <v>2870</v>
+        <v>2871</v>
       </c>
       <c r="F422" s="12" t="n">
-        <v>29685.6</v>
+        <v>29717.3</v>
       </c>
       <c r="G422" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H422" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I422" s="13" t="inlineStr">
         <is>
@@ -18471,16 +18471,16 @@
         <v>90.2</v>
       </c>
       <c r="E423" s="12" t="n">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F423" s="12" t="n">
-        <v>4486.7</v>
+        <v>4496.8</v>
       </c>
       <c r="G423" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H423" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I423" s="13" t="inlineStr">
         <is>
@@ -18506,16 +18506,16 @@
         <v>90.09999999999999</v>
       </c>
       <c r="E424" s="12" t="n">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="F424" s="12" t="n">
-        <v>19193.1</v>
+        <v>19218.3</v>
       </c>
       <c r="G424" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H424" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I424" s="13" t="inlineStr">
         <is>
@@ -18538,19 +18538,19 @@
         </is>
       </c>
       <c r="D425" s="12" t="n">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E425" s="12" t="n">
         <v>3652</v>
       </c>
       <c r="F425" s="12" t="n">
-        <v>35953</v>
+        <v>35985.1</v>
       </c>
       <c r="G425" s="12" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
       <c r="H425" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I425" s="14" t="inlineStr">
         <is>
@@ -18579,13 +18579,13 @@
         <v>1615</v>
       </c>
       <c r="F426" s="12" t="n">
-        <v>14329.4</v>
+        <v>14340.8</v>
       </c>
       <c r="G426" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="H426" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="I426" s="14" t="inlineStr">
         <is>
@@ -18608,19 +18608,19 @@
         </is>
       </c>
       <c r="D427" s="12" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="E427" s="12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F427" s="12" t="n">
-        <v>1693</v>
+        <v>1695.5</v>
       </c>
       <c r="G427" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H427" s="12" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I427" s="14" t="inlineStr">
         <is>
@@ -18646,16 +18646,16 @@
         <v>86.3</v>
       </c>
       <c r="E428" s="12" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F428" s="12" t="n">
-        <v>8029</v>
+        <v>8036.4</v>
       </c>
       <c r="G428" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H428" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I428" s="14" t="inlineStr">
         <is>
@@ -18678,19 +18678,19 @@
         </is>
       </c>
       <c r="D429" s="12" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="E429" s="12" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F429" s="12" t="n">
-        <v>3068.3</v>
+        <v>3074.7</v>
       </c>
       <c r="G429" s="12" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
       <c r="H429" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I429" s="14" t="inlineStr">
         <is>
@@ -18716,16 +18716,16 @@
         <v>85.5</v>
       </c>
       <c r="E430" s="12" t="n">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="F430" s="12" t="n">
-        <v>14442.7</v>
+        <v>14461.3</v>
       </c>
       <c r="G430" s="12" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
       <c r="H430" s="12" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
       <c r="I430" s="14" t="inlineStr">
         <is>
@@ -18751,16 +18751,16 @@
         <v>85.3</v>
       </c>
       <c r="E431" s="12" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F431" s="12" t="n">
-        <v>2165.4</v>
+        <v>2167.9</v>
       </c>
       <c r="G431" s="12" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
       <c r="H431" s="12" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I431" s="14" t="inlineStr">
         <is>
@@ -18786,16 +18786,16 @@
         <v>85.2</v>
       </c>
       <c r="E432" s="12" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="F432" s="12" t="n">
-        <v>4922.1</v>
+        <v>4932.1</v>
       </c>
       <c r="G432" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="H432" s="12" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I432" s="14" t="inlineStr">
         <is>
@@ -18821,16 +18821,16 @@
         <v>82.5</v>
       </c>
       <c r="E433" s="12" t="n">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="F433" s="12" t="n">
-        <v>10353.7</v>
+        <v>10368.5</v>
       </c>
       <c r="G433" s="12" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
       <c r="H433" s="12" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
       <c r="I433" s="14" t="inlineStr">
         <is>
@@ -18856,16 +18856,16 @@
         <v>82.3</v>
       </c>
       <c r="E434" s="12" t="n">
-        <v>8286</v>
+        <v>8292</v>
       </c>
       <c r="F434" s="12" t="n">
-        <v>46768.3</v>
+        <v>46803.5</v>
       </c>
       <c r="G434" s="12" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
       <c r="H434" s="12" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
       <c r="I434" s="14" t="inlineStr">
         <is>
@@ -18891,16 +18891,16 @@
         <v>80.09999999999999</v>
       </c>
       <c r="E435" s="12" t="n">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F435" s="12" t="n">
-        <v>3724.5</v>
+        <v>3730.4</v>
       </c>
       <c r="G435" s="12" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="H435" s="12" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
       <c r="I435" s="14" t="inlineStr">
         <is>
@@ -18926,16 +18926,16 @@
         <v>74.5</v>
       </c>
       <c r="E436" s="12" t="n">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="F436" s="12" t="n">
-        <v>11740.6</v>
+        <v>11753.3</v>
       </c>
       <c r="G436" s="12" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
       <c r="H436" s="12" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
       <c r="I436" s="14" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>82343</v>
+        <v>82411</v>
       </c>
     </row>
     <row r="3">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="B3" s="16" t="n">
-        <v>26563</v>
+        <v>26581</v>
       </c>
     </row>
     <row r="4">
@@ -19001,7 +19001,7 @@
         </is>
       </c>
       <c r="B4" s="16" t="n">
-        <v>20726</v>
+        <v>20745</v>
       </c>
     </row>
     <row r="5">
@@ -19011,7 +19011,7 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>17332</v>
+        <v>17348</v>
       </c>
     </row>
     <row r="6">
@@ -19021,7 +19021,7 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>15698</v>
+        <v>15713</v>
       </c>
     </row>
     <row r="7">
@@ -19031,7 +19031,7 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>14537</v>
+        <v>14549</v>
       </c>
     </row>
     <row r="8">
@@ -19041,7 +19041,7 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>13868</v>
+        <v>13895</v>
       </c>
     </row>
     <row r="9">
@@ -19051,7 +19051,7 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>12880</v>
+        <v>12891</v>
       </c>
     </row>
     <row r="10">
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>12035</v>
+        <v>12055</v>
       </c>
     </row>
     <row r="11">
@@ -19071,7 +19071,7 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>10702</v>
+        <v>10716</v>
       </c>
     </row>
     <row r="12">
@@ -19081,7 +19081,7 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>8213</v>
+        <v>8220</v>
       </c>
     </row>
     <row r="13">
@@ -19091,7 +19091,7 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>7811</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="14">
@@ -19101,7 +19101,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>7730</v>
+        <v>7737</v>
       </c>
     </row>
     <row r="15">
@@ -19111,7 +19111,7 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>7045</v>
+        <v>7053</v>
       </c>
     </row>
     <row r="16">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>5477</v>
+        <v>5486</v>
       </c>
     </row>
     <row r="17">
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>5005</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="18">
@@ -19141,7 +19141,7 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>4722</v>
+        <v>4728</v>
       </c>
     </row>
     <row r="19">
@@ -19151,7 +19151,7 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>4431</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="20">
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="B21" s="16" t="n">
-        <v>2372</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="22">
@@ -19191,7 +19191,7 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>1969</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="24">
@@ -19201,7 +19201,7 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="25">
@@ -19221,7 +19221,7 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="27">
@@ -19231,7 +19231,7 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="28">
@@ -19241,7 +19241,7 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="29">
@@ -19261,7 +19261,7 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31">

--- a/Analysis/Results/literature_gap_matrix.xlsx
+++ b/Analysis/Results/literature_gap_matrix.xlsx
@@ -2155,7 +2155,7 @@
         <v>18</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="U16" s="6" t="n">
         <v>667</v>
@@ -2185,7 +2185,7 @@
         <v>543</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="AE16" s="6" t="n">
         <v>234</v>
@@ -2349,7 +2349,7 @@
         <v>51</v>
       </c>
       <c r="T18" s="10" t="n">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>531</v>
@@ -2379,7 +2379,7 @@
         <v>360</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="AE18" s="5" t="n">
         <v>58</v>
@@ -2476,7 +2476,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AE19" s="7" t="n">
         <v>10</v>
@@ -2531,13 +2531,13 @@
         <v>223</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>81</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="S20" s="7" t="n">
         <v>16</v>
@@ -2573,10 +2573,10 @@
         <v>49</v>
       </c>
       <c r="AD20" s="10" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -2649,13 +2649,13 @@
         <v>318</v>
       </c>
       <c r="W21" s="10" t="n">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>10</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Z21" s="7" t="n">
         <v>15</v>
@@ -2670,7 +2670,7 @@
         <v>24</v>
       </c>
       <c r="AD21" s="10" t="n">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="AE21" s="5" t="n">
         <v>135</v>
@@ -2837,7 +2837,7 @@
         <v>636</v>
       </c>
       <c r="U23" s="10" t="n">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="V23" s="6" t="n">
         <v>256</v>
@@ -2864,7 +2864,7 @@
         <v>677</v>
       </c>
       <c r="AD23" s="10" t="n">
-        <v>8324</v>
+        <v>8326</v>
       </c>
       <c r="AE23" s="6" t="n">
         <v>382</v>
@@ -2946,7 +2946,7 @@
         <v>1987</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Z24" s="7" t="n">
         <v>13</v>
@@ -3031,7 +3031,7 @@
         <v>91</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V25" s="7" t="n">
         <v>18</v>
@@ -3040,7 +3040,7 @@
         <v>254</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="Y25" s="4" t="n">
         <v>7108</v>
@@ -3252,7 +3252,7 @@
         <v>329</v>
       </c>
       <c r="AD27" s="10" t="n">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AE27" s="6" t="n">
         <v>285</v>
@@ -3501,28 +3501,28 @@
         <v>881</v>
       </c>
       <c r="P30" s="10" t="n">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>389</v>
       </c>
       <c r="R30" s="10" t="n">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T30" s="10" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="V30" s="6" t="n">
         <v>579</v>
       </c>
       <c r="W30" s="10" t="n">
-        <v>8324</v>
+        <v>8326</v>
       </c>
       <c r="X30" s="6" t="n">
         <v>325</v>
@@ -3534,7 +3534,7 @@
         <v>735</v>
       </c>
       <c r="AA30" s="10" t="n">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="AB30" s="7" t="n">
         <v>46</v>
@@ -3610,7 +3610,7 @@
         <v>10</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U31" s="5" t="n">
         <v>135</v>
@@ -9406,7 +9406,7 @@
         <v>99.40000000000001</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F164" s="12" t="n">
         <v>10198.6</v>
@@ -10141,7 +10141,7 @@
         <v>99.3</v>
       </c>
       <c r="E185" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F185" s="12" t="n">
         <v>8818.9</v>
@@ -13524,28 +13524,28 @@
       </c>
       <c r="B282" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>CV Complications</t>
         </is>
       </c>
       <c r="C282" s="12" t="inlineStr">
         <is>
-          <t>Prevention / DPP</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D282" s="12" t="n">
         <v>98.2</v>
       </c>
       <c r="E282" s="12" t="n">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="F282" s="12" t="n">
-        <v>7191.1</v>
+        <v>13780.1</v>
       </c>
       <c r="G282" s="12" t="n">
-        <v>625</v>
+        <v>26715</v>
       </c>
       <c r="H282" s="12" t="n">
-        <v>82739</v>
+        <v>7108</v>
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
@@ -13559,28 +13559,28 @@
       </c>
       <c r="B283" s="12" t="inlineStr">
         <is>
-          <t>CV Complications</t>
+          <t>Epigenetics</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>AI / ML Predict</t>
         </is>
       </c>
       <c r="D283" s="12" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E283" s="12" t="n">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="F283" s="12" t="n">
-        <v>13780.1</v>
+        <v>9778.200000000001</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>26715</v>
+        <v>7861</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>7108</v>
+        <v>12163</v>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
@@ -13594,28 +13594,28 @@
       </c>
       <c r="B284" s="12" t="inlineStr">
         <is>
-          <t>Epigenetics</t>
+          <t>GLP-1 Agonists</t>
         </is>
       </c>
       <c r="C284" s="12" t="inlineStr">
         <is>
-          <t>AI / ML Predict</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D284" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E284" s="12" t="n">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="F284" s="12" t="n">
-        <v>9778.200000000001</v>
+        <v>2961.3</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>7861</v>
+        <v>14031</v>
       </c>
       <c r="H284" s="12" t="n">
-        <v>12163</v>
+        <v>625</v>
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
@@ -13634,23 +13634,23 @@
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>CGM Technology</t>
         </is>
       </c>
       <c r="D285" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E285" s="12" t="n">
-        <v>56</v>
+        <v>187</v>
       </c>
       <c r="F285" s="12" t="n">
-        <v>2961.3</v>
+        <v>9986.6</v>
       </c>
       <c r="G285" s="12" t="n">
         <v>14031</v>
       </c>
       <c r="H285" s="12" t="n">
-        <v>625</v>
+        <v>7108</v>
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
@@ -13664,28 +13664,28 @@
       </c>
       <c r="B286" s="12" t="inlineStr">
         <is>
-          <t>GLP-1 Agonists</t>
+          <t>Multi-Omics</t>
         </is>
       </c>
       <c r="C286" s="12" t="inlineStr">
         <is>
-          <t>CGM Technology</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="D286" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E286" s="12" t="n">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="F286" s="12" t="n">
-        <v>9986.6</v>
+        <v>1096.3</v>
       </c>
       <c r="G286" s="12" t="n">
-        <v>14031</v>
+        <v>1923</v>
       </c>
       <c r="H286" s="12" t="n">
-        <v>7108</v>
+        <v>625</v>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
@@ -13699,28 +13699,28 @@
       </c>
       <c r="B287" s="12" t="inlineStr">
         <is>
-          <t>Multi-Omics</t>
+          <t>Drug Repurposing</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Drug Repurposing</t>
+          <t>Prevention / DPP</t>
         </is>
       </c>
       <c r="D287" s="12" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="E287" s="12" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="F287" s="12" t="n">
-        <v>1096.3</v>
+        <v>7191.1</v>
       </c>
       <c r="G287" s="12" t="n">
-        <v>1923</v>
+        <v>625</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>625</v>
+        <v>82739</v>
       </c>
       <c r="I287" s="13" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>97.7</v>
       </c>
       <c r="E306" s="12" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F306" s="12" t="n">
         <v>15040.2</v>
@@ -17841,7 +17841,7 @@
         <v>93.3</v>
       </c>
       <c r="E405" s="12" t="n">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="F405" s="12" t="n">
         <v>19771.7</v>
@@ -18051,7 +18051,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="E411" s="12" t="n">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="F411" s="12" t="n">
         <v>31723.1</v>
@@ -18156,7 +18156,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="E414" s="12" t="n">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="F414" s="12" t="n">
         <v>37979.9</v>
@@ -18226,7 +18226,7 @@
         <v>91.8</v>
       </c>
       <c r="E416" s="12" t="n">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="F416" s="12" t="n">
         <v>34795.4</v>
@@ -18296,7 +18296,7 @@
         <v>91.7</v>
       </c>
       <c r="E418" s="12" t="n">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="F418" s="12" t="n">
         <v>26106</v>
@@ -18331,7 +18331,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="E419" s="12" t="n">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="F419" s="12" t="n">
         <v>32764.9</v>
@@ -18681,7 +18681,7 @@
         <v>85.5</v>
       </c>
       <c r="E429" s="12" t="n">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="F429" s="12" t="n">
         <v>14561.9</v>
@@ -18856,7 +18856,7 @@
         <v>82.3</v>
       </c>
       <c r="E434" s="12" t="n">
-        <v>8324</v>
+        <v>8326</v>
       </c>
       <c r="F434" s="12" t="n">
         <v>47014.6</v>
@@ -18891,7 +18891,7 @@
         <v>80</v>
       </c>
       <c r="E435" s="12" t="n">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F435" s="12" t="n">
         <v>3758.1</v>
